--- a/KPH-AI.xlsx
+++ b/KPH-AI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="372">
   <si>
     <t>Praziluk</t>
   </si>
@@ -746,9 +746,6 @@
   </si>
   <si>
     <t>Mesane zitarice</t>
-  </si>
-  <si>
-    <t>spagete</t>
   </si>
   <si>
     <t>caj biljni + secer</t>
@@ -1231,6 +1228,24 @@
   </si>
   <si>
     <t>Sok Tonic water</t>
+  </si>
+  <si>
+    <t>Spagete</t>
+  </si>
+  <si>
+    <t>Burek sa sirom</t>
+  </si>
+  <si>
+    <t>Burek sa mesom</t>
+  </si>
+  <si>
+    <t>Burek sa jabukama</t>
+  </si>
+  <si>
+    <t>Pita sa visnjama</t>
+  </si>
+  <si>
+    <t>Pita sa spanacem</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1352,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1376,6 +1391,12 @@
         </stop>
       </gradientFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1404,7 +1425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1510,6 +1531,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1643,6 +1667,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF99"/>
       <color rgb="FFCCFF99"/>
       <color rgb="FF99FF66"/>
       <color rgb="FF008000"/>
@@ -1650,7 +1675,6 @@
       <color rgb="FFFF7C80"/>
       <color rgb="FFC6E6A2"/>
       <color rgb="FF66FFFF"/>
-      <color rgb="FFFFFF99"/>
       <color rgb="FFFFCC00"/>
       <color rgb="FFFFFFFF"/>
     </mruColors>
@@ -1951,7 +1975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D365"/>
+  <dimension ref="A1:D370"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54.8984375" style="37" customWidth="1"/>
@@ -1975,7 +1999,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B2" s="4">
         <v>300</v>
@@ -1989,7 +2013,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B3" s="4">
         <v>245</v>
@@ -2017,7 +2041,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B5" s="4">
         <v>330</v>
@@ -2087,7 +2111,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B10" s="4">
         <v>150</v>
@@ -2101,7 +2125,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B11" s="4">
         <v>125</v>
@@ -2115,7 +2139,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B12" s="4">
         <v>370</v>
@@ -2143,7 +2167,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B14" s="4">
         <v>220</v>
@@ -2157,7 +2181,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B15" s="4">
         <v>289</v>
@@ -2213,7 +2237,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B19" s="4">
         <v>220</v>
@@ -2227,7 +2251,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B20" s="4">
         <v>300</v>
@@ -2269,7 +2293,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B23" s="4">
         <v>315</v>
@@ -2325,7 +2349,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B27" s="4">
         <v>310</v>
@@ -2479,7 +2503,7 @@
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1">
       <c r="A38" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B38" s="4">
         <v>281</v>
@@ -2493,7 +2517,7 @@
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1">
       <c r="A39" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B39" s="4">
         <v>320</v>
@@ -2591,7 +2615,7 @@
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1">
       <c r="A46" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B46" s="4">
         <v>263</v>
@@ -2619,7 +2643,7 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1">
       <c r="A48" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B48" s="4">
         <v>207</v>
@@ -2689,7 +2713,7 @@
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1">
       <c r="A53" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B53" s="4">
         <v>285</v>
@@ -2703,7 +2727,7 @@
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1">
       <c r="A54" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B54" s="4">
         <v>310</v>
@@ -2759,7 +2783,7 @@
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1">
       <c r="A58" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B58" s="4">
         <v>800</v>
@@ -2843,7 +2867,7 @@
     </row>
     <row r="64" spans="1:4" ht="15" customHeight="1">
       <c r="A64" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B64" s="4">
         <v>200</v>
@@ -2857,7 +2881,7 @@
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1">
       <c r="A65" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B65" s="4">
         <v>335</v>
@@ -2927,7 +2951,7 @@
     </row>
     <row r="70" spans="1:4" ht="15" customHeight="1">
       <c r="A70" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B70" s="4">
         <v>194</v>
@@ -2941,7 +2965,7 @@
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1">
       <c r="A71" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B71" s="4">
         <v>275</v>
@@ -2955,7 +2979,7 @@
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1">
       <c r="A72" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B72" s="4">
         <v>405</v>
@@ -2969,7 +2993,7 @@
     </row>
     <row r="73" spans="1:4" ht="15" customHeight="1">
       <c r="A73" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B73" s="4">
         <v>133</v>
@@ -3025,7 +3049,7 @@
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1">
       <c r="A77" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B77" s="4">
         <v>245</v>
@@ -3039,7 +3063,7 @@
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1">
       <c r="A78" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B78" s="4">
         <v>280</v>
@@ -3053,7 +3077,7 @@
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1">
       <c r="A79" s="38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B79" s="4">
         <v>250</v>
@@ -3067,7 +3091,7 @@
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1">
       <c r="A80" s="38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B80" s="4">
         <v>220</v>
@@ -3095,7 +3119,7 @@
     </row>
     <row r="82" spans="1:4" ht="15" customHeight="1">
       <c r="A82" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B82" s="4">
         <v>362</v>
@@ -3207,7 +3231,7 @@
     </row>
     <row r="90" spans="1:4" ht="15" customHeight="1">
       <c r="A90" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B90" s="4">
         <v>310</v>
@@ -3235,7 +3259,7 @@
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1">
       <c r="A92" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B92" s="5">
         <v>439</v>
@@ -3249,7 +3273,7 @@
     </row>
     <row r="93" spans="1:4" ht="15" customHeight="1">
       <c r="A93" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B93" s="4">
         <v>328</v>
@@ -3263,7 +3287,7 @@
     </row>
     <row r="94" spans="1:4" ht="15" customHeight="1">
       <c r="A94" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B94" s="4">
         <v>400</v>
@@ -3275,7 +3299,7 @@
     </row>
     <row r="95" spans="1:4" ht="15" customHeight="1">
       <c r="A95" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B95" s="4">
         <v>294</v>
@@ -3289,7 +3313,7 @@
     </row>
     <row r="96" spans="1:4" ht="15" customHeight="1">
       <c r="A96" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B96" s="4">
         <v>396</v>
@@ -3303,7 +3327,7 @@
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
       <c r="A97" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B97" s="4">
         <v>324</v>
@@ -3317,7 +3341,7 @@
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
       <c r="A98" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B98" s="4">
         <v>330</v>
@@ -3331,7 +3355,7 @@
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
       <c r="A99" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B99" s="4">
         <v>441</v>
@@ -3345,7 +3369,7 @@
     </row>
     <row r="100" spans="1:4" ht="15" customHeight="1">
       <c r="A100" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B100" s="4">
         <v>630</v>
@@ -3357,7 +3381,7 @@
     </row>
     <row r="101" spans="1:4" ht="15" customHeight="1">
       <c r="A101" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B101" s="4">
         <v>400</v>
@@ -3369,7 +3393,7 @@
     </row>
     <row r="102" spans="1:4" ht="15" customHeight="1">
       <c r="A102" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B102" s="4">
         <v>299</v>
@@ -3383,7 +3407,7 @@
     </row>
     <row r="103" spans="1:4" ht="15" customHeight="1">
       <c r="A103" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B103" s="4">
         <v>306</v>
@@ -3397,7 +3421,7 @@
     </row>
     <row r="104" spans="1:4" ht="15" customHeight="1">
       <c r="A104" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B104" s="4">
         <v>349</v>
@@ -3411,7 +3435,7 @@
     </row>
     <row r="105" spans="1:4" ht="15" customHeight="1">
       <c r="A105" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B105" s="4">
         <v>340</v>
@@ -3425,7 +3449,7 @@
     </row>
     <row r="106" spans="1:4" ht="15" customHeight="1">
       <c r="A106" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B106" s="5">
         <v>427</v>
@@ -3439,7 +3463,7 @@
     </row>
     <row r="107" spans="1:4" ht="15" customHeight="1">
       <c r="A107" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B107" s="4">
         <v>268</v>
@@ -3453,7 +3477,7 @@
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
       <c r="A108" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B108" s="4">
         <v>352</v>
@@ -3467,7 +3491,7 @@
     </row>
     <row r="109" spans="1:4" ht="15" customHeight="1">
       <c r="A109" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B109" s="4">
         <v>168</v>
@@ -3481,7 +3505,7 @@
     </row>
     <row r="110" spans="1:4" ht="15" customHeight="1">
       <c r="A110" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B110" s="4">
         <v>182</v>
@@ -3495,7 +3519,7 @@
     </row>
     <row r="111" spans="1:4" ht="15" customHeight="1">
       <c r="A111" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B111" s="5">
         <v>637</v>
@@ -3509,7 +3533,7 @@
     </row>
     <row r="112" spans="1:4" ht="15" customHeight="1">
       <c r="A112" s="23" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B112" s="5">
         <v>351</v>
@@ -3535,7 +3559,7 @@
     </row>
     <row r="114" spans="1:4" ht="15" customHeight="1">
       <c r="A114" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B114" s="5">
         <v>430</v>
@@ -3549,7 +3573,7 @@
     </row>
     <row r="115" spans="1:4" ht="15" customHeight="1">
       <c r="A115" s="15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B115" s="4">
         <v>267</v>
@@ -3563,7 +3587,7 @@
     </row>
     <row r="116" spans="1:4" ht="15" customHeight="1">
       <c r="A116" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B116" s="4">
         <v>280</v>
@@ -3577,7 +3601,7 @@
     </row>
     <row r="117" spans="1:4" ht="15" customHeight="1">
       <c r="A117" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B117" s="4">
         <v>149</v>
@@ -3591,7 +3615,7 @@
     </row>
     <row r="118" spans="1:4" ht="15" customHeight="1">
       <c r="A118" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B118" s="4">
         <v>158</v>
@@ -3605,7 +3629,7 @@
     </row>
     <row r="119" spans="1:4" ht="15" customHeight="1">
       <c r="A119" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B119" s="4">
         <v>205</v>
@@ -3619,7 +3643,7 @@
     </row>
     <row r="120" spans="1:4" ht="15" customHeight="1">
       <c r="A120" s="19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B120" s="4">
         <v>158</v>
@@ -3633,7 +3657,7 @@
     </row>
     <row r="121" spans="1:4" ht="15" customHeight="1">
       <c r="A121" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B121" s="4">
         <v>136</v>
@@ -3801,7 +3825,7 @@
     </row>
     <row r="133" spans="1:4" ht="15" customHeight="1">
       <c r="A133" s="15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B133" s="4">
         <v>132</v>
@@ -3815,7 +3839,7 @@
     </row>
     <row r="134" spans="1:4" ht="15" customHeight="1">
       <c r="A134" s="15" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B134" s="4">
         <v>120</v>
@@ -3829,7 +3853,7 @@
     </row>
     <row r="135" spans="1:4" ht="15" customHeight="1">
       <c r="A135" s="15" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B135" s="4">
         <v>102</v>
@@ -3843,7 +3867,7 @@
     </row>
     <row r="136" spans="1:4" ht="15" customHeight="1">
       <c r="A136" s="15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B136" s="4">
         <v>95</v>
@@ -3857,7 +3881,7 @@
     </row>
     <row r="137" spans="1:4" ht="15" customHeight="1">
       <c r="A137" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B137" s="4">
         <v>87</v>
@@ -3871,7 +3895,7 @@
     </row>
     <row r="138" spans="1:4" ht="15" customHeight="1">
       <c r="A138" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B138" s="4">
         <v>107</v>
@@ -3885,7 +3909,7 @@
     </row>
     <row r="139" spans="1:4" ht="15" customHeight="1">
       <c r="A139" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B139" s="4">
         <v>62</v>
@@ -3899,7 +3923,7 @@
     </row>
     <row r="140" spans="1:4" ht="15" customHeight="1">
       <c r="A140" s="15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B140" s="4">
         <v>76</v>
@@ -3913,7 +3937,7 @@
     </row>
     <row r="141" spans="1:4" ht="15" customHeight="1">
       <c r="A141" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B141" s="4">
         <v>123</v>
@@ -3927,7 +3951,7 @@
     </row>
     <row r="142" spans="1:4" ht="15" customHeight="1">
       <c r="A142" s="15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B142" s="4">
         <v>81</v>
@@ -3941,7 +3965,7 @@
     </row>
     <row r="143" spans="1:4" ht="15" customHeight="1">
       <c r="A143" s="15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B143" s="4">
         <v>128</v>
@@ -3955,7 +3979,7 @@
     </row>
     <row r="144" spans="1:4" ht="15" customHeight="1">
       <c r="A144" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B144" s="4">
         <v>38</v>
@@ -3997,7 +4021,7 @@
     </row>
     <row r="147" spans="1:4" ht="15" customHeight="1">
       <c r="A147" s="20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B147" s="4">
         <v>190</v>
@@ -4011,7 +4035,7 @@
     </row>
     <row r="148" spans="1:4" ht="15" customHeight="1">
       <c r="A148" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B148" s="4">
         <v>190</v>
@@ -4025,7 +4049,7 @@
     </row>
     <row r="149" spans="1:4" ht="15" customHeight="1">
       <c r="A149" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B149" s="4">
         <v>149</v>
@@ -4039,7 +4063,7 @@
     </row>
     <row r="150" spans="1:4" ht="15" customHeight="1">
       <c r="A150" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B150" s="4">
         <v>147</v>
@@ -4053,7 +4077,7 @@
     </row>
     <row r="151" spans="1:4" ht="15" customHeight="1">
       <c r="A151" s="15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B151" s="4">
         <v>130</v>
@@ -4067,7 +4091,7 @@
     </row>
     <row r="152" spans="1:4" ht="15" customHeight="1">
       <c r="A152" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B152" s="4">
         <v>210</v>
@@ -4081,7 +4105,7 @@
     </row>
     <row r="153" spans="1:4" ht="15" customHeight="1">
       <c r="A153" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B153" s="4">
         <v>233</v>
@@ -4095,7 +4119,7 @@
     </row>
     <row r="154" spans="1:4" ht="15" customHeight="1">
       <c r="A154" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B154" s="4">
         <v>132</v>
@@ -4109,7 +4133,7 @@
     </row>
     <row r="155" spans="1:4" ht="15" customHeight="1">
       <c r="A155" s="16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B155" s="6">
         <v>142</v>
@@ -4193,7 +4217,7 @@
     </row>
     <row r="161" spans="1:4" ht="15" customHeight="1">
       <c r="A161" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B161" s="12">
         <v>0</v>
@@ -4207,7 +4231,7 @@
     </row>
     <row r="162" spans="1:4" ht="15" customHeight="1">
       <c r="A162" s="20" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B162" s="4">
         <v>130</v>
@@ -4221,7 +4245,7 @@
     </row>
     <row r="163" spans="1:4" ht="15" customHeight="1">
       <c r="A163" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B163" s="5">
         <v>570</v>
@@ -4235,7 +4259,7 @@
     </row>
     <row r="164" spans="1:4" ht="15" customHeight="1">
       <c r="A164" s="15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B164" s="4">
         <v>310</v>
@@ -4249,7 +4273,7 @@
     </row>
     <row r="165" spans="1:4" ht="15" customHeight="1">
       <c r="A165" s="15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B165" s="5">
         <v>455</v>
@@ -4263,7 +4287,7 @@
     </row>
     <row r="166" spans="1:4" ht="15" customHeight="1">
       <c r="A166" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B166" s="4">
         <v>350</v>
@@ -4277,7 +4301,7 @@
     </row>
     <row r="167" spans="1:4" ht="15" customHeight="1">
       <c r="A167" s="18" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B167" s="5">
         <v>500</v>
@@ -4291,7 +4315,7 @@
     </row>
     <row r="168" spans="1:4" ht="15" customHeight="1">
       <c r="A168" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B168" s="5">
         <v>460</v>
@@ -4305,7 +4329,7 @@
     </row>
     <row r="169" spans="1:4" ht="15" customHeight="1">
       <c r="A169" s="18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B169" s="5">
         <v>1275</v>
@@ -5073,7 +5097,7 @@
     </row>
     <row r="224" spans="1:4" ht="15" customHeight="1">
       <c r="A224" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>10</v>
@@ -5101,7 +5125,7 @@
     </row>
     <row r="226" spans="1:4" ht="15" customHeight="1">
       <c r="A226" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B226" s="4">
         <v>43</v>
@@ -5115,7 +5139,7 @@
     </row>
     <row r="227" spans="1:4" ht="15" customHeight="1">
       <c r="A227" s="20" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B227" s="4">
         <v>131</v>
@@ -5171,7 +5195,7 @@
     </row>
     <row r="231" spans="1:4" ht="15" customHeight="1">
       <c r="A231" s="15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B231" s="5">
         <v>450</v>
@@ -5185,7 +5209,7 @@
     </row>
     <row r="232" spans="1:4" ht="15" customHeight="1">
       <c r="A232" s="15" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B232" s="5">
         <v>422</v>
@@ -5199,7 +5223,7 @@
     </row>
     <row r="233" spans="1:4" ht="15" customHeight="1">
       <c r="A233" s="15" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B233" s="4">
         <v>346</v>
@@ -5659,7 +5683,7 @@
     </row>
     <row r="266" spans="1:4" ht="15" customHeight="1">
       <c r="A266" s="33" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B266" s="4">
         <v>140</v>
@@ -5993,7 +6017,7 @@
     </row>
     <row r="290" spans="1:4" ht="15" customHeight="1">
       <c r="A290" s="15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B290" s="5">
         <v>500</v>
@@ -6133,7 +6157,7 @@
     </row>
     <row r="300" spans="1:4" ht="15" customHeight="1">
       <c r="A300" s="21" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B300" s="4">
         <v>100</v>
@@ -6175,7 +6199,7 @@
     </row>
     <row r="303" spans="1:4" ht="15" customHeight="1">
       <c r="A303" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B303" s="4">
         <v>130</v>
@@ -6203,7 +6227,7 @@
     </row>
     <row r="305" spans="1:4" ht="15" customHeight="1">
       <c r="A305" s="21" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B305" s="4">
         <v>0</v>
@@ -6243,7 +6267,7 @@
     </row>
     <row r="308" spans="1:4" ht="15" customHeight="1">
       <c r="A308" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B308" s="5">
         <v>400</v>
@@ -6271,7 +6295,7 @@
     </row>
     <row r="310" spans="1:4" ht="15" customHeight="1">
       <c r="A310" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B310" s="5">
         <v>452</v>
@@ -6635,7 +6659,7 @@
     </row>
     <row r="336" spans="1:4" ht="15" customHeight="1">
       <c r="A336" s="25" t="s">
-        <v>244</v>
+        <v>366</v>
       </c>
       <c r="B336" s="4">
         <v>70</v>
@@ -6648,378 +6672,382 @@
       </c>
     </row>
     <row r="337" spans="1:4" ht="15" customHeight="1">
-      <c r="A337" s="20" t="s">
-        <v>357</v>
+      <c r="A337" s="39" t="s">
+        <v>367</v>
       </c>
       <c r="B337" s="4">
+        <v>160</v>
+      </c>
+      <c r="C337" s="2">
         <v>150</v>
       </c>
-      <c r="C337" s="2">
-        <v>110</v>
-      </c>
       <c r="D337" s="7">
-        <v>-500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15" customHeight="1">
-      <c r="A338" s="20" t="s">
-        <v>358</v>
+      <c r="A338" s="39" t="s">
+        <v>369</v>
       </c>
       <c r="B338" s="4">
+        <v>120</v>
+      </c>
+      <c r="C338" s="2">
+        <v>50</v>
+      </c>
+      <c r="D338" s="7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" ht="15" customHeight="1">
+      <c r="A339" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="B339" s="4">
+        <v>220</v>
+      </c>
+      <c r="C339" s="2">
+        <v>170</v>
+      </c>
+      <c r="D339" s="7">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" ht="15" customHeight="1">
+      <c r="A340" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="B340" s="4">
         <v>100</v>
       </c>
-      <c r="C338" s="2">
-        <v>95</v>
-      </c>
-      <c r="D338" s="7">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" ht="15" customHeight="1">
-      <c r="A339" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="B339" s="4">
+      <c r="C340" s="2">
+        <v>40</v>
+      </c>
+      <c r="D340" s="7">
         <v>100</v>
       </c>
-      <c r="C339" s="2">
-        <v>95</v>
-      </c>
-      <c r="D339" s="7">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" ht="15" customHeight="1">
-      <c r="A340" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="B340" s="4">
-        <v>145</v>
-      </c>
-      <c r="C340" s="2">
-        <v>135</v>
-      </c>
-      <c r="D340" s="7">
-        <v>-500</v>
-      </c>
     </row>
     <row r="341" spans="1:4" ht="15" customHeight="1">
-      <c r="A341" s="20" t="s">
-        <v>361</v>
+      <c r="A341" s="39" t="s">
+        <v>371</v>
       </c>
       <c r="B341" s="4">
-        <v>338</v>
+        <v>200</v>
       </c>
       <c r="C341" s="2">
-        <v>347</v>
+        <v>150</v>
       </c>
       <c r="D341" s="7">
-        <v>-370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15" customHeight="1">
       <c r="A342" s="20" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B342" s="4">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="C342" s="2">
-        <v>244</v>
+        <v>110</v>
       </c>
       <c r="D342" s="7">
-        <v>-370</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15" customHeight="1">
       <c r="A343" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="B343" s="4">
+        <v>100</v>
+      </c>
+      <c r="C343" s="2">
+        <v>95</v>
+      </c>
+      <c r="D343" s="7">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" ht="15" customHeight="1">
+      <c r="A344" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="B344" s="4">
+        <v>100</v>
+      </c>
+      <c r="C344" s="2">
+        <v>95</v>
+      </c>
+      <c r="D344" s="7">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="15" customHeight="1">
+      <c r="A345" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="B345" s="4">
+        <v>145</v>
+      </c>
+      <c r="C345" s="2">
+        <v>135</v>
+      </c>
+      <c r="D345" s="7">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" ht="15" customHeight="1">
+      <c r="A346" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="B346" s="4">
+        <v>338</v>
+      </c>
+      <c r="C346" s="2">
+        <v>347</v>
+      </c>
+      <c r="D346" s="7">
+        <v>-370</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" ht="15" customHeight="1">
+      <c r="A347" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B347" s="4">
+        <v>209</v>
+      </c>
+      <c r="C347" s="2">
+        <v>244</v>
+      </c>
+      <c r="D347" s="7">
+        <v>-370</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" ht="15" customHeight="1">
+      <c r="A348" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="B348" s="4">
+        <v>131</v>
+      </c>
+      <c r="C348" s="2">
+        <v>120</v>
+      </c>
+      <c r="D348" s="7">
+        <v>-635</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" ht="15" customHeight="1">
+      <c r="A349" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="B343" s="4">
-        <v>131</v>
-      </c>
-      <c r="C343" s="2">
-        <v>120</v>
-      </c>
-      <c r="D343" s="7">
-        <v>-635</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" ht="15" customHeight="1">
-      <c r="A344" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="B344" s="4">
+      <c r="B349" s="4">
         <v>1</v>
       </c>
-      <c r="C344" s="2">
+      <c r="C349" s="2">
         <v>1</v>
       </c>
-      <c r="D344" s="7"/>
-    </row>
-    <row r="345" spans="1:4" ht="15" customHeight="1">
-      <c r="A345" s="19" t="s">
+      <c r="D349" s="7"/>
+    </row>
+    <row r="350" spans="1:4" ht="15" customHeight="1">
+      <c r="A350" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B345" s="4">
+      <c r="B350" s="4">
         <v>1</v>
-      </c>
-      <c r="C345" s="2">
-        <v>1</v>
-      </c>
-      <c r="D345" s="7"/>
-    </row>
-    <row r="346" spans="1:4" ht="15" customHeight="1">
-      <c r="A346" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="B346" s="4">
-        <v>1</v>
-      </c>
-      <c r="C346" s="2">
-        <v>15</v>
-      </c>
-      <c r="D346" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" ht="15" customHeight="1">
-      <c r="A347" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B347" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="C347" s="2">
-        <v>1</v>
-      </c>
-      <c r="D347" s="7"/>
-    </row>
-    <row r="348" spans="1:4" ht="15" customHeight="1">
-      <c r="A348" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B348" s="4">
-        <v>7.5</v>
-      </c>
-      <c r="C348" s="2">
-        <v>1</v>
-      </c>
-      <c r="D348" s="7"/>
-    </row>
-    <row r="349" spans="1:4" ht="15" customHeight="1">
-      <c r="A349" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="B349" s="4">
-        <v>9</v>
-      </c>
-      <c r="C349" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D349" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" ht="15" customHeight="1">
-      <c r="A350" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="B350" s="4">
-        <v>37</v>
       </c>
       <c r="C350" s="2">
         <v>1</v>
       </c>
-      <c r="D350" s="7">
-        <v>3</v>
-      </c>
+      <c r="D350" s="7"/>
     </row>
     <row r="351" spans="1:4" ht="15" customHeight="1">
-      <c r="A351" s="20" t="s">
-        <v>247</v>
+      <c r="A351" s="28" t="s">
+        <v>253</v>
       </c>
       <c r="B351" s="4">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="C351" s="2">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D351" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15" customHeight="1">
-      <c r="A352" s="20" t="s">
-        <v>114</v>
+      <c r="A352" s="21" t="s">
+        <v>122</v>
       </c>
       <c r="B352" s="4">
-        <v>549</v>
+        <v>10.8</v>
       </c>
       <c r="C352" s="2">
-        <v>152</v>
-      </c>
-      <c r="D352" s="7">
-        <v>26</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D352" s="7"/>
     </row>
     <row r="353" spans="1:4" ht="15" customHeight="1">
-      <c r="A353" s="20" t="s">
-        <v>126</v>
+      <c r="A353" s="21" t="s">
+        <v>121</v>
       </c>
       <c r="B353" s="4">
-        <v>150</v>
+        <v>7.5</v>
       </c>
       <c r="C353" s="2">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="D353" s="7"/>
     </row>
     <row r="354" spans="1:4" ht="15" customHeight="1">
       <c r="A354" s="21" t="s">
-        <v>125</v>
+        <v>244</v>
       </c>
       <c r="B354" s="4">
-        <v>49</v>
-      </c>
-      <c r="C354" s="2">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D354" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15" customHeight="1">
       <c r="A355" s="21" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B355" s="4">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C355" s="2">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D355" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15" customHeight="1">
-      <c r="A356" s="21" t="s">
-        <v>249</v>
+      <c r="A356" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="B356" s="4">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="C356" s="2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D356" s="7">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15" customHeight="1">
-      <c r="A357" s="21" t="s">
-        <v>127</v>
+      <c r="A357" s="20" t="s">
+        <v>114</v>
       </c>
       <c r="B357" s="4">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="C357" s="2">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="D357" s="7">
-        <v>91</v>
+        <v>26</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15" customHeight="1">
-      <c r="A358" s="21" t="s">
-        <v>250</v>
+      <c r="A358" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="B358" s="4">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="C358" s="2">
-        <v>3</v>
-      </c>
-      <c r="D358" s="7">
-        <v>14</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D358" s="7"/>
     </row>
     <row r="359" spans="1:4" ht="15" customHeight="1">
       <c r="A359" s="21" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B359" s="4">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C359" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D359" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15" customHeight="1">
       <c r="A360" s="21" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B360" s="4">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C360" s="2">
-        <v>50</v>
-      </c>
-      <c r="D360" s="7"/>
+        <v>35</v>
+      </c>
+      <c r="D360" s="7">
+        <v>4</v>
+      </c>
     </row>
     <row r="361" spans="1:4" ht="15" customHeight="1">
       <c r="A361" s="21" t="s">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="B361" s="4">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="C361" s="2">
-        <v>100</v>
-      </c>
-      <c r="D361" s="7"/>
+        <v>80</v>
+      </c>
+      <c r="D361" s="7">
+        <v>39</v>
+      </c>
     </row>
     <row r="362" spans="1:4" ht="15" customHeight="1">
       <c r="A362" s="21" t="s">
-        <v>366</v>
+        <v>127</v>
       </c>
       <c r="B362" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C362" s="2">
         <v>0</v>
       </c>
       <c r="D362" s="7">
-        <v>19</v>
+        <v>91</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15" customHeight="1">
       <c r="A363" s="21" t="s">
-        <v>116</v>
+        <v>249</v>
       </c>
       <c r="B363" s="4">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="C363" s="2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D363" s="7">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15" customHeight="1">
       <c r="A364" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B364" s="4">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="C364" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D364" s="7">
         <v>3</v>
@@ -7027,15 +7055,81 @@
     </row>
     <row r="365" spans="1:4" ht="15" customHeight="1">
       <c r="A365" s="21" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B365" s="4">
+        <v>50</v>
+      </c>
+      <c r="C365" s="2">
+        <v>50</v>
+      </c>
+      <c r="D365" s="7"/>
+    </row>
+    <row r="366" spans="1:4" ht="15" customHeight="1">
+      <c r="A366" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="B366" s="4">
+        <v>10</v>
+      </c>
+      <c r="C366" s="2">
+        <v>100</v>
+      </c>
+      <c r="D366" s="7"/>
+    </row>
+    <row r="367" spans="1:4" ht="15" customHeight="1">
+      <c r="A367" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="B367" s="4">
         <v>0</v>
       </c>
-      <c r="C365" s="2">
+      <c r="C367" s="2">
         <v>0</v>
       </c>
-      <c r="D365" s="7">
+      <c r="D367" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" ht="15" customHeight="1">
+      <c r="A368" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B368" s="4">
+        <v>82</v>
+      </c>
+      <c r="C368" s="2">
+        <v>15</v>
+      </c>
+      <c r="D368" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" ht="15" customHeight="1">
+      <c r="A369" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B369" s="4">
+        <v>102</v>
+      </c>
+      <c r="C369" s="2">
+        <v>10</v>
+      </c>
+      <c r="D369" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" ht="15" customHeight="1">
+      <c r="A370" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="B370" s="4">
+        <v>0</v>
+      </c>
+      <c r="C370" s="2">
+        <v>0</v>
+      </c>
+      <c r="D370" s="7">
         <v>0</v>
       </c>
     </row>
@@ -7063,13 +7157,13 @@
       <formula>2000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B365">
+  <conditionalFormatting sqref="B2:B370">
     <cfRule type="cellIs" dxfId="5" priority="18" operator="between">
       <formula>400</formula>
       <formula>5000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B365">
+  <conditionalFormatting sqref="B1:B370">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="between">
       <formula>100</formula>
       <formula>200</formula>

--- a/KPH-AI.xlsx
+++ b/KPH-AI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="385">
   <si>
     <t>Praziluk</t>
   </si>
@@ -82,9 +82,6 @@
     <t>Krvavica</t>
   </si>
   <si>
-    <t>Hamburger</t>
-  </si>
-  <si>
     <t>Piletina kuvana</t>
   </si>
   <si>
@@ -295,9 +292,6 @@
     <t>Smokve suve</t>
   </si>
   <si>
-    <t>Jabuka sok</t>
-  </si>
-  <si>
     <t>Breskva sok</t>
   </si>
   <si>
@@ -361,9 +355,6 @@
     <t>Kakao sa mlekom</t>
   </si>
   <si>
-    <t>Pivo</t>
-  </si>
-  <si>
     <t>Vino belo 12.5% alk.</t>
   </si>
   <si>
@@ -379,12 +370,6 @@
     <t>Kuvani kukuruz</t>
   </si>
   <si>
-    <t>Red Bull 0.25</t>
-  </si>
-  <si>
-    <t>Red Bull 0.25 Shugarfree</t>
-  </si>
-  <si>
     <t>Cedjeni limun</t>
   </si>
   <si>
@@ -577,9 +562,6 @@
     <t>Kupus kiseli oceden</t>
   </si>
   <si>
-    <t>Malina sirup razreden</t>
-  </si>
-  <si>
     <t>Pirinac Smedi</t>
   </si>
   <si>
@@ -634,9 +616,6 @@
     <t>Smokve sveze</t>
   </si>
   <si>
-    <t>Grozde sok</t>
-  </si>
-  <si>
     <t>Borovnica dzem</t>
   </si>
   <si>
@@ -709,9 +688,6 @@
     <t>Kruska sok</t>
   </si>
   <si>
-    <t>Visnja sok</t>
-  </si>
-  <si>
     <t>Kompot Kruska</t>
   </si>
   <si>
@@ -748,9 +724,6 @@
     <t>Mesane zitarice</t>
   </si>
   <si>
-    <t>caj biljni + secer</t>
-  </si>
-  <si>
     <t>Caj indijski +secer</t>
   </si>
   <si>
@@ -761,9 +734,6 @@
   </si>
   <si>
     <t>Kafa s pavlakom +secer</t>
-  </si>
-  <si>
-    <t>Sok Narandza i slicno</t>
   </si>
   <si>
     <t>Zestoka pica 40 % alk.</t>
@@ -787,20 +757,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Coca Cola Fosforna </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>aditivi fosf.kiselina E338</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Boza </t>
     </r>
     <r>
@@ -937,12 +893,6 @@
   </si>
   <si>
     <t>Riba Pastrmka</t>
-  </si>
-  <si>
-    <t>Riba Losos  P260-300</t>
-  </si>
-  <si>
-    <t>Riba Stuka P200-300  K300-400</t>
   </si>
   <si>
     <t>Riba Som</t>
@@ -1247,12 +1197,101 @@
   <si>
     <t>Pita sa spanacem</t>
   </si>
+  <si>
+    <t>Supa koksija - porcija tanjir 250ml</t>
+  </si>
+  <si>
+    <t>Supa govedja - porcija tanjir 250ml</t>
+  </si>
+  <si>
+    <t>Riba Losos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riba Stuka </t>
+  </si>
+  <si>
+    <t>Hamburger npr. Big Mack Mc.Donalds</t>
+  </si>
+  <si>
+    <t>Hamburger klasicni sa prilozima meso pola-pola jun-svinj.</t>
+  </si>
+  <si>
+    <t>Sataras - becar paprikas</t>
+  </si>
+  <si>
+    <t>Palacinke kom. Cca 60g (prazna + fil)</t>
+  </si>
+  <si>
+    <t>Sok od jabuke 50%</t>
+  </si>
+  <si>
+    <t>Sok od Narandze Orange juice 100% / cedjena</t>
+  </si>
+  <si>
+    <t>Caj biljni + secer</t>
+  </si>
+  <si>
+    <r>
+      <t>Coca Cola  +</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>E338!</t>
+    </r>
+  </si>
+  <si>
+    <t>Red Bull 0.25 clasic</t>
+  </si>
+  <si>
+    <t>Red Bull 0.25 zeroo</t>
+  </si>
+  <si>
+    <t>Sok narandza bistri/mutni</t>
+  </si>
+  <si>
+    <t>Sok CEDEVITA sa kiselom vodom</t>
+  </si>
+  <si>
+    <t>Sok CEDEVITA sa obicnom vodom</t>
+  </si>
+  <si>
+    <t>Sok Brusnica</t>
+  </si>
+  <si>
+    <t>Sok Borovnica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sok Jagoda </t>
+  </si>
+  <si>
+    <t>Sok Ananas</t>
+  </si>
+  <si>
+    <t>Sok Visnja</t>
+  </si>
+  <si>
+    <t>Sok Malina sirup razreden</t>
+  </si>
+  <si>
+    <t>Sok Grozde</t>
+  </si>
+  <si>
+    <t>Pivo bezalkoholno Heineken 0.0</t>
+  </si>
+  <si>
+    <t>Pivo 5% alk.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1351,8 +1390,21 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3" tint="-0.249977111117893"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="3" tint="-0.249977111117893"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1397,6 +1449,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99FF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1425,7 +1495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1534,6 +1604,27 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1667,9 +1758,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF99FF66"/>
+      <color rgb="FFCCFF99"/>
       <color rgb="FFFFFF99"/>
-      <color rgb="FFCCFF99"/>
-      <color rgb="FF99FF66"/>
       <color rgb="FF008000"/>
       <color rgb="FFFFA7A9"/>
       <color rgb="FFFF7C80"/>
@@ -1975,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D370"/>
+  <dimension ref="A1:D383"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54.8984375" style="37" customWidth="1"/>
@@ -1999,7 +2090,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B2" s="4">
         <v>300</v>
@@ -2013,7 +2104,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="15" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="B3" s="4">
         <v>245</v>
@@ -2027,7 +2118,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B4" s="4">
         <v>360</v>
@@ -2041,7 +2132,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="15" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B5" s="4">
         <v>330</v>
@@ -2055,7 +2146,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="15" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B6" s="4">
         <v>240</v>
@@ -2069,7 +2160,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="15" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B7" s="4">
         <v>340</v>
@@ -2083,7 +2174,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="15" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B8" s="4">
         <v>340</v>
@@ -2097,7 +2188,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="15" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B9" s="4">
         <v>320</v>
@@ -2111,7 +2202,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="17" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B10" s="4">
         <v>150</v>
@@ -2125,7 +2216,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="17" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="B11" s="4">
         <v>125</v>
@@ -2138,115 +2229,115 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="15" t="s">
-        <v>264</v>
+      <c r="A12" s="17" t="s">
+        <v>365</v>
       </c>
       <c r="B12" s="4">
-        <v>370</v>
+        <v>290</v>
       </c>
       <c r="C12" s="2">
-        <v>215</v>
-      </c>
-      <c r="D12" s="7">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="D12" s="14">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="15" t="s">
-        <v>149</v>
+        <v>253</v>
       </c>
       <c r="B13" s="4">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="C13" s="2">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D13" s="7">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="15" t="s">
-        <v>265</v>
+        <v>144</v>
       </c>
       <c r="B14" s="4">
-        <v>220</v>
+        <v>331</v>
       </c>
       <c r="C14" s="2">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D14" s="7">
-        <v>66</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="15" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B15" s="4">
-        <v>289</v>
+        <v>220</v>
       </c>
       <c r="C15" s="2">
         <v>180</v>
       </c>
       <c r="D15" s="7">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="15" t="s">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="B16" s="4">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="C16" s="2">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D16" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="15" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B17" s="4">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C17" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D17" s="7">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="15" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="B18" s="4">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="C18" s="2">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D18" s="7">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="15" t="s">
-        <v>267</v>
+        <v>164</v>
       </c>
       <c r="B19" s="4">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="D19" s="7">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2254,10 +2345,10 @@
         <v>256</v>
       </c>
       <c r="B20" s="4">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="D20" s="7">
         <v>63</v>
@@ -2265,1385 +2356,1387 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="B21" s="4">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C21" s="2">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="D21" s="7">
-        <v>86</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B22" s="4">
-        <v>333</v>
+        <v>289</v>
       </c>
       <c r="C22" s="2">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="D22" s="7">
-        <v>46</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="15" t="s">
-        <v>255</v>
+        <v>166</v>
       </c>
       <c r="B23" s="4">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="C23" s="2">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="D23" s="7">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="15" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="B24" s="4">
-        <v>220</v>
+        <v>315</v>
       </c>
       <c r="C24" s="2">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="D24" s="7">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="15" t="s">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="B25" s="4">
-        <v>332</v>
+        <v>220</v>
       </c>
       <c r="C25" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D25" s="7">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="15" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="C26" s="2">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="D26" s="7">
-        <v>70</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="15" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
       <c r="B27" s="4">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C27" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D27" s="7">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="15" t="s">
-        <v>153</v>
+        <v>257</v>
       </c>
       <c r="B28" s="4">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="D28" s="7">
-        <v>84</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="15" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="B29" s="4">
-        <v>220</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2">
-        <v>270</v>
+        <v>194</v>
       </c>
       <c r="D29" s="7">
-        <v>158</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="15" t="s">
-        <v>172</v>
+        <v>12</v>
       </c>
       <c r="B30" s="4">
+        <v>220</v>
+      </c>
+      <c r="C30" s="2">
+        <v>270</v>
+      </c>
+      <c r="D30" s="7">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B31" s="4">
         <v>218</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C31" s="2">
         <v>240</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D31" s="7">
         <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1">
-      <c r="A31" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B31" s="4">
-        <v>292</v>
-      </c>
-      <c r="C31" s="2">
-        <v>358</v>
-      </c>
-      <c r="D31" s="7">
-        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B32" s="4">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2">
-        <v>435</v>
+        <v>358</v>
       </c>
       <c r="D32" s="7">
-        <v>76</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="B33" s="4">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2">
-        <v>362</v>
+        <v>435</v>
       </c>
       <c r="D33" s="7">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1">
       <c r="A34" s="15" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="B34" s="4">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="C34" s="2">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="D34" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1">
       <c r="A35" s="15" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B35" s="4">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2">
-        <v>229</v>
+        <v>340</v>
       </c>
       <c r="D35" s="7">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1">
       <c r="A36" s="15" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
       <c r="B36" s="4">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="C36" s="2">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="D36" s="7">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1">
       <c r="A37" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B37" s="4">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c r="C37" s="2">
-        <v>400</v>
+        <v>187</v>
       </c>
       <c r="D37" s="7">
-        <v>153</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1">
       <c r="A38" s="15" t="s">
-        <v>269</v>
+        <v>15</v>
       </c>
       <c r="B38" s="4">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="D38" s="7">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1">
       <c r="A39" s="15" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B39" s="4">
-        <v>320</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2">
-        <v>230</v>
+        <v>366</v>
       </c>
       <c r="D39" s="7">
-        <v>95</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1">
       <c r="A40" s="15" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="B40" s="4">
-        <v>248</v>
+        <v>320</v>
       </c>
       <c r="C40" s="2">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="D40" s="7">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1">
       <c r="A41" s="15" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B41" s="4">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C41" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D41" s="7">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1">
       <c r="A42" s="15" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="B42" s="4">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="C42" s="2">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="D42" s="7">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1">
       <c r="A43" s="15" t="s">
-        <v>177</v>
+        <v>16</v>
       </c>
       <c r="B43" s="4">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="C43" s="2">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="D43" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1">
       <c r="A44" s="15" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="B44" s="4">
+        <v>265</v>
+      </c>
+      <c r="C44" s="2">
+        <v>180</v>
+      </c>
+      <c r="D44" s="7">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1">
+      <c r="A45" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B45" s="4">
         <v>177</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C45" s="2">
         <v>182</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D45" s="7">
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="B45" s="4">
+    <row r="46" spans="1:4">
+      <c r="A46" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="B46" s="4">
         <v>173</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C46" s="2">
         <v>191</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D46" s="7">
         <v>738</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="B46" s="4">
+    <row r="47" spans="1:4" ht="15" customHeight="1">
+      <c r="A47" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="B47" s="4">
         <v>263</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C47" s="2">
         <v>190</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D47" s="7">
         <v>745</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B47" s="4">
-        <v>200</v>
-      </c>
-      <c r="C47" s="2">
-        <v>144</v>
-      </c>
-      <c r="D47" s="7">
-        <v>820</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1">
       <c r="A48" s="15" t="s">
-        <v>272</v>
+        <v>149</v>
       </c>
       <c r="B48" s="4">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C48" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D48" s="7">
-        <v>668</v>
+        <v>820</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1">
       <c r="A49" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>10</v>
+        <v>261</v>
+      </c>
+      <c r="B49" s="4">
+        <v>207</v>
       </c>
       <c r="C49" s="2">
-        <v>246</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>10</v>
+        <v>143</v>
+      </c>
+      <c r="D49" s="7">
+        <v>668</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1">
       <c r="A50" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="2">
+        <v>246</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1">
+      <c r="A51" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B51" s="4">
         <v>300</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C51" s="2">
         <v>40</v>
-      </c>
-      <c r="D50" s="7">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1">
-      <c r="A51" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B51" s="4">
-        <v>190</v>
-      </c>
-      <c r="C51" s="2">
-        <v>113</v>
       </c>
       <c r="D51" s="7">
         <v>820</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="4">
         <v>190</v>
       </c>
-      <c r="B52" s="5">
-        <v>400</v>
-      </c>
       <c r="C52" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D52" s="7">
-        <v>1600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1">
       <c r="A53" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B53" s="4">
-        <v>285</v>
+        <v>184</v>
+      </c>
+      <c r="B53" s="5">
+        <v>400</v>
       </c>
       <c r="C53" s="2">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="D53" s="7">
-        <v>1440</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1">
       <c r="A54" s="15" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B54" s="4">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="C54" s="2">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="D54" s="7">
-        <v>1130</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1">
       <c r="A55" s="15" t="s">
-        <v>20</v>
+        <v>263</v>
       </c>
       <c r="B55" s="4">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="C55" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D55" s="7">
-        <v>2240</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1">
       <c r="A56" s="15" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="B56" s="4">
+        <v>377</v>
+      </c>
+      <c r="C56" s="2">
         <v>204</v>
       </c>
-      <c r="C56" s="2">
-        <v>170</v>
-      </c>
       <c r="D56" s="7">
-        <v>941</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="B57" s="4">
+        <v>204</v>
+      </c>
+      <c r="C57" s="2">
+        <v>170</v>
+      </c>
+      <c r="D57" s="7">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15" customHeight="1">
+      <c r="A58" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="4">
         <v>377</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C58" s="2">
         <v>204</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D58" s="7">
         <v>2240</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15" customHeight="1">
-      <c r="A58" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="B58" s="4">
+    <row r="59" spans="1:4" ht="15" customHeight="1">
+      <c r="A59" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="B59" s="4">
         <v>800</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C59" s="2">
         <v>235</v>
-      </c>
-      <c r="D58" s="7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="15" customHeight="1">
-      <c r="A59" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B59" s="4">
-        <v>115</v>
-      </c>
-      <c r="C59" s="2">
-        <v>83</v>
       </c>
       <c r="D59" s="7">
         <v>400</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1">
-      <c r="A60" s="19" t="s">
-        <v>213</v>
+      <c r="A60" s="21" t="s">
+        <v>125</v>
       </c>
       <c r="B60" s="4">
+        <v>115</v>
+      </c>
+      <c r="C60" s="2">
+        <v>83</v>
+      </c>
+      <c r="D60" s="7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15" customHeight="1">
+      <c r="A61" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B61" s="4">
         <v>180</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C61" s="2">
         <v>107</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D61" s="7">
         <v>778</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="15" customHeight="1">
-      <c r="A61" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="B61" s="4">
-        <v>300</v>
-      </c>
-      <c r="C61" s="2">
-        <v>483</v>
-      </c>
-      <c r="D61" s="7">
-        <v>930</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1">
       <c r="A62" s="20" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="B62" s="4">
+        <v>300</v>
+      </c>
+      <c r="C62" s="2">
+        <v>483</v>
+      </c>
+      <c r="D62" s="7">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15" customHeight="1">
+      <c r="A63" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B63" s="4">
         <v>190</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C63" s="2">
         <v>129</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D63" s="7">
         <v>770</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15" customHeight="1">
-      <c r="A63" s="19" t="s">
+    <row r="64" spans="1:4" ht="15" customHeight="1">
+      <c r="A64" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B64" s="4">
         <v>170</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C64" s="2">
         <v>84</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D64" s="7">
         <v>350</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15" customHeight="1">
-      <c r="A64" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="B64" s="4">
+    <row r="65" spans="1:4" ht="15" customHeight="1">
+      <c r="A65" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B65" s="4">
         <v>200</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C65" s="2">
         <v>130</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D65" s="7">
         <v>830</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15" customHeight="1">
-      <c r="A65" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="B65" s="4">
+    <row r="66" spans="1:4" ht="15" customHeight="1">
+      <c r="A66" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B66" s="4">
         <v>335</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C66" s="2">
         <v>226</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D66" s="7">
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15" customHeight="1">
-      <c r="A66" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="B66" s="4">
+    <row r="67" spans="1:4" ht="15" customHeight="1">
+      <c r="A67" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="B67" s="4">
         <v>210</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C67" s="2">
         <v>178</v>
       </c>
-      <c r="D66" s="7">
-        <v>-575</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15" customHeight="1">
-      <c r="A67" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B67" s="4">
-        <v>329</v>
-      </c>
-      <c r="C67" s="2">
-        <v>270</v>
-      </c>
       <c r="D67" s="7">
-        <v>70</v>
+        <v>575</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15" customHeight="1">
       <c r="A68" s="15" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="B68" s="4">
-        <v>203</v>
+        <v>329</v>
       </c>
       <c r="C68" s="2">
-        <v>158</v>
+        <v>270</v>
       </c>
       <c r="D68" s="7">
-        <v>562</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15" customHeight="1">
       <c r="A69" s="15" t="s">
-        <v>178</v>
+        <v>363</v>
       </c>
       <c r="B69" s="4">
-        <v>313</v>
+        <v>192</v>
       </c>
       <c r="C69" s="2">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="D69" s="7">
-        <v>66</v>
+        <v>460</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15" customHeight="1">
       <c r="A70" s="15" t="s">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="B70" s="4">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="C70" s="2">
-        <v>272</v>
+        <v>180</v>
       </c>
       <c r="D70" s="7">
-        <v>64</v>
+        <v>380</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1">
       <c r="A71" s="15" t="s">
-        <v>279</v>
+        <v>173</v>
       </c>
       <c r="B71" s="4">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="C71" s="2">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="D71" s="7">
-        <v>-350</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1">
       <c r="A72" s="15" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B72" s="4">
+        <v>194</v>
+      </c>
+      <c r="C72" s="2">
+        <v>272</v>
+      </c>
+      <c r="D72" s="7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15" customHeight="1">
+      <c r="A73" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="B73" s="4">
+        <v>275</v>
+      </c>
+      <c r="C73" s="2">
+        <v>210</v>
+      </c>
+      <c r="D73" s="7">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15" customHeight="1">
+      <c r="A74" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" s="4">
         <v>405</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C74" s="2">
         <v>201</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D74" s="7">
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15" customHeight="1">
-      <c r="A73" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="B73" s="4">
+    <row r="75" spans="1:4" ht="15" customHeight="1">
+      <c r="A75" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B75" s="4">
         <v>133</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C75" s="2">
         <v>51</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D75" s="7">
         <v>117</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="15" customHeight="1">
-      <c r="A74" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="B74" s="4">
-        <v>204</v>
-      </c>
-      <c r="C74" s="2">
-        <v>156</v>
-      </c>
-      <c r="D74" s="7">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="15" customHeight="1">
-      <c r="A75" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B75" s="4">
-        <v>285</v>
-      </c>
-      <c r="C75" s="2">
-        <v>190</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-550</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15" customHeight="1">
       <c r="A76" s="20" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B76" s="4">
-        <v>280</v>
+        <v>204</v>
       </c>
       <c r="C76" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="D76" s="7">
-        <v>-670</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1">
       <c r="A77" s="20" t="s">
-        <v>281</v>
+        <v>22</v>
       </c>
       <c r="B77" s="4">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="C77" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D77" s="7">
-        <v>-560</v>
+        <v>550</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1">
       <c r="A78" s="20" t="s">
-        <v>282</v>
+        <v>154</v>
       </c>
       <c r="B78" s="4">
         <v>280</v>
       </c>
       <c r="C78" s="2">
+        <v>220</v>
+      </c>
+      <c r="D78" s="7">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15" customHeight="1">
+      <c r="A79" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="B79" s="4">
+        <v>245</v>
+      </c>
+      <c r="C79" s="2">
+        <v>199</v>
+      </c>
+      <c r="D79" s="7">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15" customHeight="1">
+      <c r="A80" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="B80" s="4">
+        <v>280</v>
+      </c>
+      <c r="C80" s="2">
         <v>203</v>
       </c>
-      <c r="D78" s="7">
-        <v>-682</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="15" customHeight="1">
-      <c r="A79" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="B79" s="4">
+      <c r="D80" s="7">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15" customHeight="1">
+      <c r="A81" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="B81" s="4">
         <v>250</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C81" s="2">
         <v>140</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D81" s="7">
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15" customHeight="1">
-      <c r="A80" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="B80" s="4">
+    <row r="82" spans="1:4" ht="15" customHeight="1">
+      <c r="A82" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="B82" s="4">
         <v>220</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C82" s="2">
         <v>130</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D82" s="7">
         <v>350</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15" customHeight="1">
-      <c r="A81" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="B81" s="4">
-        <v>330</v>
-      </c>
-      <c r="C81" s="2">
-        <v>290</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-475</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="15" customHeight="1">
-      <c r="A82" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="B82" s="4">
-        <v>362</v>
-      </c>
-      <c r="C82" s="2">
-        <v>219</v>
-      </c>
-      <c r="D82" s="7">
-        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15" customHeight="1">
       <c r="A83" s="15" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="B83" s="4">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C83" s="2">
-        <v>222</v>
+        <v>290</v>
       </c>
       <c r="D83" s="7">
-        <v>96</v>
+        <v>475</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15" customHeight="1">
       <c r="A84" s="15" t="s">
-        <v>180</v>
+        <v>272</v>
       </c>
       <c r="B84" s="4">
-        <v>250</v>
+        <v>362</v>
       </c>
       <c r="C84" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D84" s="7">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15" customHeight="1">
       <c r="A85" s="15" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B85" s="4">
-        <v>371</v>
+        <v>340</v>
       </c>
       <c r="C85" s="2">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="D85" s="7">
-        <v>-454</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15" customHeight="1">
       <c r="A86" s="15" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="B86" s="4">
-        <v>338</v>
+        <v>250</v>
       </c>
       <c r="C86" s="2">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="D86" s="7">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15" customHeight="1">
       <c r="A87" s="15" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="B87" s="4">
-        <v>260</v>
+        <v>371</v>
       </c>
       <c r="C87" s="2">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D87" s="7">
-        <v>37</v>
+        <v>454</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15" customHeight="1">
       <c r="A88" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B88" s="4">
-        <v>270</v>
+        <v>338</v>
       </c>
       <c r="C88" s="2">
-        <v>186</v>
+        <v>250</v>
       </c>
       <c r="D88" s="7">
-        <v>57</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15" customHeight="1">
       <c r="A89" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B89" s="4">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C89" s="2">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="D89" s="7">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15" customHeight="1">
       <c r="A90" s="15" t="s">
-        <v>284</v>
+        <v>25</v>
       </c>
       <c r="B90" s="4">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="C90" s="2">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="D90" s="7">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15" customHeight="1">
       <c r="A91" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B91" s="4">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="C91" s="2">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D91" s="7">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1">
       <c r="A92" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="B92" s="5">
-        <v>439</v>
+        <v>273</v>
+      </c>
+      <c r="B92" s="4">
+        <v>310</v>
       </c>
       <c r="C92" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D92" s="7">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15" customHeight="1">
       <c r="A93" s="15" t="s">
-        <v>286</v>
+        <v>27</v>
       </c>
       <c r="B93" s="4">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="C93" s="2">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="D93" s="7">
-        <v>87</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15" customHeight="1">
       <c r="A94" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="B94" s="4">
-        <v>400</v>
+        <v>274</v>
+      </c>
+      <c r="B94" s="5">
+        <v>439</v>
       </c>
       <c r="C94" s="2">
-        <v>220</v>
-      </c>
-      <c r="D94" s="7"/>
+        <v>200</v>
+      </c>
+      <c r="D94" s="7">
+        <v>60</v>
+      </c>
     </row>
     <row r="95" spans="1:4" ht="15" customHeight="1">
       <c r="A95" s="15" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="B95" s="4">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="C95" s="2">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="D95" s="7">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15" customHeight="1">
       <c r="A96" s="15" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B96" s="4">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C96" s="2">
-        <v>244</v>
-      </c>
-      <c r="D96" s="7">
-        <v>95</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="D96" s="7"/>
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
       <c r="A97" s="15" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="B97" s="4">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="C97" s="2">
-        <v>238</v>
+        <v>142</v>
       </c>
       <c r="D97" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
       <c r="A98" s="15" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="B98" s="4">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C98" s="2">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="D98" s="7">
-        <v>47</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
       <c r="A99" s="15" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B99" s="4">
-        <v>441</v>
+        <v>324</v>
       </c>
       <c r="C99" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D99" s="7">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15" customHeight="1">
       <c r="A100" s="15" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="B100" s="4">
-        <v>630</v>
+        <v>330</v>
       </c>
       <c r="C100" s="2">
-        <v>300</v>
-      </c>
-      <c r="D100" s="7"/>
+        <v>198</v>
+      </c>
+      <c r="D100" s="7">
+        <v>47</v>
+      </c>
     </row>
     <row r="101" spans="1:4" ht="15" customHeight="1">
       <c r="A101" s="15" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="B101" s="4">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="C101" s="2">
-        <v>300</v>
-      </c>
-      <c r="D101" s="7"/>
+        <v>242</v>
+      </c>
+      <c r="D101" s="7">
+        <v>40</v>
+      </c>
     </row>
     <row r="102" spans="1:4" ht="15" customHeight="1">
       <c r="A102" s="15" t="s">
-        <v>295</v>
+        <v>361</v>
       </c>
       <c r="B102" s="4">
-        <v>299</v>
+        <v>630</v>
       </c>
       <c r="C102" s="2">
-        <v>202</v>
-      </c>
-      <c r="D102" s="7">
-        <v>53</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D102" s="7"/>
     </row>
     <row r="103" spans="1:4" ht="15" customHeight="1">
       <c r="A103" s="15" t="s">
-        <v>296</v>
+        <v>362</v>
       </c>
       <c r="B103" s="4">
-        <v>306</v>
+        <v>400</v>
       </c>
       <c r="C103" s="2">
-        <v>216</v>
-      </c>
-      <c r="D103" s="7">
-        <v>46</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D103" s="7"/>
     </row>
     <row r="104" spans="1:4" ht="15" customHeight="1">
       <c r="A104" s="15" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B104" s="4">
-        <v>349</v>
+        <v>299</v>
       </c>
       <c r="C104" s="2">
-        <v>277</v>
+        <v>202</v>
       </c>
       <c r="D104" s="7">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15" customHeight="1">
       <c r="A105" s="15" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="B105" s="4">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="C105" s="2">
         <v>216</v>
       </c>
       <c r="D105" s="7">
-        <v>80</v>
+        <v>46</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15" customHeight="1">
       <c r="A106" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="B106" s="5">
-        <v>427</v>
+        <v>284</v>
+      </c>
+      <c r="B106" s="4">
+        <v>349</v>
       </c>
       <c r="C106" s="2">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="D106" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15" customHeight="1">
       <c r="A107" s="15" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="B107" s="4">
-        <v>268</v>
+        <v>340</v>
       </c>
       <c r="C107" s="2">
-        <v>285</v>
+        <v>216</v>
       </c>
       <c r="D107" s="7">
-        <v>369</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
       <c r="A108" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="B108" s="4">
+        <v>285</v>
+      </c>
+      <c r="B108" s="5">
+        <v>427</v>
+      </c>
+      <c r="C108" s="2">
+        <v>231</v>
+      </c>
+      <c r="D108" s="7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15" customHeight="1">
+      <c r="A109" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="B109" s="4">
+        <v>268</v>
+      </c>
+      <c r="C109" s="2">
+        <v>285</v>
+      </c>
+      <c r="D109" s="7">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15" customHeight="1">
+      <c r="A110" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="B110" s="4">
         <v>352</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C110" s="2">
         <v>185</v>
       </c>
-      <c r="D108" s="7">
+      <c r="D110" s="7">
         <v>380</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15" customHeight="1">
-      <c r="A109" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="B109" s="4">
+    <row r="111" spans="1:4" ht="15" customHeight="1">
+      <c r="A111" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="B111" s="4">
         <v>168</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C111" s="2">
         <v>136</v>
       </c>
-      <c r="D109" s="7">
+      <c r="D111" s="7">
         <v>244</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="15" customHeight="1">
-      <c r="A110" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="B110" s="4">
+    <row r="112" spans="1:4" ht="15" customHeight="1">
+      <c r="A112" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="B112" s="4">
         <v>182</v>
       </c>
-      <c r="C110" s="2">
+      <c r="C112" s="2">
         <v>137</v>
       </c>
-      <c r="D110" s="7">
+      <c r="D112" s="7">
         <v>224</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" ht="15" customHeight="1">
-      <c r="A111" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="B111" s="5">
-        <v>637</v>
-      </c>
-      <c r="C111" s="2">
-        <v>580</v>
-      </c>
-      <c r="D111" s="7">
-        <v>-744</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="15" customHeight="1">
-      <c r="A112" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="B112" s="5">
-        <v>351</v>
-      </c>
-      <c r="C112" s="2">
-        <v>120</v>
-      </c>
-      <c r="D112" s="7"/>
     </row>
     <row r="113" spans="1:4" ht="15" customHeight="1">
       <c r="A113" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B113" s="4">
-        <v>216</v>
+        <v>291</v>
+      </c>
+      <c r="B113" s="5">
+        <v>637</v>
       </c>
       <c r="C113" s="2">
         <v>580</v>
       </c>
       <c r="D113" s="7">
-        <v>110</v>
+        <v>744</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15" customHeight="1">
-      <c r="A114" s="15" t="s">
-        <v>306</v>
+      <c r="A114" s="23" t="s">
+        <v>292</v>
       </c>
       <c r="B114" s="5">
-        <v>430</v>
+        <v>351</v>
       </c>
       <c r="C114" s="2">
-        <v>520</v>
+        <v>120</v>
       </c>
       <c r="D114" s="7">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15" customHeight="1">
       <c r="A115" s="15" t="s">
-        <v>307</v>
+        <v>28</v>
       </c>
       <c r="B115" s="4">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="C115" s="2">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="D115" s="7">
-        <v>380</v>
+        <v>110</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15" customHeight="1">
       <c r="A116" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="B116" s="4">
+        <v>293</v>
+      </c>
+      <c r="B116" s="5">
+        <v>430</v>
+      </c>
+      <c r="C116" s="2">
+        <v>520</v>
+      </c>
+      <c r="D116" s="7">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15" customHeight="1">
+      <c r="A117" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B117" s="4">
+        <v>267</v>
+      </c>
+      <c r="C117" s="2">
+        <v>210</v>
+      </c>
+      <c r="D117" s="7">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15" customHeight="1">
+      <c r="A118" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="B118" s="4">
         <v>280</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C118" s="2">
         <v>190</v>
       </c>
-      <c r="D116" s="7">
+      <c r="D118" s="7">
         <v>420</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="15" customHeight="1">
-      <c r="A117" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="B117" s="4">
+    <row r="119" spans="1:4" ht="15" customHeight="1">
+      <c r="A119" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="B119" s="4">
         <v>149</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C119" s="2">
         <v>92</v>
       </c>
-      <c r="D117" s="7">
+      <c r="D119" s="7">
         <v>16</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15" customHeight="1">
-      <c r="A118" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="B118" s="4">
-        <v>158</v>
-      </c>
-      <c r="C118" s="2">
-        <v>93</v>
-      </c>
-      <c r="D118" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="15" customHeight="1">
-      <c r="A119" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B119" s="4">
-        <v>205</v>
-      </c>
-      <c r="C119" s="2">
-        <v>111</v>
-      </c>
-      <c r="D119" s="7">
-        <v>50</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15" customHeight="1">
       <c r="A120" s="19" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="B120" s="4">
         <v>158</v>
@@ -3656,1689 +3749,1689 @@
       </c>
     </row>
     <row r="121" spans="1:4" ht="15" customHeight="1">
-      <c r="A121" s="15" t="s">
-        <v>313</v>
+      <c r="A121" s="20" t="s">
+        <v>298</v>
       </c>
       <c r="B121" s="4">
+        <v>205</v>
+      </c>
+      <c r="C121" s="2">
+        <v>111</v>
+      </c>
+      <c r="D121" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15" customHeight="1">
+      <c r="A122" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="B122" s="4">
+        <v>158</v>
+      </c>
+      <c r="C122" s="2">
+        <v>93</v>
+      </c>
+      <c r="D122" s="7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15" customHeight="1">
+      <c r="A123" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="B123" s="4">
         <v>136</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C123" s="2">
         <v>158</v>
       </c>
-      <c r="D121" s="7">
+      <c r="D123" s="7">
         <v>44</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="15" customHeight="1">
-      <c r="A122" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B122" s="4">
-        <v>187</v>
-      </c>
-      <c r="C122" s="2">
-        <v>109</v>
-      </c>
-      <c r="D122" s="7">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="15" customHeight="1">
-      <c r="A123" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B123" s="4">
-        <v>149</v>
-      </c>
-      <c r="C123" s="2">
-        <v>87</v>
-      </c>
-      <c r="D123" s="7">
-        <v>45</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15" customHeight="1">
       <c r="A124" s="20" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B124" s="4">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="C124" s="2">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D124" s="7">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15" customHeight="1">
       <c r="A125" s="20" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="B125" s="4">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C125" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D125" s="7">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15" customHeight="1">
       <c r="A126" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B126" s="4">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C126" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D126" s="7">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15" customHeight="1">
       <c r="A127" s="20" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B127" s="4">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C127" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D127" s="7">
-        <v>70</v>
+        <v>39</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15" customHeight="1">
       <c r="A128" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B128" s="4">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C128" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D128" s="7">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15" customHeight="1">
       <c r="A129" s="20" t="s">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="B129" s="4">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C129" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D129" s="7">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15" customHeight="1">
-      <c r="A130" s="21" t="s">
+      <c r="A130" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B130" s="4">
+        <v>149</v>
+      </c>
+      <c r="C130" s="2">
+        <v>92</v>
+      </c>
+      <c r="D130" s="7">
         <v>36</v>
-      </c>
-      <c r="B130" s="4">
-        <v>112</v>
-      </c>
-      <c r="C130" s="2">
-        <v>63</v>
-      </c>
-      <c r="D130" s="7">
-        <v>41</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15" customHeight="1">
       <c r="A131" s="20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B131" s="4">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C131" s="2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D131" s="7">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15" customHeight="1">
-      <c r="A132" s="15" t="s">
-        <v>38</v>
+      <c r="A132" s="21" t="s">
+        <v>35</v>
       </c>
       <c r="B132" s="4">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="C132" s="2">
-        <v>480</v>
+        <v>63</v>
       </c>
       <c r="D132" s="7">
-        <v>987</v>
+        <v>41</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15" customHeight="1">
-      <c r="A133" s="15" t="s">
-        <v>314</v>
+      <c r="A133" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="B133" s="4">
         <v>132</v>
       </c>
       <c r="C133" s="2">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="D133" s="7">
-        <v>1170</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15" customHeight="1">
-      <c r="A134" s="15" t="s">
-        <v>315</v>
+      <c r="A134" s="20" t="s">
+        <v>366</v>
       </c>
       <c r="B134" s="4">
+        <v>150</v>
+      </c>
+      <c r="C134" s="2">
         <v>120</v>
       </c>
-      <c r="C134" s="2">
-        <v>540</v>
-      </c>
       <c r="D134" s="7">
-        <v>900</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15" customHeight="1">
       <c r="A135" s="15" t="s">
-        <v>316</v>
+        <v>37</v>
       </c>
       <c r="B135" s="4">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="C135" s="2">
-        <v>530</v>
+        <v>480</v>
       </c>
       <c r="D135" s="7">
-        <v>675</v>
+        <v>987</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15" customHeight="1">
       <c r="A136" s="15" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B136" s="4">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="C136" s="2">
-        <v>570</v>
+        <v>188</v>
       </c>
       <c r="D136" s="7">
-        <v>800</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15" customHeight="1">
       <c r="A137" s="15" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="B137" s="4">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C137" s="2">
-        <v>403</v>
+        <v>540</v>
       </c>
       <c r="D137" s="7">
-        <v>654</v>
+        <v>900</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15" customHeight="1">
       <c r="A138" s="15" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B138" s="4">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C138" s="2">
-        <v>636</v>
+        <v>530</v>
       </c>
       <c r="D138" s="7">
-        <v>450</v>
+        <v>675</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15" customHeight="1">
       <c r="A139" s="15" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="B139" s="4">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="C139" s="2">
-        <v>360</v>
+        <v>570</v>
       </c>
       <c r="D139" s="7">
-        <v>1100</v>
+        <v>800</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15" customHeight="1">
       <c r="A140" s="15" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="B140" s="4">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C140" s="2">
-        <v>443</v>
+        <v>403</v>
       </c>
       <c r="D140" s="7">
-        <v>869</v>
+        <v>654</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15" customHeight="1">
       <c r="A141" s="15" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="B141" s="4">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C141" s="2">
-        <v>356</v>
+        <v>636</v>
       </c>
       <c r="D141" s="7">
-        <v>398</v>
+        <v>450</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15" customHeight="1">
       <c r="A142" s="15" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="B142" s="4">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="C142" s="2">
-        <v>605</v>
+        <v>360</v>
       </c>
       <c r="D142" s="7">
-        <v>336</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15" customHeight="1">
       <c r="A143" s="15" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="B143" s="4">
+        <v>76</v>
+      </c>
+      <c r="C143" s="2">
+        <v>443</v>
+      </c>
+      <c r="D143" s="7">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15" customHeight="1">
+      <c r="A144" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B144" s="4">
+        <v>123</v>
+      </c>
+      <c r="C144" s="2">
+        <v>356</v>
+      </c>
+      <c r="D144" s="7">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15" customHeight="1">
+      <c r="A145" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B145" s="4">
+        <v>81</v>
+      </c>
+      <c r="C145" s="2">
+        <v>605</v>
+      </c>
+      <c r="D145" s="7">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15" customHeight="1">
+      <c r="A146" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="B146" s="4">
         <v>128</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C146" s="2">
         <v>256</v>
       </c>
-      <c r="D143" s="7">
+      <c r="D146" s="7">
         <v>1300</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="15" customHeight="1">
-      <c r="A144" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="B144" s="4">
-        <v>38</v>
-      </c>
-      <c r="C144" s="2">
-        <v>239</v>
-      </c>
-      <c r="D144" s="7">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="15" customHeight="1">
-      <c r="A145" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B145" s="4">
-        <v>55</v>
-      </c>
-      <c r="C145" s="2">
-        <v>1200</v>
-      </c>
-      <c r="D145" s="7">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="15" customHeight="1">
-      <c r="A146" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="B146" s="4">
-        <v>95</v>
-      </c>
-      <c r="C146" s="2">
-        <v>160</v>
-      </c>
-      <c r="D146" s="7">
-        <v>40</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15" customHeight="1">
       <c r="A147" s="20" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="B147" s="4">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="C147" s="2">
-        <v>100</v>
+        <v>239</v>
       </c>
       <c r="D147" s="7">
-        <v>62</v>
+        <v>137</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15" customHeight="1">
-      <c r="A148" s="20" t="s">
-        <v>327</v>
+      <c r="A148" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="B148" s="4">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="C148" s="2">
-        <v>116</v>
+        <v>1200</v>
       </c>
       <c r="D148" s="7">
-        <v>44</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15" customHeight="1">
       <c r="A149" s="20" t="s">
-        <v>328</v>
+        <v>185</v>
       </c>
       <c r="B149" s="4">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="C149" s="2">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="D149" s="7">
-        <v>62</v>
+        <v>40</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15" customHeight="1">
       <c r="A150" s="20" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="B150" s="4">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="C150" s="2">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D150" s="7">
         <v>62</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15" customHeight="1">
-      <c r="A151" s="15" t="s">
-        <v>330</v>
+      <c r="A151" s="20" t="s">
+        <v>314</v>
       </c>
       <c r="B151" s="4">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="C151" s="2">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="D151" s="7">
-        <v>133</v>
+        <v>44</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15" customHeight="1">
-      <c r="A152" s="15" t="s">
-        <v>331</v>
+      <c r="A152" s="20" t="s">
+        <v>315</v>
       </c>
       <c r="B152" s="4">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="C152" s="2">
-        <v>208</v>
+        <v>86</v>
       </c>
       <c r="D152" s="7">
-        <v>138</v>
+        <v>62</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15" customHeight="1">
-      <c r="A153" s="15" t="s">
-        <v>332</v>
+      <c r="A153" s="20" t="s">
+        <v>316</v>
       </c>
       <c r="B153" s="4">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="C153" s="2">
-        <v>220</v>
+        <v>86</v>
       </c>
       <c r="D153" s="7">
-        <v>146</v>
+        <v>62</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15" customHeight="1">
       <c r="A154" s="15" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="B154" s="4">
+        <v>130</v>
+      </c>
+      <c r="C154" s="2">
+        <v>202</v>
+      </c>
+      <c r="D154" s="7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15" customHeight="1">
+      <c r="A155" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B155" s="4">
+        <v>210</v>
+      </c>
+      <c r="C155" s="2">
+        <v>208</v>
+      </c>
+      <c r="D155" s="7">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15" customHeight="1">
+      <c r="A156" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="B156" s="4">
+        <v>233</v>
+      </c>
+      <c r="C156" s="2">
+        <v>220</v>
+      </c>
+      <c r="D156" s="7">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15" customHeight="1">
+      <c r="A157" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="B157" s="4">
         <v>132</v>
       </c>
-      <c r="C154" s="2">
+      <c r="C157" s="2">
         <v>226</v>
       </c>
-      <c r="D154" s="7">
+      <c r="D157" s="7">
         <v>141</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="15" customHeight="1">
-      <c r="A155" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="B155" s="6">
+    <row r="158" spans="1:4" ht="15" customHeight="1">
+      <c r="A158" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="B158" s="6">
         <v>142</v>
       </c>
-      <c r="C155" s="9">
+      <c r="C158" s="9">
         <v>170</v>
       </c>
-      <c r="D155" s="8">
+      <c r="D158" s="8">
         <v>151</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="15" customHeight="1">
-      <c r="A156" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B156" s="4">
-        <v>42</v>
-      </c>
-      <c r="C156" s="2">
-        <v>23</v>
-      </c>
-      <c r="D156" s="7">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="15" customHeight="1">
-      <c r="A157" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B157" s="4">
-        <v>30</v>
-      </c>
-      <c r="C157" s="2">
-        <v>16</v>
-      </c>
-      <c r="D157" s="7">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="15" customHeight="1">
-      <c r="A158" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B158" s="4">
-        <v>26</v>
-      </c>
-      <c r="C158" s="2">
-        <v>23</v>
-      </c>
-      <c r="D158" s="7">
-        <v>827</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15" customHeight="1">
       <c r="A159" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B159" s="12">
-        <v>0</v>
-      </c>
-      <c r="C159" s="13">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="B159" s="4">
+        <v>42</v>
+      </c>
+      <c r="C159" s="2">
+        <v>23</v>
       </c>
       <c r="D159" s="7">
-        <v>0</v>
+        <v>943</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15" customHeight="1">
-      <c r="A160" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B160" s="12">
-        <v>0</v>
-      </c>
-      <c r="C160" s="13">
-        <v>0</v>
+      <c r="A160" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B160" s="4">
+        <v>30</v>
+      </c>
+      <c r="C160" s="2">
+        <v>16</v>
       </c>
       <c r="D160" s="7">
-        <v>0</v>
+        <v>994</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15" customHeight="1">
       <c r="A161" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="B161" s="12">
+        <v>41</v>
+      </c>
+      <c r="B161" s="4">
+        <v>26</v>
+      </c>
+      <c r="C161" s="2">
+        <v>23</v>
+      </c>
+      <c r="D161" s="7">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15" customHeight="1">
+      <c r="A162" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B162" s="12">
         <v>0</v>
       </c>
-      <c r="C161" s="2">
+      <c r="C162" s="13">
+        <v>0</v>
+      </c>
+      <c r="D162" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="15" customHeight="1">
+      <c r="A163" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B163" s="12">
+        <v>0</v>
+      </c>
+      <c r="C163" s="13">
+        <v>0</v>
+      </c>
+      <c r="D163" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15" customHeight="1">
+      <c r="A164" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="B164" s="12">
+        <v>0</v>
+      </c>
+      <c r="C164" s="2">
         <v>28</v>
       </c>
-      <c r="D161" s="7">
+      <c r="D164" s="7">
         <v>568</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="15" customHeight="1">
-      <c r="A162" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="B162" s="4">
+    <row r="165" spans="1:4" ht="15" customHeight="1">
+      <c r="A165" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="B165" s="4">
         <v>130</v>
       </c>
-      <c r="C162" s="2">
+      <c r="C165" s="2">
         <v>73</v>
       </c>
-      <c r="D162" s="7">
+      <c r="D165" s="7">
         <v>1252</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="15" customHeight="1">
-      <c r="A163" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="B163" s="5">
-        <v>570</v>
-      </c>
-      <c r="C163" s="2">
-        <v>54</v>
-      </c>
-      <c r="D163" s="7">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="15" customHeight="1">
-      <c r="A164" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="B164" s="4">
-        <v>310</v>
-      </c>
-      <c r="C164" s="2">
-        <v>40</v>
-      </c>
-      <c r="D164" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="15" customHeight="1">
-      <c r="A165" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="B165" s="5">
-        <v>455</v>
-      </c>
-      <c r="C165" s="2">
-        <v>33</v>
-      </c>
-      <c r="D165" s="7">
-        <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15" customHeight="1">
       <c r="A166" s="15" t="s">
-        <v>339</v>
-      </c>
-      <c r="B166" s="4">
-        <v>350</v>
+        <v>324</v>
+      </c>
+      <c r="B166" s="5">
+        <v>570</v>
       </c>
       <c r="C166" s="2">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D166" s="7">
-        <v>-300</v>
+        <v>27</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15" customHeight="1">
-      <c r="A167" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="B167" s="5">
-        <v>500</v>
+      <c r="A167" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B167" s="4">
+        <v>310</v>
       </c>
       <c r="C167" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D167" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15" customHeight="1">
-      <c r="A168" s="18" t="s">
+      <c r="A168" s="15" t="s">
         <v>341</v>
       </c>
       <c r="B168" s="5">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C168" s="2">
         <v>33</v>
       </c>
       <c r="D168" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="15" customHeight="1">
+      <c r="A169" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B169" s="4">
+        <v>350</v>
+      </c>
+      <c r="C169" s="2">
+        <v>61</v>
+      </c>
+      <c r="D169" s="7">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="15" customHeight="1">
+      <c r="A170" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="B170" s="5">
+        <v>500</v>
+      </c>
+      <c r="C170" s="2">
+        <v>46</v>
+      </c>
+      <c r="D170" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15" customHeight="1">
+      <c r="A171" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="B171" s="5">
+        <v>460</v>
+      </c>
+      <c r="C171" s="2">
+        <v>33</v>
+      </c>
+      <c r="D171" s="7">
         <v>-450</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="15" customHeight="1">
-      <c r="A169" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="B169" s="5">
+    <row r="172" spans="1:4" ht="15" customHeight="1">
+      <c r="A172" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="B172" s="5">
         <v>1275</v>
       </c>
-      <c r="C169" s="2">
+      <c r="C172" s="2">
         <v>93</v>
       </c>
-      <c r="D169" s="7">
+      <c r="D172" s="7">
         <v>594</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="15" customHeight="1">
-      <c r="A170" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="B170" s="4">
-        <v>376</v>
-      </c>
-      <c r="C170" s="2">
-        <v>67</v>
-      </c>
-      <c r="D170" s="7">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="15" customHeight="1">
-      <c r="A171" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B171" s="4">
-        <v>328</v>
-      </c>
-      <c r="C171" s="2">
-        <v>54</v>
-      </c>
-      <c r="D171" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="15" customHeight="1">
-      <c r="A172" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B172" s="4">
-        <v>340</v>
-      </c>
-      <c r="C172" s="2">
-        <v>66</v>
-      </c>
-      <c r="D172" s="7">
-        <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15" customHeight="1">
       <c r="A173" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B173" s="5">
-        <v>550</v>
+        <v>157</v>
+      </c>
+      <c r="B173" s="4">
+        <v>376</v>
       </c>
       <c r="C173" s="2">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="D173" s="7">
-        <v>31</v>
+        <v>133</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15" customHeight="1">
       <c r="A174" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B174" s="5">
-        <v>490</v>
+        <v>44</v>
+      </c>
+      <c r="B174" s="4">
+        <v>328</v>
       </c>
       <c r="C174" s="2">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="D174" s="7">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15" customHeight="1">
       <c r="A175" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B175" s="5">
-        <v>464</v>
+        <v>45</v>
+      </c>
+      <c r="B175" s="4">
+        <v>340</v>
       </c>
       <c r="C175" s="2">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D175" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15" customHeight="1">
-      <c r="A176" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B176" s="4">
-        <v>227</v>
+      <c r="A176" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B176" s="5">
+        <v>550</v>
       </c>
       <c r="C176" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D176" s="7">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15" customHeight="1">
-      <c r="A177" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B177" s="4">
-        <v>266</v>
+      <c r="A177" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B177" s="5">
+        <v>490</v>
       </c>
       <c r="C177" s="2">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="D177" s="7">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15" customHeight="1">
       <c r="A178" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B178" s="4">
+        <v>48</v>
+      </c>
+      <c r="B178" s="5">
+        <v>464</v>
+      </c>
+      <c r="C178" s="2">
+        <v>82</v>
+      </c>
+      <c r="D178" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15" customHeight="1">
+      <c r="A179" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B179" s="4">
+        <v>227</v>
+      </c>
+      <c r="C179" s="2">
+        <v>27</v>
+      </c>
+      <c r="D179" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15" customHeight="1">
+      <c r="A180" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B180" s="4">
+        <v>266</v>
+      </c>
+      <c r="C180" s="2">
+        <v>30</v>
+      </c>
+      <c r="D180" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="15" customHeight="1">
+      <c r="A181" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B181" s="4">
         <v>288</v>
       </c>
-      <c r="C178" s="2">
+      <c r="C181" s="2">
         <v>43</v>
       </c>
-      <c r="D178" s="7">
+      <c r="D181" s="7">
         <v>355</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="15" customHeight="1">
-      <c r="A179" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B179" s="4">
-        <v>300</v>
-      </c>
-      <c r="C179" s="2">
-        <v>50</v>
-      </c>
-      <c r="D179" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" ht="15" customHeight="1">
-      <c r="A180" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B180" s="4">
-        <v>399</v>
-      </c>
-      <c r="C180" s="2">
-        <v>56</v>
-      </c>
-      <c r="D180" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" ht="15" customHeight="1">
-      <c r="A181" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="B181" s="5">
-        <v>1000</v>
-      </c>
-      <c r="C181" s="2">
-        <v>128</v>
-      </c>
-      <c r="D181" s="7">
-        <v>33</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15" customHeight="1">
       <c r="A182" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B182" s="4">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="C182" s="2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D182" s="7">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15" customHeight="1">
       <c r="A183" s="15" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="B183" s="4">
-        <v>322</v>
+        <v>399</v>
       </c>
       <c r="C183" s="2">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D183" s="7">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15" customHeight="1">
-      <c r="A184" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B184" s="4">
-        <v>346</v>
+      <c r="A184" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="B184" s="5">
+        <v>1000</v>
       </c>
       <c r="C184" s="2">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="D184" s="7">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15" customHeight="1">
       <c r="A185" s="15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B185" s="4">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="C185" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D185" s="7">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15" customHeight="1">
-      <c r="A186" s="20" t="s">
-        <v>56</v>
+      <c r="A186" s="15" t="s">
+        <v>158</v>
       </c>
       <c r="B186" s="4">
-        <v>215</v>
+        <v>322</v>
       </c>
       <c r="C186" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D186" s="7">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15" customHeight="1">
       <c r="A187" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="B187" s="5">
-        <v>633</v>
+        <v>53</v>
+      </c>
+      <c r="B187" s="4">
+        <v>346</v>
       </c>
       <c r="C187" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D187" s="7">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15" customHeight="1">
       <c r="A188" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B188" s="4">
+        <v>360</v>
+      </c>
+      <c r="C188" s="2">
+        <v>12</v>
+      </c>
+      <c r="D188" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15" customHeight="1">
+      <c r="A189" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B189" s="4">
+        <v>215</v>
+      </c>
+      <c r="C189" s="2">
+        <v>20</v>
+      </c>
+      <c r="D189" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15" customHeight="1">
+      <c r="A190" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B190" s="5">
+        <v>633</v>
+      </c>
+      <c r="C190" s="2">
+        <v>55</v>
+      </c>
+      <c r="D190" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15" customHeight="1">
+      <c r="A191" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B191" s="4">
         <v>291</v>
       </c>
-      <c r="C188" s="2">
+      <c r="C191" s="2">
         <v>90</v>
       </c>
-      <c r="D188" s="7">
+      <c r="D191" s="7">
         <v>98</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="15" customHeight="1">
-      <c r="A189" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B189" s="4">
+    <row r="192" spans="1:4" ht="15" customHeight="1">
+      <c r="A192" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B192" s="4">
         <v>325</v>
       </c>
-      <c r="C189" s="2">
+      <c r="C192" s="2">
         <v>44</v>
       </c>
-      <c r="D189" s="7">
+      <c r="D192" s="7">
         <v>30</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="15" customHeight="1">
-      <c r="A190" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B190" s="4">
-        <v>265</v>
-      </c>
-      <c r="C190" s="2">
-        <v>29</v>
-      </c>
-      <c r="D190" s="7">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="15" customHeight="1">
-      <c r="A191" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B191" s="5">
-        <v>554</v>
-      </c>
-      <c r="C191" s="2">
-        <v>65</v>
-      </c>
-      <c r="D191" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" ht="15" customHeight="1">
-      <c r="A192" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="B192" s="4">
-        <v>380</v>
-      </c>
-      <c r="C192" s="2">
-        <v>50</v>
-      </c>
-      <c r="D192" s="7">
-        <v>32</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15" customHeight="1">
       <c r="A193" s="20" t="s">
-        <v>218</v>
+        <v>57</v>
       </c>
       <c r="B193" s="4">
-        <v>315</v>
+        <v>265</v>
       </c>
       <c r="C193" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D193" s="7">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15" customHeight="1">
       <c r="A194" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B194" s="4">
-        <v>400</v>
+        <v>58</v>
+      </c>
+      <c r="B194" s="5">
+        <v>554</v>
       </c>
       <c r="C194" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D194" s="7">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15" customHeight="1">
       <c r="A195" s="20" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B195" s="4">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="C195" s="2">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D195" s="7">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15" customHeight="1">
       <c r="A196" s="20" t="s">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="B196" s="4">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="C196" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D196" s="7">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15" customHeight="1">
-      <c r="A197" s="15" t="s">
-        <v>63</v>
+      <c r="A197" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="B197" s="4">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="C197" s="2">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D197" s="7">
-        <v>-288</v>
+        <v>50</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15" customHeight="1">
       <c r="A198" s="20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B198" s="4">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C198" s="2">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D198" s="7">
-        <v>-235</v>
+        <v>58</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15" customHeight="1">
-      <c r="A199" s="15" t="s">
-        <v>164</v>
+      <c r="A199" s="20" t="s">
+        <v>3</v>
       </c>
       <c r="B199" s="4">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C199" s="2">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="D199" s="7">
-        <v>-455</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15" customHeight="1">
       <c r="A200" s="15" t="s">
-        <v>219</v>
+        <v>62</v>
       </c>
       <c r="B200" s="4">
-        <v>340</v>
+        <v>230</v>
       </c>
       <c r="C200" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D200" s="7">
-        <v>1</v>
+        <v>288</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15" customHeight="1">
       <c r="A201" s="15" t="s">
-        <v>165</v>
+        <v>359</v>
       </c>
       <c r="B201" s="4">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C201" s="2">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="D201" s="7">
-        <v>-212</v>
+        <v>350</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15" customHeight="1">
-      <c r="A202" s="20" t="s">
-        <v>65</v>
+      <c r="A202" s="15" t="s">
+        <v>360</v>
       </c>
       <c r="B202" s="4">
-        <v>248</v>
+        <v>180</v>
       </c>
       <c r="C202" s="2">
-        <v>37</v>
+        <v>150</v>
       </c>
       <c r="D202" s="7">
-        <v>2</v>
+        <v>327</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15" customHeight="1">
       <c r="A203" s="20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B203" s="4">
-        <v>550</v>
+        <v>200</v>
       </c>
       <c r="C203" s="2">
-        <v>230</v>
+        <v>83</v>
       </c>
       <c r="D203" s="7">
-        <v>0</v>
+        <v>235</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15" customHeight="1">
-      <c r="A204" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B204" s="5">
-        <v>1680</v>
+      <c r="A204" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B204" s="4">
+        <v>265</v>
       </c>
       <c r="C204" s="2">
-        <v>555</v>
+        <v>101</v>
       </c>
       <c r="D204" s="7">
-        <v>5</v>
+        <v>455</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15" customHeight="1">
-      <c r="A205" s="20" t="s">
-        <v>118</v>
+      <c r="A205" s="15" t="s">
+        <v>212</v>
       </c>
       <c r="B205" s="4">
-        <v>121</v>
+        <v>340</v>
       </c>
       <c r="C205" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D205" s="7">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15" customHeight="1">
-      <c r="A206" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="B206" s="5">
-        <v>1660</v>
+      <c r="A206" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B206" s="4">
+        <v>250</v>
       </c>
       <c r="C206" s="2">
-        <v>600</v>
+        <v>119</v>
       </c>
       <c r="D206" s="7">
-        <v>1</v>
+        <v>212</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15" customHeight="1">
       <c r="A207" s="20" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B207" s="4">
-        <v>137</v>
+        <v>248</v>
       </c>
       <c r="C207" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D207" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15" customHeight="1">
+      <c r="A208" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B208" s="4">
+        <v>550</v>
+      </c>
+      <c r="C208" s="2">
+        <v>230</v>
+      </c>
+      <c r="D208" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="15" customHeight="1">
-      <c r="A208" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="B208" s="4">
-        <v>140</v>
-      </c>
-      <c r="C208" s="2">
-        <v>17</v>
-      </c>
-      <c r="D208" s="7">
-        <v>13</v>
-      </c>
-    </row>
     <row r="209" spans="1:4" ht="15" customHeight="1">
-      <c r="A209" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B209" s="4">
-        <v>300</v>
+      <c r="A209" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B209" s="5">
+        <v>1680</v>
       </c>
       <c r="C209" s="2">
-        <v>114</v>
-      </c>
-      <c r="D209" s="7" t="s">
-        <v>70</v>
+        <v>555</v>
+      </c>
+      <c r="D209" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15" customHeight="1">
       <c r="A210" s="20" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B210" s="4">
-        <v>320</v>
+        <v>121</v>
       </c>
       <c r="C210" s="2">
-        <v>45</v>
-      </c>
-      <c r="D210" s="7"/>
+        <v>97</v>
+      </c>
+      <c r="D210" s="7">
+        <v>7</v>
+      </c>
     </row>
     <row r="211" spans="1:4" ht="15" customHeight="1">
-      <c r="A211" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B211" s="4">
-        <v>340</v>
+      <c r="A211" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B211" s="5">
+        <v>1660</v>
       </c>
       <c r="C211" s="2">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="D211" s="7">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15" customHeight="1">
-      <c r="A212" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="B212" s="5">
-        <v>3170</v>
+      <c r="A212" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B212" s="4">
+        <v>137</v>
       </c>
       <c r="C212" s="2">
-        <v>327</v>
+        <v>57</v>
       </c>
       <c r="D212" s="7">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15" customHeight="1">
-      <c r="A213" s="29" t="s">
-        <v>132</v>
+      <c r="A213" s="27" t="s">
+        <v>187</v>
       </c>
       <c r="B213" s="4">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C213" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D213" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15" customHeight="1">
-      <c r="A214" s="29" t="s">
-        <v>194</v>
+      <c r="A214" s="20" t="s">
+        <v>68</v>
       </c>
       <c r="B214" s="4">
-        <v>176</v>
+        <v>300</v>
       </c>
       <c r="C214" s="2">
-        <v>23</v>
-      </c>
-      <c r="D214" s="7">
-        <v>2</v>
+        <v>114</v>
+      </c>
+      <c r="D214" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15" customHeight="1">
       <c r="A215" s="20" t="s">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="B215" s="4">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="C215" s="2">
-        <v>33</v>
-      </c>
-      <c r="D215" s="7">
-        <v>2</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D215" s="7"/>
     </row>
     <row r="216" spans="1:4" ht="15" customHeight="1">
       <c r="A216" s="20" t="s">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="B216" s="4">
-        <v>275</v>
+        <v>340</v>
       </c>
       <c r="C216" s="2">
+        <v>46</v>
+      </c>
+      <c r="D216" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="15" customHeight="1">
+      <c r="A217" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B217" s="5">
+        <v>3170</v>
+      </c>
+      <c r="C217" s="2">
+        <v>327</v>
+      </c>
+      <c r="D217" s="7">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="15" customHeight="1">
+      <c r="A218" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="B218" s="4">
+        <v>129</v>
+      </c>
+      <c r="C218" s="2">
         <v>25</v>
       </c>
-      <c r="D216" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" ht="15" customHeight="1">
-      <c r="A217" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B217" s="4">
-        <v>207</v>
-      </c>
-      <c r="C217" s="2">
-        <v>46</v>
-      </c>
-      <c r="D217" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" ht="15" customHeight="1">
-      <c r="A218" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B218" s="4">
-        <v>310</v>
-      </c>
-      <c r="C218" s="2">
-        <v>19</v>
-      </c>
       <c r="D218" s="7">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15" customHeight="1">
-      <c r="A219" s="20" t="s">
-        <v>73</v>
+      <c r="A219" s="29" t="s">
+        <v>188</v>
       </c>
       <c r="B219" s="4">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C219" s="2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D219" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15" customHeight="1">
       <c r="A220" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B220" s="5">
-        <v>400</v>
+        <v>189</v>
+      </c>
+      <c r="B220" s="4">
+        <v>305</v>
       </c>
       <c r="C220" s="2">
-        <v>153</v>
+        <v>33</v>
       </c>
       <c r="D220" s="7">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15" customHeight="1">
       <c r="A221" s="20" t="s">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="B221" s="4">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="C221" s="2">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D221" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15" customHeight="1">
       <c r="A222" s="20" t="s">
-        <v>75</v>
+        <v>214</v>
       </c>
       <c r="B222" s="4">
-        <v>148</v>
+        <v>207</v>
       </c>
       <c r="C222" s="2">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D222" s="7">
-        <v>274</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15" customHeight="1">
-      <c r="A223" s="20" t="s">
-        <v>76</v>
+      <c r="A223" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="B223" s="4">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="C223" s="2">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D223" s="7">
-        <v>759</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15" customHeight="1">
       <c r="A224" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>10</v>
+        <v>72</v>
+      </c>
+      <c r="B224" s="4">
+        <v>192</v>
       </c>
       <c r="C224" s="2">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D224" s="7">
-        <v>1353</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15" customHeight="1">
       <c r="A225" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="B225" s="4">
-        <v>140</v>
+        <v>73</v>
+      </c>
+      <c r="B225" s="5">
+        <v>400</v>
       </c>
       <c r="C225" s="2">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="D225" s="7">
-        <v>650</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15" customHeight="1">
       <c r="A226" s="20" t="s">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="B226" s="4">
-        <v>43</v>
+        <v>234</v>
       </c>
       <c r="C226" s="2">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D226" s="7">
-        <v>2100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15" customHeight="1">
       <c r="A227" s="20" t="s">
-        <v>345</v>
+        <v>74</v>
       </c>
       <c r="B227" s="4">
-        <v>131</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>10</v>
+        <v>148</v>
+      </c>
+      <c r="C227" s="2">
+        <v>17</v>
       </c>
       <c r="D227" s="7">
-        <v>1248</v>
+        <v>274</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15" customHeight="1">
-      <c r="A228" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="B228" s="5">
-        <v>800</v>
+      <c r="A228" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B228" s="4">
+        <v>269</v>
       </c>
       <c r="C228" s="2">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D228" s="7">
-        <v>1200</v>
+        <v>759</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15" customHeight="1">
       <c r="A229" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="B229" s="4">
-        <v>220</v>
+        <v>330</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C229" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D229" s="7">
-        <v>360</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15" customHeight="1">
-      <c r="A230" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B230" s="5">
-        <v>1000</v>
+      <c r="A230" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B230" s="4">
+        <v>140</v>
       </c>
       <c r="C230" s="2">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D230" s="7">
-        <v>450</v>
+        <v>650</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15" customHeight="1">
-      <c r="A231" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="B231" s="5">
-        <v>450</v>
+      <c r="A231" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="B231" s="4">
+        <v>43</v>
       </c>
       <c r="C231" s="2">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="D231" s="7">
-        <v>3</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15" customHeight="1">
-      <c r="A232" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="B232" s="5">
-        <v>422</v>
-      </c>
-      <c r="C232" s="2">
-        <v>123</v>
+      <c r="A232" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B232" s="4">
+        <v>131</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D232" s="7">
-        <v>8</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15" customHeight="1">
-      <c r="A233" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="B233" s="4">
-        <v>346</v>
+      <c r="A233" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B233" s="5">
+        <v>800</v>
       </c>
       <c r="C233" s="2">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="D233" s="7">
-        <v>2</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15" customHeight="1">
       <c r="A234" s="20" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="B234" s="4">
+        <v>220</v>
+      </c>
+      <c r="C234" s="2">
+        <v>19</v>
+      </c>
+      <c r="D234" s="7">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="15" customHeight="1">
+      <c r="A235" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B235" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C235" s="2">
+        <v>70</v>
+      </c>
+      <c r="D235" s="7">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="15" customHeight="1">
+      <c r="A236" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B236" s="5">
+        <v>450</v>
+      </c>
+      <c r="C236" s="2">
+        <v>50</v>
+      </c>
+      <c r="D236" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="15" customHeight="1">
+      <c r="A237" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="B237" s="5">
+        <v>422</v>
+      </c>
+      <c r="C237" s="2">
+        <v>123</v>
+      </c>
+      <c r="D237" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="15" customHeight="1">
+      <c r="A238" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="B238" s="4">
+        <v>346</v>
+      </c>
+      <c r="C238" s="2">
+        <v>115</v>
+      </c>
+      <c r="D238" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="15" customHeight="1">
+      <c r="A239" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B239" s="4">
         <v>277</v>
       </c>
-      <c r="C234" s="2">
+      <c r="C239" s="2">
         <v>18</v>
       </c>
-      <c r="D234" s="7">
+      <c r="D239" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="15" customHeight="1">
-      <c r="A235" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B235" s="4">
+    <row r="240" spans="1:4" ht="15" customHeight="1">
+      <c r="A240" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B240" s="4">
         <v>149</v>
       </c>
-      <c r="C235" s="2">
+      <c r="C240" s="2">
         <v>16</v>
       </c>
-      <c r="D235" s="7">
+      <c r="D240" s="7">
         <v>3</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" ht="15" customHeight="1">
-      <c r="A236" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B236" s="4">
-        <v>210</v>
-      </c>
-      <c r="C236" s="2">
-        <v>20</v>
-      </c>
-      <c r="D236" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" ht="15" customHeight="1">
-      <c r="A237" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="B237" s="4">
-        <v>260</v>
-      </c>
-      <c r="C237" s="2">
-        <v>8</v>
-      </c>
-      <c r="D237" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" ht="15" customHeight="1">
-      <c r="A238" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="B238" s="4">
-        <v>177</v>
-      </c>
-      <c r="C238" s="2">
-        <v>23</v>
-      </c>
-      <c r="D238" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" ht="15" customHeight="1">
-      <c r="A239" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="B239" s="4">
-        <v>81</v>
-      </c>
-      <c r="C239" s="2">
-        <v>13</v>
-      </c>
-      <c r="D239" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" ht="15" customHeight="1">
-      <c r="A240" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="B240" s="5">
-        <v>782</v>
-      </c>
-      <c r="C240" s="2">
-        <v>110</v>
-      </c>
-      <c r="D240" s="7">
-        <v>21</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15" customHeight="1">
       <c r="A241" s="20" t="s">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="B241" s="4">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C241" s="2">
         <v>20</v>
@@ -5349,1787 +5442,1969 @@
     </row>
     <row r="242" spans="1:4" ht="15" customHeight="1">
       <c r="A242" s="20" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B242" s="4">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="C242" s="2">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D242" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15" customHeight="1">
       <c r="A243" s="20" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B243" s="4">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C243" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D243" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15" customHeight="1">
-      <c r="A244" s="20" t="s">
-        <v>82</v>
+      <c r="A244" s="21" t="s">
+        <v>192</v>
       </c>
       <c r="B244" s="4">
+        <v>81</v>
+      </c>
+      <c r="C244" s="2">
+        <v>13</v>
+      </c>
+      <c r="D244" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="15" customHeight="1">
+      <c r="A245" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B245" s="5">
+        <v>782</v>
+      </c>
+      <c r="C245" s="2">
+        <v>110</v>
+      </c>
+      <c r="D245" s="7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="15" customHeight="1">
+      <c r="A246" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B246" s="4">
+        <v>192</v>
+      </c>
+      <c r="C246" s="2">
+        <v>20</v>
+      </c>
+      <c r="D246" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="15" customHeight="1">
+      <c r="A247" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="B247" s="4">
+        <v>147</v>
+      </c>
+      <c r="C247" s="2">
+        <v>29</v>
+      </c>
+      <c r="D247" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="15" customHeight="1">
+      <c r="A248" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B248" s="4">
+        <v>170</v>
+      </c>
+      <c r="C248" s="2">
+        <v>22</v>
+      </c>
+      <c r="D248" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="15" customHeight="1">
+      <c r="A249" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B249" s="4">
         <v>310</v>
       </c>
-      <c r="C244" s="2">
+      <c r="C249" s="2">
         <v>40</v>
       </c>
-      <c r="D244" s="7">
+      <c r="D249" s="7">
         <v>2</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" ht="15" customHeight="1">
-      <c r="A245" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B245" s="4">
-        <v>238</v>
-      </c>
-      <c r="C245" s="2">
-        <v>27</v>
-      </c>
-      <c r="D245" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" ht="15" customHeight="1">
-      <c r="A246" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B246" s="4">
-        <v>114</v>
-      </c>
-      <c r="C246" s="10"/>
-      <c r="D246" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" ht="15" customHeight="1">
-      <c r="A247" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="B247" s="4">
-        <v>144</v>
-      </c>
-      <c r="C247" s="2">
-        <v>12</v>
-      </c>
-      <c r="D247" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" ht="15" customHeight="1">
-      <c r="A248" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="B248" s="4">
-        <v>126</v>
-      </c>
-      <c r="C248" s="2">
-        <v>15</v>
-      </c>
-      <c r="D248" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" ht="15" customHeight="1">
-      <c r="A249" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="B249" s="5">
-        <v>1340</v>
-      </c>
-      <c r="C249" s="2">
-        <v>126</v>
-      </c>
-      <c r="D249" s="7">
-        <v>9</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15" customHeight="1">
       <c r="A250" s="20" t="s">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="B250" s="4">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="C250" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D250" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15" customHeight="1">
-      <c r="A251" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="B251" s="5">
-        <v>1370</v>
-      </c>
-      <c r="C251" s="2">
+      <c r="A251" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B251" s="4">
         <v>114</v>
       </c>
+      <c r="C251" s="10"/>
       <c r="D251" s="7">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15" customHeight="1">
-      <c r="A252" s="20" t="s">
-        <v>204</v>
+      <c r="A252" s="29" t="s">
+        <v>84</v>
       </c>
       <c r="B252" s="4">
-        <v>278</v>
+        <v>144</v>
       </c>
       <c r="C252" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D252" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="15" customHeight="1">
+      <c r="A253" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="B253" s="4">
+        <v>126</v>
+      </c>
+      <c r="C253" s="2">
+        <v>15</v>
+      </c>
+      <c r="D253" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="15" customHeight="1">
-      <c r="A253" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="B253" s="5">
-        <v>860</v>
-      </c>
-      <c r="C253" s="2">
-        <v>83</v>
-      </c>
-      <c r="D253" s="7">
-        <v>12</v>
-      </c>
-    </row>
     <row r="254" spans="1:4" ht="15" customHeight="1">
-      <c r="A254" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="B254" s="4">
-        <v>221</v>
+      <c r="A254" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="B254" s="5">
+        <v>1340</v>
       </c>
       <c r="C254" s="2">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="D254" s="7">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15" customHeight="1">
       <c r="A255" s="20" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="B255" s="4">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="C255" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D255" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15" customHeight="1">
-      <c r="A256" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B256" s="4">
-        <v>191</v>
+      <c r="A256" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="B256" s="5">
+        <v>1370</v>
       </c>
       <c r="C256" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="D256" s="7">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15" customHeight="1">
       <c r="A257" s="20" t="s">
-        <v>86</v>
+        <v>198</v>
       </c>
       <c r="B257" s="4">
-        <v>173</v>
+        <v>278</v>
       </c>
       <c r="C257" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D257" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15" customHeight="1">
-      <c r="A258" s="20" t="s">
-        <v>87</v>
+      <c r="A258" s="31" t="s">
+        <v>219</v>
       </c>
       <c r="B258" s="5">
-        <v>503</v>
+        <v>860</v>
       </c>
       <c r="C258" s="2">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D258" s="7">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15" customHeight="1">
       <c r="A259" s="20" t="s">
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="B259" s="4">
-        <v>393</v>
+        <v>221</v>
       </c>
       <c r="C259" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D259" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15" customHeight="1">
       <c r="A260" s="20" t="s">
-        <v>89</v>
+        <v>221</v>
       </c>
       <c r="B260" s="4">
-        <v>295</v>
+        <v>229</v>
       </c>
       <c r="C260" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D260" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15" customHeight="1">
       <c r="A261" s="20" t="s">
-        <v>90</v>
+        <v>222</v>
       </c>
       <c r="B261" s="4">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C261" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D261" s="7">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15" customHeight="1">
-      <c r="A262" s="15" t="s">
-        <v>4</v>
+      <c r="A262" s="20" t="s">
+        <v>85</v>
       </c>
       <c r="B262" s="4">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="C262" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D262" s="7">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15" customHeight="1">
       <c r="A263" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B263" s="4">
-        <v>158</v>
+        <v>86</v>
+      </c>
+      <c r="B263" s="5">
+        <v>503</v>
       </c>
       <c r="C263" s="2">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D263" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15" customHeight="1">
       <c r="A264" s="20" t="s">
-        <v>205</v>
+        <v>87</v>
       </c>
       <c r="B264" s="4">
-        <v>240</v>
+        <v>393</v>
       </c>
       <c r="C264" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D264" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15" customHeight="1">
-      <c r="A265" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="B265" s="5">
-        <v>850</v>
+      <c r="A265" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B265" s="4">
+        <v>295</v>
       </c>
       <c r="C265" s="2">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="D265" s="7">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15" customHeight="1">
-      <c r="A266" s="33" t="s">
-        <v>349</v>
+      <c r="A266" s="20" t="s">
+        <v>89</v>
       </c>
       <c r="B266" s="4">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="C266" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D266" s="7">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15" customHeight="1">
-      <c r="A267" s="33" t="s">
-        <v>123</v>
+      <c r="A267" s="15" t="s">
+        <v>4</v>
       </c>
       <c r="B267" s="4">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="C267" s="2">
+        <v>21</v>
+      </c>
+      <c r="D267" s="7">
         <v>20</v>
       </c>
-      <c r="D267" s="7">
-        <v>1</v>
-      </c>
     </row>
     <row r="268" spans="1:4" ht="15" customHeight="1">
-      <c r="A268" s="33" t="s">
-        <v>206</v>
+      <c r="A268" s="20" t="s">
+        <v>90</v>
       </c>
       <c r="B268" s="4">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C268" s="2">
         <v>11</v>
       </c>
       <c r="D268" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="15" customHeight="1">
+      <c r="A269" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="B269" s="4">
+        <v>240</v>
+      </c>
+      <c r="C269" s="2">
+        <v>32</v>
+      </c>
+      <c r="D269" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="15" customHeight="1">
+      <c r="A270" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B270" s="5">
+        <v>850</v>
+      </c>
+      <c r="C270" s="2">
+        <v>108</v>
+      </c>
+      <c r="D270" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="15" customHeight="1">
+      <c r="A271" s="42" t="s">
+        <v>336</v>
+      </c>
+      <c r="B271" s="4">
+        <v>140</v>
+      </c>
+      <c r="C271" s="2">
+        <v>10</v>
+      </c>
+      <c r="D271" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="15" customHeight="1">
+      <c r="A272" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="B272" s="4">
+        <v>124</v>
+      </c>
+      <c r="C272" s="2">
+        <v>20</v>
+      </c>
+      <c r="D272" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="15" customHeight="1">
+      <c r="A273" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="B273" s="4">
+        <v>132</v>
+      </c>
+      <c r="C273" s="2">
+        <v>11</v>
+      </c>
+      <c r="D273" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="15" customHeight="1">
-      <c r="A269" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="B269" s="4">
+    <row r="274" spans="1:4" ht="15" customHeight="1">
+      <c r="A274" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B274" s="4">
         <v>105</v>
       </c>
-      <c r="C269" s="2">
+      <c r="C274" s="2">
         <v>14</v>
       </c>
-      <c r="D269" s="7">
+      <c r="D274" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="15" customHeight="1">
-      <c r="A270" s="33" t="s">
+    <row r="275" spans="1:4" ht="15" customHeight="1">
+      <c r="A275" s="43" t="s">
+        <v>367</v>
+      </c>
+      <c r="B275" s="4">
+        <v>100</v>
+      </c>
+      <c r="C275" s="2">
+        <v>12</v>
+      </c>
+      <c r="D275" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="15" customHeight="1">
+      <c r="A276" s="42" t="s">
+        <v>368</v>
+      </c>
+      <c r="B276" s="4">
+        <v>200</v>
+      </c>
+      <c r="C276" s="2">
+        <v>25</v>
+      </c>
+      <c r="D276" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="15" customHeight="1">
+      <c r="A277" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="B277" s="4">
+        <v>33</v>
+      </c>
+      <c r="C277" s="2">
+        <v>3</v>
+      </c>
+      <c r="D277" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="15" customHeight="1">
+      <c r="A278" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B278" s="4">
+        <v>78</v>
+      </c>
+      <c r="C278" s="2">
+        <v>11</v>
+      </c>
+      <c r="D278" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="15" customHeight="1">
+      <c r="A279" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="B270" s="4">
-        <v>116</v>
-      </c>
-      <c r="C270" s="2">
-        <v>7</v>
-      </c>
-      <c r="D270" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" ht="15" customHeight="1">
-      <c r="A271" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="B271" s="4">
-        <v>33</v>
-      </c>
-      <c r="C271" s="2">
+      <c r="B279" s="4">
+        <v>362</v>
+      </c>
+      <c r="C279" s="2">
+        <v>23</v>
+      </c>
+      <c r="D279" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="15" customHeight="1">
+      <c r="A280" s="42" t="s">
+        <v>376</v>
+      </c>
+      <c r="B280" s="4">
+        <v>50</v>
+      </c>
+      <c r="C280" s="2">
+        <v>5</v>
+      </c>
+      <c r="D280" s="7">
         <v>3</v>
       </c>
-      <c r="D271" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" ht="15" customHeight="1">
-      <c r="A272" s="33" t="s">
+    </row>
+    <row r="281" spans="1:4" ht="15" customHeight="1">
+      <c r="A281" s="42" t="s">
+        <v>377</v>
+      </c>
+      <c r="B281" s="4">
+        <v>80</v>
+      </c>
+      <c r="C281" s="2">
+        <v>10</v>
+      </c>
+      <c r="D281" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="15" customHeight="1">
+      <c r="A282" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="B282" s="4">
+        <v>100</v>
+      </c>
+      <c r="C282" s="2">
+        <v>10</v>
+      </c>
+      <c r="D282" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="15" customHeight="1">
+      <c r="A283" s="42" t="s">
+        <v>378</v>
+      </c>
+      <c r="B283" s="4">
+        <v>60</v>
+      </c>
+      <c r="C283" s="2">
+        <v>8</v>
+      </c>
+      <c r="D283" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="15" customHeight="1">
+      <c r="A284" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="B284" s="4">
+        <v>130</v>
+      </c>
+      <c r="C284" s="2">
+        <v>17</v>
+      </c>
+      <c r="D284" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="15" customHeight="1">
+      <c r="A285" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="B285" s="4">
         <v>94</v>
       </c>
-      <c r="B272" s="4">
-        <v>78</v>
-      </c>
-      <c r="C272" s="2">
-        <v>11</v>
-      </c>
-      <c r="D272" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" ht="15" customHeight="1">
-      <c r="A273" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B273" s="4">
-        <v>362</v>
-      </c>
-      <c r="C273" s="2">
-        <v>23</v>
-      </c>
-      <c r="D273" s="7">
+      <c r="C285" s="2">
+        <v>5</v>
+      </c>
+      <c r="D285" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="15" customHeight="1">
-      <c r="A274" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="B274" s="4">
-        <v>130</v>
-      </c>
-      <c r="C274" s="2">
-        <v>17</v>
-      </c>
-      <c r="D274" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" ht="15" customHeight="1">
-      <c r="A275" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="B275" s="4">
-        <v>94</v>
-      </c>
-      <c r="C275" s="2">
-        <v>5</v>
-      </c>
-      <c r="D275" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" ht="15" customHeight="1">
-      <c r="A276" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="B276" s="4">
+    <row r="286" spans="1:4" ht="15" customHeight="1">
+      <c r="A286" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="B286" s="4">
         <v>150</v>
-      </c>
-      <c r="C276" s="2">
-        <v>10</v>
-      </c>
-      <c r="D276" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" ht="15" customHeight="1">
-      <c r="A277" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="B277" s="4">
-        <v>90</v>
-      </c>
-      <c r="C277" s="2">
-        <v>5</v>
-      </c>
-      <c r="D277" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" ht="15" customHeight="1">
-      <c r="A278" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="B278" s="4">
-        <v>260</v>
-      </c>
-      <c r="C278" s="2">
-        <v>13</v>
-      </c>
-      <c r="D278" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" ht="15" customHeight="1">
-      <c r="A279" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="B279" s="4">
-        <v>80</v>
-      </c>
-      <c r="C279" s="2">
-        <v>8</v>
-      </c>
-      <c r="D279" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" ht="15" customHeight="1">
-      <c r="A280" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="B280" s="4">
-        <v>125</v>
-      </c>
-      <c r="C280" s="2">
-        <v>15</v>
-      </c>
-      <c r="D280" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" ht="15" customHeight="1">
-      <c r="A281" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B281" s="4">
-        <v>407</v>
-      </c>
-      <c r="C281" s="2">
-        <v>152</v>
-      </c>
-      <c r="D281" s="7"/>
-    </row>
-    <row r="282" spans="1:4" ht="15" customHeight="1">
-      <c r="A282" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="B282" s="4">
-        <v>45</v>
-      </c>
-      <c r="C282" s="2">
-        <v>7</v>
-      </c>
-      <c r="D282" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" ht="15" customHeight="1">
-      <c r="A283" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B283" s="4">
-        <v>80</v>
-      </c>
-      <c r="C283" s="2">
-        <v>16</v>
-      </c>
-      <c r="D283" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" ht="15" customHeight="1">
-      <c r="A284" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="B284" s="4">
-        <v>65</v>
-      </c>
-      <c r="C284" s="2">
-        <v>15</v>
-      </c>
-      <c r="D284" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" ht="15" customHeight="1">
-      <c r="A285" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B285" s="4">
-        <v>104</v>
-      </c>
-      <c r="C285" s="2">
-        <v>11</v>
-      </c>
-      <c r="D285" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" ht="15" customHeight="1">
-      <c r="A286" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="B286" s="4">
-        <v>130</v>
       </c>
       <c r="C286" s="2">
         <v>10</v>
       </c>
       <c r="D286" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15" customHeight="1">
-      <c r="A287" s="21" t="s">
-        <v>236</v>
+      <c r="A287" s="33" t="s">
+        <v>224</v>
       </c>
       <c r="B287" s="4">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="C287" s="2">
+        <v>5</v>
+      </c>
+      <c r="D287" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="15" customHeight="1">
+      <c r="A288" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B288" s="4">
+        <v>260</v>
+      </c>
+      <c r="C288" s="2">
         <v>13</v>
       </c>
-      <c r="D287" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" ht="15" customHeight="1">
-      <c r="A288" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B288" s="5">
-        <v>705</v>
-      </c>
-      <c r="C288" s="2">
-        <v>481</v>
-      </c>
       <c r="D288" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="15" customHeight="1">
+      <c r="A289" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="B289" s="4">
+        <v>80</v>
+      </c>
+      <c r="C289" s="2">
+        <v>8</v>
+      </c>
+      <c r="D289" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="15" customHeight="1">
+      <c r="A290" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="B290" s="4">
+        <v>125</v>
+      </c>
+      <c r="C290" s="2">
+        <v>15</v>
+      </c>
+      <c r="D290" s="7">
         <v>4</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" ht="15" customHeight="1">
-      <c r="A289" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B289" s="5">
-        <v>592</v>
-      </c>
-      <c r="C289" s="2">
-        <v>107</v>
-      </c>
-      <c r="D289" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" ht="15" customHeight="1">
-      <c r="A290" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="B290" s="5">
-        <v>500</v>
-      </c>
-      <c r="C290" s="2">
-        <v>80</v>
-      </c>
-      <c r="D290" s="7">
-        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15" customHeight="1">
       <c r="A291" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="B291" s="5">
-        <v>777</v>
+        <v>131</v>
+      </c>
+      <c r="B291" s="4">
+        <v>407</v>
       </c>
       <c r="C291" s="2">
-        <v>409</v>
-      </c>
-      <c r="D291" s="7">
-        <v>6</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="D291" s="7"/>
     </row>
     <row r="292" spans="1:4" ht="15" customHeight="1">
-      <c r="A292" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="B292" s="5">
-        <v>786</v>
+      <c r="A292" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B292" s="4">
+        <v>45</v>
       </c>
       <c r="C292" s="2">
-        <v>410</v>
+        <v>7</v>
       </c>
       <c r="D292" s="7">
-        <v>-420</v>
+        <v>50</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15" customHeight="1">
-      <c r="A293" s="15" t="s">
-        <v>96</v>
+      <c r="A293" s="21" t="s">
+        <v>5</v>
       </c>
       <c r="B293" s="4">
-        <v>379</v>
+        <v>80</v>
       </c>
       <c r="C293" s="2">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="D293" s="7">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15" customHeight="1">
-      <c r="A294" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="B294" s="5">
-        <v>704</v>
+      <c r="A294" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="B294" s="4">
+        <v>65</v>
       </c>
       <c r="C294" s="2">
-        <v>333</v>
+        <v>15</v>
       </c>
       <c r="D294" s="7">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15" customHeight="1">
-      <c r="A295" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B295" s="5">
-        <v>544</v>
+      <c r="A295" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="B295" s="4">
+        <v>104</v>
       </c>
       <c r="C295" s="2">
-        <v>409</v>
+        <v>11</v>
       </c>
       <c r="D295" s="7">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15" customHeight="1">
-      <c r="A296" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B296" s="5">
-        <v>818</v>
+      <c r="A296" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B296" s="4">
+        <v>130</v>
       </c>
       <c r="C296" s="2">
-        <v>1144</v>
+        <v>10</v>
       </c>
       <c r="D296" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="15" customHeight="1">
+      <c r="A297" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B297" s="4">
+        <v>44</v>
+      </c>
+      <c r="C297" s="2">
+        <v>13</v>
+      </c>
+      <c r="D297" s="7">
         <v>18</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" ht="15" customHeight="1">
-      <c r="A297" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B297" s="5">
-        <v>705</v>
-      </c>
-      <c r="C297" s="2">
-        <v>854</v>
-      </c>
-      <c r="D297" s="7">
-        <v>21</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15" customHeight="1">
       <c r="A298" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B298" s="4">
-        <v>458</v>
+        <v>126</v>
+      </c>
+      <c r="B298" s="5">
+        <v>705</v>
       </c>
       <c r="C298" s="2">
-        <v>607</v>
+        <v>481</v>
       </c>
       <c r="D298" s="7">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15" customHeight="1">
       <c r="A299" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B299" s="5">
+        <v>592</v>
+      </c>
+      <c r="C299" s="2">
+        <v>107</v>
+      </c>
+      <c r="D299" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="15" customHeight="1">
+      <c r="A300" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="B300" s="5">
+        <v>500</v>
+      </c>
+      <c r="C300" s="2">
+        <v>80</v>
+      </c>
+      <c r="D300" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="15" customHeight="1">
+      <c r="A301" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="B301" s="5">
+        <v>777</v>
+      </c>
+      <c r="C301" s="2">
+        <v>409</v>
+      </c>
+      <c r="D301" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="15" customHeight="1">
+      <c r="A302" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B302" s="5">
+        <v>786</v>
+      </c>
+      <c r="C302" s="2">
+        <v>410</v>
+      </c>
+      <c r="D302" s="7">
+        <v>-420</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="15" customHeight="1">
+      <c r="A303" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B303" s="4">
+        <v>379</v>
+      </c>
+      <c r="C303" s="2">
+        <v>94</v>
+      </c>
+      <c r="D303" s="7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="15" customHeight="1">
+      <c r="A304" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B304" s="5">
+        <v>704</v>
+      </c>
+      <c r="C304" s="2">
+        <v>333</v>
+      </c>
+      <c r="D304" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" ht="15" customHeight="1">
+      <c r="A305" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B305" s="5">
+        <v>544</v>
+      </c>
+      <c r="C305" s="2">
+        <v>409</v>
+      </c>
+      <c r="D305" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="15" customHeight="1">
+      <c r="A306" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B306" s="5">
+        <v>818</v>
+      </c>
+      <c r="C306" s="2">
+        <v>1144</v>
+      </c>
+      <c r="D306" s="7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="15" customHeight="1">
+      <c r="A307" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B307" s="5">
+        <v>705</v>
+      </c>
+      <c r="C307" s="2">
+        <v>854</v>
+      </c>
+      <c r="D307" s="7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="15" customHeight="1">
+      <c r="A308" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B308" s="4">
+        <v>458</v>
+      </c>
+      <c r="C308" s="2">
+        <v>607</v>
+      </c>
+      <c r="D308" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" ht="15" customHeight="1">
+      <c r="A309" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B309" s="5">
+        <v>690</v>
+      </c>
+      <c r="C309" s="2">
+        <v>100</v>
+      </c>
+      <c r="D309" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" ht="15" customHeight="1">
+      <c r="A310" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="B310" s="4">
+        <v>100</v>
+      </c>
+      <c r="C310" s="2">
+        <v>100</v>
+      </c>
+      <c r="D310" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" ht="15" customHeight="1">
+      <c r="A311" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B311" s="4">
+        <v>250</v>
+      </c>
+      <c r="C311" s="2">
+        <v>150</v>
+      </c>
+      <c r="D311" s="7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" ht="15" customHeight="1">
+      <c r="A312" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B312" s="4">
+        <v>100</v>
+      </c>
+      <c r="C312" s="2">
+        <v>145</v>
+      </c>
+      <c r="D312" s="7">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="15" customHeight="1">
+      <c r="A313" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="B313" s="4">
+        <v>130</v>
+      </c>
+      <c r="C313" s="2">
+        <v>130</v>
+      </c>
+      <c r="D313" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" ht="15" customHeight="1">
+      <c r="A314" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B314" s="4">
+        <v>50</v>
+      </c>
+      <c r="C314" s="2">
+        <v>20</v>
+      </c>
+      <c r="D314" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" ht="15" customHeight="1">
+      <c r="A315" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="B315" s="4">
+        <v>0</v>
+      </c>
+      <c r="C315" s="2">
+        <v>0</v>
+      </c>
+      <c r="D315" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" ht="15" customHeight="1">
+      <c r="A316" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B299" s="5">
-        <v>690</v>
-      </c>
-      <c r="C299" s="2">
+      <c r="B316" s="4">
+        <v>3</v>
+      </c>
+      <c r="C316" s="2">
+        <v>7</v>
+      </c>
+      <c r="D316" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" ht="15" customHeight="1">
+      <c r="A317" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B317" s="4">
+        <v>50</v>
+      </c>
+      <c r="C317" s="2">
+        <v>20</v>
+      </c>
+      <c r="D317" s="7"/>
+    </row>
+    <row r="318" spans="1:4" ht="15" customHeight="1">
+      <c r="A318" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B318" s="5">
+        <v>400</v>
+      </c>
+      <c r="C318" s="2">
+        <v>200</v>
+      </c>
+      <c r="D318" s="7">
         <v>100</v>
       </c>
-      <c r="D299" s="7">
+    </row>
+    <row r="319" spans="1:4" ht="15" customHeight="1">
+      <c r="A319" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B319" s="4">
+        <v>151</v>
+      </c>
+      <c r="C319" s="2">
+        <v>117</v>
+      </c>
+      <c r="D319" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" ht="15" customHeight="1">
+      <c r="A320" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="B320" s="5">
+        <v>452</v>
+      </c>
+      <c r="C320" s="2">
+        <v>264</v>
+      </c>
+      <c r="D320" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" ht="15" customHeight="1">
+      <c r="A321" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B321" s="4">
+        <v>160</v>
+      </c>
+      <c r="C321" s="2">
+        <v>189</v>
+      </c>
+      <c r="D321" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="15" customHeight="1">
-      <c r="A300" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="B300" s="4">
-        <v>100</v>
-      </c>
-      <c r="C300" s="2">
-        <v>100</v>
-      </c>
-      <c r="D300" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" ht="15" customHeight="1">
-      <c r="A301" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="B301" s="4">
-        <v>250</v>
-      </c>
-      <c r="C301" s="2">
-        <v>150</v>
-      </c>
-      <c r="D301" s="7">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" ht="15" customHeight="1">
-      <c r="A302" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B302" s="4">
-        <v>100</v>
-      </c>
-      <c r="C302" s="2">
-        <v>145</v>
-      </c>
-      <c r="D302" s="7">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" ht="15" customHeight="1">
-      <c r="A303" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="B303" s="4">
-        <v>130</v>
-      </c>
-      <c r="C303" s="2">
-        <v>130</v>
-      </c>
-      <c r="D303" s="7">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" ht="15" customHeight="1">
-      <c r="A304" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B304" s="4">
-        <v>50</v>
-      </c>
-      <c r="C304" s="2">
-        <v>20</v>
-      </c>
-      <c r="D304" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" ht="15" customHeight="1">
-      <c r="A305" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="B305" s="4">
-        <v>0</v>
-      </c>
-      <c r="C305" s="2">
-        <v>0</v>
-      </c>
-      <c r="D305" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" ht="15" customHeight="1">
-      <c r="A306" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B306" s="4">
-        <v>3</v>
-      </c>
-      <c r="C306" s="2">
-        <v>7</v>
-      </c>
-      <c r="D306" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" ht="15" customHeight="1">
-      <c r="A307" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="B307" s="4">
-        <v>50</v>
-      </c>
-      <c r="C307" s="2">
-        <v>20</v>
-      </c>
-      <c r="D307" s="7"/>
-    </row>
-    <row r="308" spans="1:4" ht="15" customHeight="1">
-      <c r="A308" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="B308" s="5">
-        <v>400</v>
-      </c>
-      <c r="C308" s="2">
-        <v>200</v>
-      </c>
-      <c r="D308" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" ht="15" customHeight="1">
-      <c r="A309" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="B309" s="4">
-        <v>151</v>
-      </c>
-      <c r="C309" s="2">
-        <v>117</v>
-      </c>
-      <c r="D309" s="7">
+    <row r="322" spans="1:4" ht="15" customHeight="1">
+      <c r="A322" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B322" s="4">
         <v>90</v>
       </c>
-    </row>
-    <row r="310" spans="1:4" ht="15" customHeight="1">
-      <c r="A310" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="B310" s="5">
-        <v>452</v>
-      </c>
-      <c r="C310" s="2">
-        <v>264</v>
-      </c>
-      <c r="D310" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" ht="15" customHeight="1">
-      <c r="A311" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B311" s="4">
-        <v>160</v>
-      </c>
-      <c r="C311" s="2">
-        <v>189</v>
-      </c>
-      <c r="D311" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" ht="15" customHeight="1">
-      <c r="A312" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B312" s="4">
-        <v>90</v>
-      </c>
-      <c r="C312" s="2">
+      <c r="C322" s="2">
         <v>115</v>
       </c>
-      <c r="D312" s="7">
+      <c r="D322" s="7">
         <v>4</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" ht="15" customHeight="1">
-      <c r="A313" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="B313" s="4">
-        <v>120</v>
-      </c>
-      <c r="C313" s="2">
-        <v>256</v>
-      </c>
-      <c r="D313" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" ht="15" customHeight="1">
-      <c r="A314" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="B314" s="4">
-        <v>139</v>
-      </c>
-      <c r="C314" s="2">
-        <v>59</v>
-      </c>
-      <c r="D314" s="7">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" ht="15" customHeight="1">
-      <c r="A315" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="B315" s="4">
-        <v>157</v>
-      </c>
-      <c r="C315" s="2">
-        <v>73</v>
-      </c>
-      <c r="D315" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" ht="15" customHeight="1">
-      <c r="A316" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B316" s="4">
-        <v>274</v>
-      </c>
-      <c r="C316" s="2">
-        <v>300</v>
-      </c>
-      <c r="D316" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" ht="15" customHeight="1">
-      <c r="A317" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="B317" s="4">
-        <v>225</v>
-      </c>
-      <c r="C317" s="2">
-        <v>250</v>
-      </c>
-      <c r="D317" s="7">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" ht="15" customHeight="1">
-      <c r="A318" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B318" s="4">
-        <v>249</v>
-      </c>
-      <c r="C318" s="2">
-        <v>103</v>
-      </c>
-      <c r="D318" s="7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" ht="15" customHeight="1">
-      <c r="A319" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="B319" s="5">
-        <v>502</v>
-      </c>
-      <c r="C319" s="2">
-        <v>344</v>
-      </c>
-      <c r="D319" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" ht="15" customHeight="1">
-      <c r="A320" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B320" s="4">
-        <v>112</v>
-      </c>
-      <c r="C320" s="2">
-        <v>75</v>
-      </c>
-      <c r="D320" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" ht="15" customHeight="1">
-      <c r="A321" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="B321" s="4">
-        <v>108</v>
-      </c>
-      <c r="C321" s="2">
-        <v>74</v>
-      </c>
-      <c r="D321" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" ht="15" customHeight="1">
-      <c r="A322" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="B322" s="4">
-        <v>126</v>
-      </c>
-      <c r="C322" s="2">
-        <v>113</v>
-      </c>
-      <c r="D322" s="7">
-        <v>3</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15" customHeight="1">
       <c r="A323" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B323" s="5">
-        <v>1390</v>
+        <v>231</v>
+      </c>
+      <c r="B323" s="4">
+        <v>120</v>
       </c>
       <c r="C323" s="2">
-        <v>1280</v>
+        <v>256</v>
       </c>
       <c r="D323" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15" customHeight="1">
-      <c r="A324" s="15" t="s">
-        <v>242</v>
+      <c r="A324" s="20" t="s">
+        <v>105</v>
       </c>
       <c r="B324" s="4">
-        <v>380</v>
+        <v>139</v>
       </c>
       <c r="C324" s="2">
-        <v>350</v>
+        <v>59</v>
       </c>
       <c r="D324" s="7">
-        <v>3</v>
+        <v>910</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15" customHeight="1">
-      <c r="A325" s="15" t="s">
-        <v>142</v>
+      <c r="A325" s="20" t="s">
+        <v>140</v>
       </c>
       <c r="B325" s="4">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C325" s="2">
-        <v>325</v>
+        <v>73</v>
       </c>
       <c r="D325" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15" customHeight="1">
-      <c r="A326" s="20" t="s">
-        <v>143</v>
+      <c r="A326" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="B326" s="4">
-        <v>103</v>
+        <v>274</v>
       </c>
       <c r="C326" s="2">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="D326" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15" customHeight="1">
-      <c r="A327" s="35" t="s">
-        <v>144</v>
+      <c r="A327" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="B327" s="4">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="C327" s="2">
-        <v>36</v>
+        <v>250</v>
       </c>
       <c r="D327" s="7">
-        <v>-448</v>
+        <v>600</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15" customHeight="1">
       <c r="A328" s="15" t="s">
-        <v>188</v>
+        <v>117</v>
       </c>
       <c r="B328" s="4">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="C328" s="2">
-        <v>250</v>
+        <v>103</v>
       </c>
       <c r="D328" s="7">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15" customHeight="1">
-      <c r="A329" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="B329" s="4">
-        <v>355</v>
+      <c r="A329" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B329" s="5">
+        <v>502</v>
       </c>
       <c r="C329" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D329" s="7">
         <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15" customHeight="1">
-      <c r="A330" s="36" t="s">
-        <v>141</v>
+      <c r="A330" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="B330" s="4">
+        <v>112</v>
+      </c>
+      <c r="C330" s="2">
+        <v>75</v>
+      </c>
+      <c r="D330" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" ht="15" customHeight="1">
+      <c r="A331" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B331" s="4">
+        <v>108</v>
+      </c>
+      <c r="C331" s="2">
+        <v>74</v>
+      </c>
+      <c r="D331" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" ht="15" customHeight="1">
+      <c r="A332" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="B332" s="4">
+        <v>126</v>
+      </c>
+      <c r="C332" s="2">
+        <v>113</v>
+      </c>
+      <c r="D332" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" ht="15" customHeight="1">
+      <c r="A333" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B333" s="5">
+        <v>1390</v>
+      </c>
+      <c r="C333" s="2">
+        <v>1280</v>
+      </c>
+      <c r="D333" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="15" customHeight="1">
+      <c r="A334" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B334" s="4">
+        <v>380</v>
+      </c>
+      <c r="C334" s="2">
+        <v>350</v>
+      </c>
+      <c r="D334" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="15" customHeight="1">
+      <c r="A335" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B335" s="4">
+        <v>130</v>
+      </c>
+      <c r="C335" s="2">
+        <v>325</v>
+      </c>
+      <c r="D335" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" ht="15" customHeight="1">
+      <c r="A336" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B336" s="4">
+        <v>103</v>
+      </c>
+      <c r="C336" s="2">
+        <v>120</v>
+      </c>
+      <c r="D336" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" ht="15" customHeight="1">
+      <c r="A337" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="B337" s="4">
+        <v>31</v>
+      </c>
+      <c r="C337" s="2">
+        <v>36</v>
+      </c>
+      <c r="D337" s="7">
+        <v>-448</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" ht="15" customHeight="1">
+      <c r="A338" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B338" s="4">
+        <v>260</v>
+      </c>
+      <c r="C338" s="2">
+        <v>250</v>
+      </c>
+      <c r="D338" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" ht="15" customHeight="1">
+      <c r="A339" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="B339" s="4">
+        <v>355</v>
+      </c>
+      <c r="C339" s="2">
+        <v>342</v>
+      </c>
+      <c r="D339" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" ht="15" customHeight="1">
+      <c r="A340" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="B340" s="4">
         <v>335</v>
       </c>
-      <c r="C330" s="2">
+      <c r="C340" s="2">
         <v>391</v>
       </c>
-      <c r="D330" s="7">
+      <c r="D340" s="7">
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="15" customHeight="1">
-      <c r="A331" s="36" t="s">
-        <v>243</v>
-      </c>
-      <c r="B331" s="4">
+    <row r="341" spans="1:4" ht="15" customHeight="1">
+      <c r="A341" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="B341" s="4">
         <v>300</v>
       </c>
-      <c r="C331" s="2">
+      <c r="C341" s="2">
         <v>98</v>
       </c>
-      <c r="D331" s="7">
+      <c r="D341" s="7">
         <v>390</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="15" customHeight="1">
-      <c r="A332" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="B332" s="4">
+    <row r="342" spans="1:4" ht="15" customHeight="1">
+      <c r="A342" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="B342" s="4">
         <v>348</v>
       </c>
-      <c r="C332" s="2">
+      <c r="C342" s="2">
         <v>298</v>
       </c>
-      <c r="D332" s="7">
+      <c r="D342" s="7">
         <v>564</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="15" customHeight="1">
-      <c r="A333" s="16" t="s">
+    <row r="343" spans="1:4" ht="15" customHeight="1">
+      <c r="A343" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B343" s="4">
+        <v>219</v>
+      </c>
+      <c r="C343" s="2">
+        <v>140</v>
+      </c>
+      <c r="D343" s="7">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" ht="15" customHeight="1">
+      <c r="A344" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B344" s="4">
+        <v>32</v>
+      </c>
+      <c r="C344" s="2">
+        <v>15</v>
+      </c>
+      <c r="D344" s="7">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="15" customHeight="1">
+      <c r="A345" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B333" s="4">
-        <v>219</v>
-      </c>
-      <c r="C333" s="2">
-        <v>140</v>
-      </c>
-      <c r="D333" s="7">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" ht="15" customHeight="1">
-      <c r="A334" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="B334" s="4">
-        <v>32</v>
-      </c>
-      <c r="C334" s="2">
-        <v>15</v>
-      </c>
-      <c r="D334" s="7">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" ht="15" customHeight="1">
-      <c r="A335" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="B335" s="4">
+      <c r="B345" s="4">
         <v>70</v>
       </c>
-      <c r="C335" s="2">
+      <c r="C345" s="2">
         <v>58</v>
       </c>
-      <c r="D335" s="7">
+      <c r="D345" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="15" customHeight="1">
-      <c r="A336" s="25" t="s">
-        <v>366</v>
-      </c>
-      <c r="B336" s="4">
+    <row r="346" spans="1:4" ht="15" customHeight="1">
+      <c r="A346" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="B346" s="4">
         <v>70</v>
       </c>
-      <c r="C336" s="2">
+      <c r="C346" s="2">
         <v>58</v>
       </c>
-      <c r="D336" s="7">
+      <c r="D346" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="15" customHeight="1">
-      <c r="A337" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="B337" s="4">
+    <row r="347" spans="1:4" ht="15" customHeight="1">
+      <c r="A347" s="39" t="s">
+        <v>354</v>
+      </c>
+      <c r="B347" s="4">
         <v>160</v>
       </c>
-      <c r="C337" s="2">
+      <c r="C347" s="2">
         <v>150</v>
       </c>
-      <c r="D337" s="7">
+      <c r="D347" s="7">
         <v>400</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="15" customHeight="1">
-      <c r="A338" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="B338" s="4">
+    <row r="348" spans="1:4" ht="15" customHeight="1">
+      <c r="A348" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="B348" s="4">
         <v>120</v>
       </c>
-      <c r="C338" s="2">
+      <c r="C348" s="2">
         <v>50</v>
       </c>
-      <c r="D338" s="7">
+      <c r="D348" s="7">
         <v>150</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="15" customHeight="1">
-      <c r="A339" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="B339" s="4">
+    <row r="349" spans="1:4" ht="15" customHeight="1">
+      <c r="A349" s="39" t="s">
+        <v>355</v>
+      </c>
+      <c r="B349" s="4">
         <v>220</v>
       </c>
-      <c r="C339" s="2">
+      <c r="C349" s="2">
         <v>170</v>
       </c>
-      <c r="D339" s="7">
+      <c r="D349" s="7">
         <v>450</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="15" customHeight="1">
-      <c r="A340" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="B340" s="4">
+    <row r="350" spans="1:4" ht="15" customHeight="1">
+      <c r="A350" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="B350" s="4">
         <v>100</v>
       </c>
-      <c r="C340" s="2">
+      <c r="C350" s="2">
         <v>40</v>
       </c>
-      <c r="D340" s="7">
+      <c r="D350" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="15" customHeight="1">
-      <c r="A341" s="39" t="s">
-        <v>371</v>
-      </c>
-      <c r="B341" s="4">
+    <row r="351" spans="1:4" ht="15" customHeight="1">
+      <c r="A351" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="B351" s="4">
         <v>200</v>
       </c>
-      <c r="C341" s="2">
+      <c r="C351" s="2">
         <v>150</v>
       </c>
-      <c r="D341" s="7">
+      <c r="D351" s="7">
         <v>350</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="15" customHeight="1">
-      <c r="A342" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="B342" s="4">
+    <row r="352" spans="1:4" ht="15" customHeight="1">
+      <c r="A352" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="B352" s="4">
         <v>150</v>
       </c>
-      <c r="C342" s="2">
+      <c r="C352" s="2">
         <v>110</v>
       </c>
-      <c r="D342" s="7">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" ht="15" customHeight="1">
-      <c r="A343" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="B343" s="4">
+      <c r="D352" s="7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="15" customHeight="1">
+      <c r="A353" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="B353" s="4">
         <v>100</v>
       </c>
-      <c r="C343" s="2">
+      <c r="C353" s="2">
         <v>95</v>
       </c>
-      <c r="D343" s="7">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" ht="15" customHeight="1">
-      <c r="A344" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="B344" s="4">
+      <c r="D353" s="7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" ht="15" customHeight="1">
+      <c r="A354" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="B354" s="4">
         <v>100</v>
       </c>
-      <c r="C344" s="2">
+      <c r="C354" s="2">
         <v>95</v>
       </c>
-      <c r="D344" s="7">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" ht="15" customHeight="1">
-      <c r="A345" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="B345" s="4">
+      <c r="D354" s="7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" ht="15" customHeight="1">
+      <c r="A355" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="B355" s="4">
         <v>145</v>
       </c>
-      <c r="C345" s="2">
+      <c r="C355" s="2">
         <v>135</v>
       </c>
-      <c r="D345" s="7">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" ht="15" customHeight="1">
-      <c r="A346" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="B346" s="4">
-        <v>338</v>
-      </c>
-      <c r="C346" s="2">
-        <v>347</v>
-      </c>
-      <c r="D346" s="7">
-        <v>-370</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" ht="15" customHeight="1">
-      <c r="A347" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="B347" s="4">
-        <v>209</v>
-      </c>
-      <c r="C347" s="2">
-        <v>244</v>
-      </c>
-      <c r="D347" s="7">
-        <v>-370</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" ht="15" customHeight="1">
-      <c r="A348" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="B348" s="4">
-        <v>131</v>
-      </c>
-      <c r="C348" s="2">
-        <v>120</v>
-      </c>
-      <c r="D348" s="7">
-        <v>-635</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" ht="15" customHeight="1">
-      <c r="A349" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="B349" s="4">
-        <v>1</v>
-      </c>
-      <c r="C349" s="2">
-        <v>1</v>
-      </c>
-      <c r="D349" s="7"/>
-    </row>
-    <row r="350" spans="1:4" ht="15" customHeight="1">
-      <c r="A350" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="B350" s="4">
-        <v>1</v>
-      </c>
-      <c r="C350" s="2">
-        <v>1</v>
-      </c>
-      <c r="D350" s="7"/>
-    </row>
-    <row r="351" spans="1:4" ht="15" customHeight="1">
-      <c r="A351" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="B351" s="4">
-        <v>1</v>
-      </c>
-      <c r="C351" s="2">
-        <v>15</v>
-      </c>
-      <c r="D351" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" ht="15" customHeight="1">
-      <c r="A352" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B352" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="C352" s="2">
-        <v>1</v>
-      </c>
-      <c r="D352" s="7"/>
-    </row>
-    <row r="353" spans="1:4" ht="15" customHeight="1">
-      <c r="A353" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B353" s="4">
-        <v>7.5</v>
-      </c>
-      <c r="C353" s="2">
-        <v>1</v>
-      </c>
-      <c r="D353" s="7"/>
-    </row>
-    <row r="354" spans="1:4" ht="15" customHeight="1">
-      <c r="A354" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="B354" s="4">
-        <v>9</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D354" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" ht="15" customHeight="1">
-      <c r="A355" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="B355" s="4">
-        <v>37</v>
-      </c>
-      <c r="C355" s="2">
-        <v>1</v>
-      </c>
       <c r="D355" s="7">
-        <v>3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15" customHeight="1">
       <c r="A356" s="20" t="s">
-        <v>246</v>
+        <v>347</v>
       </c>
       <c r="B356" s="4">
-        <v>400</v>
+        <v>338</v>
       </c>
       <c r="C356" s="2">
-        <v>60</v>
+        <v>347</v>
       </c>
       <c r="D356" s="7">
-        <v>10</v>
+        <v>370</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15" customHeight="1">
       <c r="A357" s="20" t="s">
-        <v>114</v>
+        <v>348</v>
       </c>
       <c r="B357" s="4">
-        <v>549</v>
+        <v>209</v>
       </c>
       <c r="C357" s="2">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="D357" s="7">
-        <v>26</v>
+        <v>370</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15" customHeight="1">
       <c r="A358" s="20" t="s">
-        <v>126</v>
+        <v>349</v>
       </c>
       <c r="B358" s="4">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C358" s="2">
-        <v>90</v>
-      </c>
-      <c r="D358" s="7"/>
+        <v>120</v>
+      </c>
+      <c r="D358" s="7">
+        <v>635</v>
+      </c>
     </row>
     <row r="359" spans="1:4" ht="15" customHeight="1">
-      <c r="A359" s="21" t="s">
-        <v>125</v>
+      <c r="A359" s="17" t="s">
+        <v>350</v>
       </c>
       <c r="B359" s="4">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C359" s="2">
-        <v>3</v>
-      </c>
-      <c r="D359" s="7">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D359" s="7"/>
     </row>
     <row r="360" spans="1:4" ht="15" customHeight="1">
-      <c r="A360" s="21" t="s">
-        <v>247</v>
+      <c r="A360" s="19" t="s">
+        <v>123</v>
       </c>
       <c r="B360" s="4">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C360" s="2">
-        <v>35</v>
-      </c>
-      <c r="D360" s="7">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D360" s="7"/>
     </row>
     <row r="361" spans="1:4" ht="15" customHeight="1">
-      <c r="A361" s="21" t="s">
-        <v>248</v>
+      <c r="A361" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B361" s="4">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C361" s="2">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="D361" s="7">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15" customHeight="1">
       <c r="A362" s="21" t="s">
-        <v>127</v>
+        <v>372</v>
       </c>
       <c r="B362" s="4">
-        <v>3</v>
+        <v>10.8</v>
       </c>
       <c r="C362" s="2">
-        <v>0</v>
-      </c>
-      <c r="D362" s="7">
-        <v>91</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D362" s="7"/>
     </row>
     <row r="363" spans="1:4" ht="15" customHeight="1">
       <c r="A363" s="21" t="s">
-        <v>249</v>
+        <v>371</v>
       </c>
       <c r="B363" s="4">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="C363" s="2">
-        <v>3</v>
-      </c>
-      <c r="D363" s="7">
-        <v>14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D363" s="7"/>
     </row>
     <row r="364" spans="1:4" ht="15" customHeight="1">
       <c r="A364" s="21" t="s">
-        <v>115</v>
+        <v>369</v>
       </c>
       <c r="B364" s="4">
-        <v>50</v>
-      </c>
-      <c r="C364" s="2">
-        <v>25</v>
+        <v>9</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D364" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15" customHeight="1">
       <c r="A365" s="21" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B365" s="4">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C365" s="2">
-        <v>50</v>
-      </c>
-      <c r="D365" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="D365" s="7">
+        <v>3</v>
+      </c>
     </row>
     <row r="366" spans="1:4" ht="15" customHeight="1">
-      <c r="A366" s="21" t="s">
-        <v>364</v>
+      <c r="A366" s="20" t="s">
+        <v>237</v>
       </c>
       <c r="B366" s="4">
+        <v>400</v>
+      </c>
+      <c r="C366" s="2">
+        <v>60</v>
+      </c>
+      <c r="D366" s="7">
         <v>10</v>
       </c>
-      <c r="C366" s="2">
-        <v>100</v>
-      </c>
-      <c r="D366" s="7"/>
     </row>
     <row r="367" spans="1:4" ht="15" customHeight="1">
-      <c r="A367" s="21" t="s">
-        <v>365</v>
+      <c r="A367" s="20" t="s">
+        <v>112</v>
       </c>
       <c r="B367" s="4">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="C367" s="2">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="D367" s="7">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15" customHeight="1">
-      <c r="A368" s="21" t="s">
-        <v>116</v>
+      <c r="A368" s="20" t="s">
+        <v>121</v>
       </c>
       <c r="B368" s="4">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="C368" s="2">
-        <v>15</v>
-      </c>
-      <c r="D368" s="7">
-        <v>2</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D368" s="7"/>
     </row>
     <row r="369" spans="1:4" ht="15" customHeight="1">
       <c r="A369" s="21" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B369" s="4">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C369" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D369" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15" customHeight="1">
       <c r="A370" s="21" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B370" s="4">
+        <v>80</v>
+      </c>
+      <c r="C370" s="2">
+        <v>35</v>
+      </c>
+      <c r="D370" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" ht="15" customHeight="1">
+      <c r="A371" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="B371" s="4">
+        <v>78</v>
+      </c>
+      <c r="C371" s="2">
+        <v>80</v>
+      </c>
+      <c r="D371" s="7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" ht="15" customHeight="1">
+      <c r="A372" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B372" s="4">
+        <v>3</v>
+      </c>
+      <c r="C372" s="2">
         <v>0</v>
       </c>
-      <c r="C370" s="2">
+      <c r="D372" s="7">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" ht="15" customHeight="1">
+      <c r="A373" s="44" t="s">
+        <v>374</v>
+      </c>
+      <c r="B373" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="C373" s="2">
         <v>0</v>
       </c>
-      <c r="D370" s="7">
+      <c r="D373" s="7">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" ht="15" customHeight="1">
+      <c r="A374" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="B374" s="40">
+        <v>0</v>
+      </c>
+      <c r="C374" s="41">
+        <v>0</v>
+      </c>
+      <c r="D374" s="41">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" ht="15" customHeight="1">
+      <c r="A375" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="B375" s="4">
+        <v>10</v>
+      </c>
+      <c r="C375" s="2">
+        <v>3</v>
+      </c>
+      <c r="D375" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" ht="15" customHeight="1">
+      <c r="A376" s="45" t="s">
+        <v>383</v>
+      </c>
+      <c r="B376" s="4">
+        <v>27</v>
+      </c>
+      <c r="C376" s="2">
+        <v>20</v>
+      </c>
+      <c r="D376" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" ht="15" customHeight="1">
+      <c r="A377" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="B377" s="4">
+        <v>27</v>
+      </c>
+      <c r="C377" s="2">
+        <v>13</v>
+      </c>
+      <c r="D377" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" ht="15" customHeight="1">
+      <c r="A378" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B378" s="4">
+        <v>50</v>
+      </c>
+      <c r="C378" s="2">
+        <v>50</v>
+      </c>
+      <c r="D378" s="7"/>
+    </row>
+    <row r="379" spans="1:4" ht="15" customHeight="1">
+      <c r="A379" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="B379" s="4">
+        <v>10</v>
+      </c>
+      <c r="C379" s="2">
+        <v>100</v>
+      </c>
+      <c r="D379" s="7"/>
+    </row>
+    <row r="380" spans="1:4" ht="15" customHeight="1">
+      <c r="A380" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="B380" s="4">
+        <v>0</v>
+      </c>
+      <c r="C380" s="2">
+        <v>0</v>
+      </c>
+      <c r="D380" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" ht="15" customHeight="1">
+      <c r="A381" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B381" s="4">
+        <v>82</v>
+      </c>
+      <c r="C381" s="2">
+        <v>15</v>
+      </c>
+      <c r="D381" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" ht="15" customHeight="1">
+      <c r="A382" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B382" s="4">
+        <v>102</v>
+      </c>
+      <c r="C382" s="2">
+        <v>10</v>
+      </c>
+      <c r="D382" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" ht="15" customHeight="1">
+      <c r="A383" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="B383" s="4">
+        <v>0</v>
+      </c>
+      <c r="C383" s="2">
+        <v>0</v>
+      </c>
+      <c r="D383" s="7">
         <v>0</v>
       </c>
     </row>
@@ -7157,13 +7432,13 @@
       <formula>2000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B370">
+  <conditionalFormatting sqref="B2:B383">
     <cfRule type="cellIs" dxfId="5" priority="18" operator="between">
       <formula>400</formula>
       <formula>5000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B370">
+  <conditionalFormatting sqref="B1:B383">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="between">
       <formula>100</formula>
       <formula>200</formula>

--- a/KPH-AI.xlsx
+++ b/KPH-AI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="386">
   <si>
     <t>Praziluk</t>
   </si>
@@ -325,9 +325,6 @@
     <t>Puding razni kuvan</t>
   </si>
   <si>
-    <t>Celo zrno</t>
-  </si>
-  <si>
     <t>Griz (Krupica)</t>
   </si>
   <si>
@@ -379,9 +376,6 @@
     <t>Kafa espresso</t>
   </si>
   <si>
-    <t>Mleko za kafu na 100ml</t>
-  </si>
-  <si>
     <t>Mineralna voda (San Pelegrino limun)</t>
   </si>
   <si>
@@ -658,9 +652,6 @@
     <t>Sojino brasno</t>
   </si>
   <si>
-    <t>spargla</t>
-  </si>
-  <si>
     <t>Nar – sipak</t>
   </si>
   <si>
@@ -673,12 +664,6 @@
     <t>Marelica susena</t>
   </si>
   <si>
-    <t>sljiva suva</t>
-  </si>
-  <si>
-    <t>sljiva sveza</t>
-  </si>
-  <si>
     <t>Tresnja sveza</t>
   </si>
   <si>
@@ -728,12 +713,6 @@
   </si>
   <si>
     <t>Kakao + secer</t>
-  </si>
-  <si>
-    <t>Kafa instant + secer</t>
-  </si>
-  <si>
-    <t>Kafa s pavlakom +secer</t>
   </si>
   <si>
     <t>Zestoka pica 40 % alk.</t>
@@ -1069,9 +1048,6 @@
     <t>Krompir Pecen bez soli</t>
   </si>
   <si>
-    <t xml:space="preserve">Pomfrit </t>
-  </si>
-  <si>
     <t>Cips</t>
   </si>
   <si>
@@ -1286,12 +1262,39 @@
   <si>
     <t>Pivo 5% alk.</t>
   </si>
+  <si>
+    <t>Sljiva suva</t>
+  </si>
+  <si>
+    <t>Sljiva sveza</t>
+  </si>
+  <si>
+    <t>Kukuruz Celo zrno</t>
+  </si>
+  <si>
+    <t>Kafa Ness + secer</t>
+  </si>
+  <si>
+    <t>Mleko za kafu porcija 5ml</t>
+  </si>
+  <si>
+    <t>Mleko za kafu 100ml</t>
+  </si>
+  <si>
+    <t>Kafa Capuchino + secer</t>
+  </si>
+  <si>
+    <t>Spargla</t>
+  </si>
+  <si>
+    <t>Pomfrit McDonalds npr.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1403,8 +1406,24 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1467,6 +1486,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1495,7 +1520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1618,14 +1643,23 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1758,10 +1792,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF008000"/>
       <color rgb="FF99FF66"/>
       <color rgb="FFCCFF99"/>
       <color rgb="FFFFFF99"/>
-      <color rgb="FF008000"/>
       <color rgb="FFFFA7A9"/>
       <color rgb="FFFF7C80"/>
       <color rgb="FFC6E6A2"/>
@@ -2066,7 +2100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D383"/>
+  <dimension ref="A1:D384"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54.8984375" style="37" customWidth="1"/>
@@ -2090,7 +2124,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B2" s="4">
         <v>300</v>
@@ -2104,7 +2138,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="15" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B3" s="4">
         <v>245</v>
@@ -2118,7 +2152,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B4" s="4">
         <v>360</v>
@@ -2132,7 +2166,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="15" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B5" s="4">
         <v>330</v>
@@ -2146,7 +2180,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B6" s="4">
         <v>240</v>
@@ -2160,7 +2194,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B7" s="4">
         <v>340</v>
@@ -2174,7 +2208,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B8" s="4">
         <v>340</v>
@@ -2188,7 +2222,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="15" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B9" s="4">
         <v>320</v>
@@ -2202,7 +2236,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="17" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B10" s="4">
         <v>150</v>
@@ -2216,7 +2250,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="17" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B11" s="4">
         <v>125</v>
@@ -2230,7 +2264,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="17" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B12" s="4">
         <v>290</v>
@@ -2244,7 +2278,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="15" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B13" s="4">
         <v>370</v>
@@ -2258,7 +2292,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B14" s="4">
         <v>331</v>
@@ -2272,7 +2306,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="15" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B15" s="4">
         <v>220</v>
@@ -2286,7 +2320,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="15" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B16" s="4">
         <v>289</v>
@@ -2300,7 +2334,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B17" s="4">
         <v>220</v>
@@ -2314,7 +2348,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B18" s="4">
         <v>230</v>
@@ -2328,7 +2362,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B19" s="4">
         <v>210</v>
@@ -2342,7 +2376,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="15" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B20" s="4">
         <v>220</v>
@@ -2356,7 +2390,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B21" s="4">
         <v>300</v>
@@ -2370,7 +2404,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B22" s="4">
         <v>289</v>
@@ -2384,7 +2418,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="15" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B23" s="4">
         <v>333</v>
@@ -2398,7 +2432,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="15" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B24" s="4">
         <v>315</v>
@@ -2412,7 +2446,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B25" s="4">
         <v>220</v>
@@ -2454,7 +2488,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="15" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B28" s="4">
         <v>310</v>
@@ -2468,7 +2502,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B29" s="4">
         <v>301</v>
@@ -2496,7 +2530,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B31" s="4">
         <v>218</v>
@@ -2510,7 +2544,7 @@
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B32" s="4">
         <v>292</v>
@@ -2524,7 +2558,7 @@
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B33" s="4">
         <v>290</v>
@@ -2552,7 +2586,7 @@
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1">
       <c r="A35" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B35" s="4">
         <v>310</v>
@@ -2566,7 +2600,7 @@
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1">
       <c r="A36" s="15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B36" s="4">
         <v>255</v>
@@ -2608,7 +2642,7 @@
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1">
       <c r="A39" s="15" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B39" s="4">
         <v>281</v>
@@ -2622,7 +2656,7 @@
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1">
       <c r="A40" s="15" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B40" s="4">
         <v>320</v>
@@ -2636,7 +2670,7 @@
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1">
       <c r="A41" s="15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B41" s="4">
         <v>248</v>
@@ -2650,7 +2684,7 @@
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1">
       <c r="A42" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B42" s="4">
         <v>262</v>
@@ -2678,7 +2712,7 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1">
       <c r="A44" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B44" s="4">
         <v>265</v>
@@ -2692,7 +2726,7 @@
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1">
       <c r="A45" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B45" s="4">
         <v>177</v>
@@ -2706,7 +2740,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="31" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B46" s="4">
         <v>173</v>
@@ -2720,7 +2754,7 @@
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1">
       <c r="A47" s="19" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B47" s="4">
         <v>263</v>
@@ -2734,7 +2768,7 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1">
       <c r="A48" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B48" s="4">
         <v>200</v>
@@ -2748,7 +2782,7 @@
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1">
       <c r="A49" s="15" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B49" s="4">
         <v>207</v>
@@ -2804,7 +2838,7 @@
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1">
       <c r="A53" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B53" s="5">
         <v>400</v>
@@ -2812,13 +2846,13 @@
       <c r="C53" s="2">
         <v>108</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="49">
         <v>1600</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1">
       <c r="A54" s="15" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B54" s="4">
         <v>285</v>
@@ -2826,13 +2860,13 @@
       <c r="C54" s="2">
         <v>172</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="49">
         <v>1440</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1">
       <c r="A55" s="15" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B55" s="4">
         <v>310</v>
@@ -2840,7 +2874,7 @@
       <c r="C55" s="2">
         <v>196</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="49">
         <v>1130</v>
       </c>
     </row>
@@ -2854,13 +2888,13 @@
       <c r="C56" s="2">
         <v>204</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="48">
         <v>2240</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B57" s="4">
         <v>204</v>
@@ -2874,7 +2908,7 @@
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1">
       <c r="A58" s="15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B58" s="4">
         <v>377</v>
@@ -2882,13 +2916,13 @@
       <c r="C58" s="2">
         <v>204</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="48">
         <v>2240</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1">
       <c r="A59" s="20" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B59" s="4">
         <v>800</v>
@@ -2902,7 +2936,7 @@
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1">
       <c r="A60" s="21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B60" s="4">
         <v>115</v>
@@ -2916,7 +2950,7 @@
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1">
       <c r="A61" s="19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B61" s="4">
         <v>180</v>
@@ -2930,7 +2964,7 @@
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1">
       <c r="A62" s="20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B62" s="4">
         <v>300</v>
@@ -2944,7 +2978,7 @@
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1">
       <c r="A63" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B63" s="4">
         <v>190</v>
@@ -2972,7 +3006,7 @@
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1">
       <c r="A65" s="20" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B65" s="4">
         <v>200</v>
@@ -2986,7 +3020,7 @@
     </row>
     <row r="66" spans="1:4" ht="15" customHeight="1">
       <c r="A66" s="15" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B66" s="4">
         <v>335</v>
@@ -3000,7 +3034,7 @@
     </row>
     <row r="67" spans="1:4" ht="15" customHeight="1">
       <c r="A67" s="19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B67" s="4">
         <v>210</v>
@@ -3014,7 +3048,7 @@
     </row>
     <row r="68" spans="1:4" ht="15" customHeight="1">
       <c r="A68" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B68" s="4">
         <v>329</v>
@@ -3028,7 +3062,7 @@
     </row>
     <row r="69" spans="1:4" ht="15" customHeight="1">
       <c r="A69" s="15" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B69" s="4">
         <v>192</v>
@@ -3042,7 +3076,7 @@
     </row>
     <row r="70" spans="1:4" ht="15" customHeight="1">
       <c r="A70" s="15" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B70" s="4">
         <v>260</v>
@@ -3056,7 +3090,7 @@
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1">
       <c r="A71" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B71" s="4">
         <v>313</v>
@@ -3070,7 +3104,7 @@
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1">
       <c r="A72" s="15" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B72" s="4">
         <v>194</v>
@@ -3084,7 +3118,7 @@
     </row>
     <row r="73" spans="1:4" ht="15" customHeight="1">
       <c r="A73" s="15" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B73" s="4">
         <v>275</v>
@@ -3098,7 +3132,7 @@
     </row>
     <row r="74" spans="1:4" ht="15" customHeight="1">
       <c r="A74" s="15" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B74" s="4">
         <v>405</v>
@@ -3112,7 +3146,7 @@
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1">
       <c r="A75" s="21" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B75" s="4">
         <v>133</v>
@@ -3126,7 +3160,7 @@
     </row>
     <row r="76" spans="1:4" ht="15" customHeight="1">
       <c r="A76" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B76" s="4">
         <v>204</v>
@@ -3154,7 +3188,7 @@
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1">
       <c r="A78" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B78" s="4">
         <v>280</v>
@@ -3168,7 +3202,7 @@
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1">
       <c r="A79" s="20" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B79" s="4">
         <v>245</v>
@@ -3182,7 +3216,7 @@
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1">
       <c r="A80" s="20" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B80" s="4">
         <v>280</v>
@@ -3196,7 +3230,7 @@
     </row>
     <row r="81" spans="1:4" ht="15" customHeight="1">
       <c r="A81" s="38" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B81" s="4">
         <v>250</v>
@@ -3210,7 +3244,7 @@
     </row>
     <row r="82" spans="1:4" ht="15" customHeight="1">
       <c r="A82" s="38" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B82" s="4">
         <v>220</v>
@@ -3224,7 +3258,7 @@
     </row>
     <row r="83" spans="1:4" ht="15" customHeight="1">
       <c r="A83" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B83" s="4">
         <v>330</v>
@@ -3238,7 +3272,7 @@
     </row>
     <row r="84" spans="1:4" ht="15" customHeight="1">
       <c r="A84" s="15" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B84" s="4">
         <v>362</v>
@@ -3252,7 +3286,7 @@
     </row>
     <row r="85" spans="1:4" ht="15" customHeight="1">
       <c r="A85" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B85" s="4">
         <v>340</v>
@@ -3266,7 +3300,7 @@
     </row>
     <row r="86" spans="1:4" ht="15" customHeight="1">
       <c r="A86" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B86" s="4">
         <v>250</v>
@@ -3280,7 +3314,7 @@
     </row>
     <row r="87" spans="1:4" ht="15" customHeight="1">
       <c r="A87" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B87" s="4">
         <v>371</v>
@@ -3350,7 +3384,7 @@
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1">
       <c r="A92" s="15" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B92" s="4">
         <v>310</v>
@@ -3378,7 +3412,7 @@
     </row>
     <row r="94" spans="1:4" ht="15" customHeight="1">
       <c r="A94" s="15" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B94" s="5">
         <v>439</v>
@@ -3392,7 +3426,7 @@
     </row>
     <row r="95" spans="1:4" ht="15" customHeight="1">
       <c r="A95" s="15" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B95" s="4">
         <v>328</v>
@@ -3406,7 +3440,7 @@
     </row>
     <row r="96" spans="1:4" ht="15" customHeight="1">
       <c r="A96" s="15" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B96" s="4">
         <v>400</v>
@@ -3418,7 +3452,7 @@
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
       <c r="A97" s="15" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B97" s="4">
         <v>294</v>
@@ -3432,7 +3466,7 @@
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
       <c r="A98" s="15" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B98" s="4">
         <v>396</v>
@@ -3446,7 +3480,7 @@
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
       <c r="A99" s="15" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B99" s="4">
         <v>324</v>
@@ -3460,7 +3494,7 @@
     </row>
     <row r="100" spans="1:4" ht="15" customHeight="1">
       <c r="A100" s="15" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B100" s="4">
         <v>330</v>
@@ -3474,7 +3508,7 @@
     </row>
     <row r="101" spans="1:4" ht="15" customHeight="1">
       <c r="A101" s="15" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B101" s="4">
         <v>441</v>
@@ -3488,7 +3522,7 @@
     </row>
     <row r="102" spans="1:4" ht="15" customHeight="1">
       <c r="A102" s="15" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B102" s="4">
         <v>630</v>
@@ -3500,7 +3534,7 @@
     </row>
     <row r="103" spans="1:4" ht="15" customHeight="1">
       <c r="A103" s="15" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B103" s="4">
         <v>400</v>
@@ -3512,7 +3546,7 @@
     </row>
     <row r="104" spans="1:4" ht="15" customHeight="1">
       <c r="A104" s="15" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B104" s="4">
         <v>299</v>
@@ -3526,7 +3560,7 @@
     </row>
     <row r="105" spans="1:4" ht="15" customHeight="1">
       <c r="A105" s="15" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B105" s="4">
         <v>306</v>
@@ -3540,7 +3574,7 @@
     </row>
     <row r="106" spans="1:4" ht="15" customHeight="1">
       <c r="A106" s="15" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B106" s="4">
         <v>349</v>
@@ -3554,7 +3588,7 @@
     </row>
     <row r="107" spans="1:4" ht="15" customHeight="1">
       <c r="A107" s="15" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B107" s="4">
         <v>340</v>
@@ -3568,7 +3602,7 @@
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
       <c r="A108" s="15" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B108" s="5">
         <v>427</v>
@@ -3582,7 +3616,7 @@
     </row>
     <row r="109" spans="1:4" ht="15" customHeight="1">
       <c r="A109" s="15" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B109" s="4">
         <v>268</v>
@@ -3596,7 +3630,7 @@
     </row>
     <row r="110" spans="1:4" ht="15" customHeight="1">
       <c r="A110" s="15" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B110" s="4">
         <v>352</v>
@@ -3610,7 +3644,7 @@
     </row>
     <row r="111" spans="1:4" ht="15" customHeight="1">
       <c r="A111" s="22" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B111" s="4">
         <v>168</v>
@@ -3624,7 +3658,7 @@
     </row>
     <row r="112" spans="1:4" ht="15" customHeight="1">
       <c r="A112" s="22" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B112" s="4">
         <v>182</v>
@@ -3638,7 +3672,7 @@
     </row>
     <row r="113" spans="1:4" ht="15" customHeight="1">
       <c r="A113" s="15" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B113" s="5">
         <v>637</v>
@@ -3652,7 +3686,7 @@
     </row>
     <row r="114" spans="1:4" ht="15" customHeight="1">
       <c r="A114" s="23" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B114" s="5">
         <v>351</v>
@@ -3680,7 +3714,7 @@
     </row>
     <row r="116" spans="1:4" ht="15" customHeight="1">
       <c r="A116" s="15" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B116" s="5">
         <v>430</v>
@@ -3694,7 +3728,7 @@
     </row>
     <row r="117" spans="1:4" ht="15" customHeight="1">
       <c r="A117" s="15" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B117" s="4">
         <v>267</v>
@@ -3708,7 +3742,7 @@
     </row>
     <row r="118" spans="1:4" ht="15" customHeight="1">
       <c r="A118" s="15" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B118" s="4">
         <v>280</v>
@@ -3722,7 +3756,7 @@
     </row>
     <row r="119" spans="1:4" ht="15" customHeight="1">
       <c r="A119" s="19" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B119" s="4">
         <v>149</v>
@@ -3736,7 +3770,7 @@
     </row>
     <row r="120" spans="1:4" ht="15" customHeight="1">
       <c r="A120" s="19" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B120" s="4">
         <v>158</v>
@@ -3750,7 +3784,7 @@
     </row>
     <row r="121" spans="1:4" ht="15" customHeight="1">
       <c r="A121" s="20" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B121" s="4">
         <v>205</v>
@@ -3764,7 +3798,7 @@
     </row>
     <row r="122" spans="1:4" ht="15" customHeight="1">
       <c r="A122" s="19" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B122" s="4">
         <v>158</v>
@@ -3778,7 +3812,7 @@
     </row>
     <row r="123" spans="1:4" ht="15" customHeight="1">
       <c r="A123" s="15" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B123" s="4">
         <v>136</v>
@@ -3834,7 +3868,7 @@
     </row>
     <row r="127" spans="1:4" ht="15" customHeight="1">
       <c r="A127" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B127" s="4">
         <v>167</v>
@@ -3862,7 +3896,7 @@
     </row>
     <row r="129" spans="1:4" ht="15" customHeight="1">
       <c r="A129" s="20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B129" s="4">
         <v>170</v>
@@ -3932,7 +3966,7 @@
     </row>
     <row r="134" spans="1:4" ht="15" customHeight="1">
       <c r="A134" s="20" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B134" s="4">
         <v>150</v>
@@ -3960,7 +3994,7 @@
     </row>
     <row r="136" spans="1:4" ht="15" customHeight="1">
       <c r="A136" s="15" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B136" s="4">
         <v>132</v>
@@ -3974,7 +4008,7 @@
     </row>
     <row r="137" spans="1:4" ht="15" customHeight="1">
       <c r="A137" s="15" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B137" s="4">
         <v>120</v>
@@ -3988,7 +4022,7 @@
     </row>
     <row r="138" spans="1:4" ht="15" customHeight="1">
       <c r="A138" s="15" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B138" s="4">
         <v>102</v>
@@ -4002,7 +4036,7 @@
     </row>
     <row r="139" spans="1:4" ht="15" customHeight="1">
       <c r="A139" s="15" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B139" s="4">
         <v>95</v>
@@ -4016,7 +4050,7 @@
     </row>
     <row r="140" spans="1:4" ht="15" customHeight="1">
       <c r="A140" s="15" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B140" s="4">
         <v>87</v>
@@ -4030,7 +4064,7 @@
     </row>
     <row r="141" spans="1:4" ht="15" customHeight="1">
       <c r="A141" s="15" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B141" s="4">
         <v>107</v>
@@ -4044,7 +4078,7 @@
     </row>
     <row r="142" spans="1:4" ht="15" customHeight="1">
       <c r="A142" s="15" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B142" s="4">
         <v>62</v>
@@ -4058,7 +4092,7 @@
     </row>
     <row r="143" spans="1:4" ht="15" customHeight="1">
       <c r="A143" s="15" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B143" s="4">
         <v>76</v>
@@ -4072,7 +4106,7 @@
     </row>
     <row r="144" spans="1:4" ht="15" customHeight="1">
       <c r="A144" s="15" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B144" s="4">
         <v>123</v>
@@ -4086,7 +4120,7 @@
     </row>
     <row r="145" spans="1:4" ht="15" customHeight="1">
       <c r="A145" s="15" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B145" s="4">
         <v>81</v>
@@ -4100,7 +4134,7 @@
     </row>
     <row r="146" spans="1:4" ht="15" customHeight="1">
       <c r="A146" s="15" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B146" s="4">
         <v>128</v>
@@ -4114,7 +4148,7 @@
     </row>
     <row r="147" spans="1:4" ht="15" customHeight="1">
       <c r="A147" s="20" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B147" s="4">
         <v>38</v>
@@ -4142,7 +4176,7 @@
     </row>
     <row r="149" spans="1:4" ht="15" customHeight="1">
       <c r="A149" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B149" s="4">
         <v>95</v>
@@ -4156,7 +4190,7 @@
     </row>
     <row r="150" spans="1:4" ht="15" customHeight="1">
       <c r="A150" s="20" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B150" s="4">
         <v>190</v>
@@ -4170,7 +4204,7 @@
     </row>
     <row r="151" spans="1:4" ht="15" customHeight="1">
       <c r="A151" s="20" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B151" s="4">
         <v>190</v>
@@ -4184,7 +4218,7 @@
     </row>
     <row r="152" spans="1:4" ht="15" customHeight="1">
       <c r="A152" s="20" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B152" s="4">
         <v>149</v>
@@ -4198,7 +4232,7 @@
     </row>
     <row r="153" spans="1:4" ht="15" customHeight="1">
       <c r="A153" s="20" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B153" s="4">
         <v>147</v>
@@ -4212,7 +4246,7 @@
     </row>
     <row r="154" spans="1:4" ht="15" customHeight="1">
       <c r="A154" s="15" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B154" s="4">
         <v>130</v>
@@ -4226,7 +4260,7 @@
     </row>
     <row r="155" spans="1:4" ht="15" customHeight="1">
       <c r="A155" s="15" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B155" s="4">
         <v>210</v>
@@ -4240,7 +4274,7 @@
     </row>
     <row r="156" spans="1:4" ht="15" customHeight="1">
       <c r="A156" s="15" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B156" s="4">
         <v>233</v>
@@ -4254,7 +4288,7 @@
     </row>
     <row r="157" spans="1:4" ht="15" customHeight="1">
       <c r="A157" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B157" s="4">
         <v>132</v>
@@ -4268,7 +4302,7 @@
     </row>
     <row r="158" spans="1:4" ht="15" customHeight="1">
       <c r="A158" s="16" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B158" s="6">
         <v>142</v>
@@ -4352,7 +4386,7 @@
     </row>
     <row r="164" spans="1:4" ht="15" customHeight="1">
       <c r="A164" s="21" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B164" s="12">
         <v>0</v>
@@ -4366,7 +4400,7 @@
     </row>
     <row r="165" spans="1:4" ht="15" customHeight="1">
       <c r="A165" s="20" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B165" s="4">
         <v>130</v>
@@ -4380,7 +4414,7 @@
     </row>
     <row r="166" spans="1:4" ht="15" customHeight="1">
       <c r="A166" s="15" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B166" s="5">
         <v>570</v>
@@ -4394,7 +4428,7 @@
     </row>
     <row r="167" spans="1:4" ht="15" customHeight="1">
       <c r="A167" s="15" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B167" s="4">
         <v>310</v>
@@ -4408,7 +4442,7 @@
     </row>
     <row r="168" spans="1:4" ht="15" customHeight="1">
       <c r="A168" s="15" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B168" s="5">
         <v>455</v>
@@ -4422,7 +4456,7 @@
     </row>
     <row r="169" spans="1:4" ht="15" customHeight="1">
       <c r="A169" s="15" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B169" s="4">
         <v>350</v>
@@ -4431,12 +4465,12 @@
         <v>61</v>
       </c>
       <c r="D169" s="7">
-        <v>-300</v>
+        <v>300</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15" customHeight="1">
       <c r="A170" s="18" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B170" s="5">
         <v>500</v>
@@ -4450,7 +4484,7 @@
     </row>
     <row r="171" spans="1:4" ht="15" customHeight="1">
       <c r="A171" s="18" t="s">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="B171" s="5">
         <v>460</v>
@@ -4459,12 +4493,12 @@
         <v>33</v>
       </c>
       <c r="D171" s="7">
-        <v>-450</v>
+        <v>400</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15" customHeight="1">
       <c r="A172" s="18" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B172" s="5">
         <v>1275</v>
@@ -4478,7 +4512,7 @@
     </row>
     <row r="173" spans="1:4" ht="15" customHeight="1">
       <c r="A173" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B173" s="4">
         <v>376</v>
@@ -4590,7 +4624,7 @@
     </row>
     <row r="181" spans="1:4" ht="15" customHeight="1">
       <c r="A181" s="15" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B181" s="4">
         <v>288</v>
@@ -4618,7 +4652,7 @@
     </row>
     <row r="183" spans="1:4" ht="15" customHeight="1">
       <c r="A183" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B183" s="4">
         <v>399</v>
@@ -4632,7 +4666,7 @@
     </row>
     <row r="184" spans="1:4" ht="15" customHeight="1">
       <c r="A184" s="26" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B184" s="5">
         <v>1000</v>
@@ -4660,7 +4694,7 @@
     </row>
     <row r="186" spans="1:4" ht="15" customHeight="1">
       <c r="A186" s="15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B186" s="4">
         <v>322</v>
@@ -4716,7 +4750,7 @@
     </row>
     <row r="190" spans="1:4" ht="15" customHeight="1">
       <c r="A190" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B190" s="5">
         <v>633</v>
@@ -4800,7 +4834,7 @@
     </row>
     <row r="196" spans="1:4" ht="15" customHeight="1">
       <c r="A196" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B196" s="4">
         <v>315</v>
@@ -4870,7 +4904,7 @@
     </row>
     <row r="201" spans="1:4" ht="15" customHeight="1">
       <c r="A201" s="15" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B201" s="4">
         <v>210</v>
@@ -4884,7 +4918,7 @@
     </row>
     <row r="202" spans="1:4" ht="15" customHeight="1">
       <c r="A202" s="15" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B202" s="4">
         <v>180</v>
@@ -4901,7 +4935,7 @@
         <v>63</v>
       </c>
       <c r="B203" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C203" s="2">
         <v>83</v>
@@ -4912,10 +4946,10 @@
     </row>
     <row r="204" spans="1:4" ht="15" customHeight="1">
       <c r="A204" s="15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B204" s="4">
-        <v>265</v>
+        <v>550</v>
       </c>
       <c r="C204" s="2">
         <v>101</v>
@@ -4926,7 +4960,7 @@
     </row>
     <row r="205" spans="1:4" ht="15" customHeight="1">
       <c r="A205" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B205" s="4">
         <v>340</v>
@@ -4940,7 +4974,7 @@
     </row>
     <row r="206" spans="1:4" ht="15" customHeight="1">
       <c r="A206" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B206" s="4">
         <v>250</v>
@@ -4996,7 +5030,7 @@
     </row>
     <row r="210" spans="1:4" ht="15" customHeight="1">
       <c r="A210" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B210" s="4">
         <v>121</v>
@@ -5010,7 +5044,7 @@
     </row>
     <row r="211" spans="1:4" ht="15" customHeight="1">
       <c r="A211" s="24" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B211" s="5">
         <v>1660</v>
@@ -5038,7 +5072,7 @@
     </row>
     <row r="213" spans="1:4" ht="15" customHeight="1">
       <c r="A213" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B213" s="4">
         <v>140</v>
@@ -5066,7 +5100,7 @@
     </row>
     <row r="215" spans="1:4" ht="15" customHeight="1">
       <c r="A215" s="20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B215" s="4">
         <v>320</v>
@@ -5074,7 +5108,9 @@
       <c r="C215" s="2">
         <v>45</v>
       </c>
-      <c r="D215" s="7"/>
+      <c r="D215" s="7">
+        <v>400</v>
+      </c>
     </row>
     <row r="216" spans="1:4" ht="15" customHeight="1">
       <c r="A216" s="20" t="s">
@@ -5092,7 +5128,7 @@
     </row>
     <row r="217" spans="1:4" ht="15" customHeight="1">
       <c r="A217" s="28" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B217" s="5">
         <v>3170</v>
@@ -5106,7 +5142,7 @@
     </row>
     <row r="218" spans="1:4" ht="15" customHeight="1">
       <c r="A218" s="29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B218" s="4">
         <v>129</v>
@@ -5120,7 +5156,7 @@
     </row>
     <row r="219" spans="1:4" ht="15" customHeight="1">
       <c r="A219" s="29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B219" s="4">
         <v>176</v>
@@ -5134,7 +5170,7 @@
     </row>
     <row r="220" spans="1:4" ht="15" customHeight="1">
       <c r="A220" s="20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B220" s="4">
         <v>305</v>
@@ -5148,7 +5184,7 @@
     </row>
     <row r="221" spans="1:4" ht="15" customHeight="1">
       <c r="A221" s="20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B221" s="4">
         <v>275</v>
@@ -5162,7 +5198,7 @@
     </row>
     <row r="222" spans="1:4" ht="15" customHeight="1">
       <c r="A222" s="20" t="s">
-        <v>214</v>
+        <v>384</v>
       </c>
       <c r="B222" s="4">
         <v>207</v>
@@ -5260,7 +5296,7 @@
     </row>
     <row r="229" spans="1:4" ht="15" customHeight="1">
       <c r="A229" s="20" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>10</v>
@@ -5274,7 +5310,7 @@
     </row>
     <row r="230" spans="1:4" ht="15" customHeight="1">
       <c r="A230" s="20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B230" s="4">
         <v>140</v>
@@ -5288,7 +5324,7 @@
     </row>
     <row r="231" spans="1:4" ht="15" customHeight="1">
       <c r="A231" s="20" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B231" s="4">
         <v>43</v>
@@ -5302,7 +5338,7 @@
     </row>
     <row r="232" spans="1:4" ht="15" customHeight="1">
       <c r="A232" s="20" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B232" s="4">
         <v>131</v>
@@ -5358,7 +5394,7 @@
     </row>
     <row r="236" spans="1:4" ht="15" customHeight="1">
       <c r="A236" s="15" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B236" s="5">
         <v>450</v>
@@ -5372,7 +5408,7 @@
     </row>
     <row r="237" spans="1:4" ht="15" customHeight="1">
       <c r="A237" s="15" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B237" s="5">
         <v>422</v>
@@ -5386,7 +5422,7 @@
     </row>
     <row r="238" spans="1:4" ht="15" customHeight="1">
       <c r="A238" s="15" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B238" s="4">
         <v>346</v>
@@ -5400,7 +5436,7 @@
     </row>
     <row r="239" spans="1:4" ht="15" customHeight="1">
       <c r="A239" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B239" s="4">
         <v>277</v>
@@ -5442,7 +5478,7 @@
     </row>
     <row r="242" spans="1:4" ht="15" customHeight="1">
       <c r="A242" s="20" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B242" s="4">
         <v>260</v>
@@ -5456,7 +5492,7 @@
     </row>
     <row r="243" spans="1:4" ht="15" customHeight="1">
       <c r="A243" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B243" s="4">
         <v>177</v>
@@ -5470,7 +5506,7 @@
     </row>
     <row r="244" spans="1:4" ht="15" customHeight="1">
       <c r="A244" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B244" s="4">
         <v>81</v>
@@ -5484,7 +5520,7 @@
     </row>
     <row r="245" spans="1:4" ht="15" customHeight="1">
       <c r="A245" s="24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B245" s="5">
         <v>782</v>
@@ -5498,7 +5534,7 @@
     </row>
     <row r="246" spans="1:4" ht="15" customHeight="1">
       <c r="A246" s="20" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B246" s="4">
         <v>192</v>
@@ -5512,7 +5548,7 @@
     </row>
     <row r="247" spans="1:4" ht="15" customHeight="1">
       <c r="A247" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B247" s="4">
         <v>147</v>
@@ -5526,7 +5562,7 @@
     </row>
     <row r="248" spans="1:4" ht="15" customHeight="1">
       <c r="A248" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B248" s="4">
         <v>170</v>
@@ -5594,7 +5630,7 @@
     </row>
     <row r="253" spans="1:4" ht="15" customHeight="1">
       <c r="A253" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B253" s="4">
         <v>126</v>
@@ -5608,7 +5644,7 @@
     </row>
     <row r="254" spans="1:4" ht="15" customHeight="1">
       <c r="A254" s="31" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B254" s="5">
         <v>1340</v>
@@ -5622,7 +5658,7 @@
     </row>
     <row r="255" spans="1:4" ht="15" customHeight="1">
       <c r="A255" s="20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B255" s="4">
         <v>205</v>
@@ -5636,7 +5672,7 @@
     </row>
     <row r="256" spans="1:4" ht="15" customHeight="1">
       <c r="A256" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B256" s="5">
         <v>1370</v>
@@ -5650,7 +5686,7 @@
     </row>
     <row r="257" spans="1:4" ht="15" customHeight="1">
       <c r="A257" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B257" s="4">
         <v>278</v>
@@ -5664,7 +5700,7 @@
     </row>
     <row r="258" spans="1:4" ht="15" customHeight="1">
       <c r="A258" s="31" t="s">
-        <v>219</v>
+        <v>377</v>
       </c>
       <c r="B258" s="5">
         <v>860</v>
@@ -5678,7 +5714,7 @@
     </row>
     <row r="259" spans="1:4" ht="15" customHeight="1">
       <c r="A259" s="20" t="s">
-        <v>220</v>
+        <v>378</v>
       </c>
       <c r="B259" s="4">
         <v>221</v>
@@ -5692,7 +5728,7 @@
     </row>
     <row r="260" spans="1:4" ht="15" customHeight="1">
       <c r="A260" s="20" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B260" s="4">
         <v>229</v>
@@ -5706,7 +5742,7 @@
     </row>
     <row r="261" spans="1:4" ht="15" customHeight="1">
       <c r="A261" s="20" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B261" s="4">
         <v>191</v>
@@ -5818,7 +5854,7 @@
     </row>
     <row r="269" spans="1:4" ht="15" customHeight="1">
       <c r="A269" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B269" s="4">
         <v>240</v>
@@ -5846,7 +5882,7 @@
     </row>
     <row r="271" spans="1:4" ht="15" customHeight="1">
       <c r="A271" s="42" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B271" s="4">
         <v>140</v>
@@ -5860,7 +5896,7 @@
     </row>
     <row r="272" spans="1:4" ht="15" customHeight="1">
       <c r="A272" s="42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B272" s="4">
         <v>124</v>
@@ -5874,7 +5910,7 @@
     </row>
     <row r="273" spans="1:4" ht="15" customHeight="1">
       <c r="A273" s="42" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B273" s="4">
         <v>132</v>
@@ -5888,7 +5924,7 @@
     </row>
     <row r="274" spans="1:4" ht="15" customHeight="1">
       <c r="A274" s="42" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B274" s="4">
         <v>105</v>
@@ -5902,7 +5938,7 @@
     </row>
     <row r="275" spans="1:4" ht="15" customHeight="1">
       <c r="A275" s="43" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B275" s="4">
         <v>100</v>
@@ -5916,7 +5952,7 @@
     </row>
     <row r="276" spans="1:4" ht="15" customHeight="1">
       <c r="A276" s="42" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B276" s="4">
         <v>200</v>
@@ -5930,7 +5966,7 @@
     </row>
     <row r="277" spans="1:4" ht="15" customHeight="1">
       <c r="A277" s="42" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B277" s="4">
         <v>33</v>
@@ -5972,7 +6008,7 @@
     </row>
     <row r="280" spans="1:4" ht="15" customHeight="1">
       <c r="A280" s="42" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B280" s="4">
         <v>50</v>
@@ -5986,7 +6022,7 @@
     </row>
     <row r="281" spans="1:4" ht="15" customHeight="1">
       <c r="A281" s="42" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B281" s="4">
         <v>80</v>
@@ -6000,7 +6036,7 @@
     </row>
     <row r="282" spans="1:4" ht="15" customHeight="1">
       <c r="A282" s="42" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B282" s="4">
         <v>100</v>
@@ -6014,7 +6050,7 @@
     </row>
     <row r="283" spans="1:4" ht="15" customHeight="1">
       <c r="A283" s="42" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B283" s="4">
         <v>60</v>
@@ -6028,7 +6064,7 @@
     </row>
     <row r="284" spans="1:4" ht="15" customHeight="1">
       <c r="A284" s="42" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B284" s="4">
         <v>130</v>
@@ -6042,7 +6078,7 @@
     </row>
     <row r="285" spans="1:4" ht="15" customHeight="1">
       <c r="A285" s="33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B285" s="4">
         <v>94</v>
@@ -6056,7 +6092,7 @@
     </row>
     <row r="286" spans="1:4" ht="15" customHeight="1">
       <c r="A286" s="34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B286" s="4">
         <v>150</v>
@@ -6070,7 +6106,7 @@
     </row>
     <row r="287" spans="1:4" ht="15" customHeight="1">
       <c r="A287" s="33" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B287" s="4">
         <v>90</v>
@@ -6084,7 +6120,7 @@
     </row>
     <row r="288" spans="1:4" ht="15" customHeight="1">
       <c r="A288" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B288" s="4">
         <v>260</v>
@@ -6098,7 +6134,7 @@
     </row>
     <row r="289" spans="1:4" ht="15" customHeight="1">
       <c r="A289" s="33" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B289" s="4">
         <v>80</v>
@@ -6112,7 +6148,7 @@
     </row>
     <row r="290" spans="1:4" ht="15" customHeight="1">
       <c r="A290" s="33" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B290" s="4">
         <v>125</v>
@@ -6126,7 +6162,7 @@
     </row>
     <row r="291" spans="1:4" ht="15" customHeight="1">
       <c r="A291" s="15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B291" s="4">
         <v>407</v>
@@ -6137,8 +6173,8 @@
       <c r="D291" s="7"/>
     </row>
     <row r="292" spans="1:4" ht="15" customHeight="1">
-      <c r="A292" s="21" t="s">
-        <v>200</v>
+      <c r="A292" s="46" t="s">
+        <v>198</v>
       </c>
       <c r="B292" s="4">
         <v>45</v>
@@ -6151,7 +6187,7 @@
       </c>
     </row>
     <row r="293" spans="1:4" ht="15" customHeight="1">
-      <c r="A293" s="21" t="s">
+      <c r="A293" s="46" t="s">
         <v>5</v>
       </c>
       <c r="B293" s="4">
@@ -6165,8 +6201,8 @@
       </c>
     </row>
     <row r="294" spans="1:4" ht="15" customHeight="1">
-      <c r="A294" s="21" t="s">
-        <v>201</v>
+      <c r="A294" s="46" t="s">
+        <v>199</v>
       </c>
       <c r="B294" s="4">
         <v>65</v>
@@ -6179,8 +6215,8 @@
       </c>
     </row>
     <row r="295" spans="1:4" ht="15" customHeight="1">
-      <c r="A295" s="20" t="s">
-        <v>202</v>
+      <c r="A295" s="46" t="s">
+        <v>200</v>
       </c>
       <c r="B295" s="4">
         <v>104</v>
@@ -6193,8 +6229,8 @@
       </c>
     </row>
     <row r="296" spans="1:4" ht="15" customHeight="1">
-      <c r="A296" s="20" t="s">
-        <v>227</v>
+      <c r="A296" s="46" t="s">
+        <v>222</v>
       </c>
       <c r="B296" s="4">
         <v>130</v>
@@ -6207,8 +6243,8 @@
       </c>
     </row>
     <row r="297" spans="1:4" ht="15" customHeight="1">
-      <c r="A297" s="21" t="s">
-        <v>228</v>
+      <c r="A297" s="46" t="s">
+        <v>223</v>
       </c>
       <c r="B297" s="4">
         <v>44</v>
@@ -6222,7 +6258,7 @@
     </row>
     <row r="298" spans="1:4" ht="15" customHeight="1">
       <c r="A298" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B298" s="5">
         <v>705</v>
@@ -6236,7 +6272,7 @@
     </row>
     <row r="299" spans="1:4" ht="15" customHeight="1">
       <c r="A299" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B299" s="5">
         <v>592</v>
@@ -6250,7 +6286,7 @@
     </row>
     <row r="300" spans="1:4" ht="15" customHeight="1">
       <c r="A300" s="15" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B300" s="5">
         <v>500</v>
@@ -6264,7 +6300,7 @@
     </row>
     <row r="301" spans="1:4" ht="15" customHeight="1">
       <c r="A301" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B301" s="5">
         <v>777</v>
@@ -6278,7 +6314,7 @@
     </row>
     <row r="302" spans="1:4" ht="15" customHeight="1">
       <c r="A302" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B302" s="5">
         <v>786</v>
@@ -6287,7 +6323,7 @@
         <v>410</v>
       </c>
       <c r="D302" s="7">
-        <v>-420</v>
+        <v>420</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15" customHeight="1">
@@ -6306,7 +6342,7 @@
     </row>
     <row r="304" spans="1:4" ht="15" customHeight="1">
       <c r="A304" s="15" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B304" s="5">
         <v>704</v>
@@ -6390,7 +6426,7 @@
     </row>
     <row r="310" spans="1:4" ht="15" customHeight="1">
       <c r="A310" s="21" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B310" s="4">
         <v>100</v>
@@ -6404,7 +6440,7 @@
     </row>
     <row r="311" spans="1:4" ht="15" customHeight="1">
       <c r="A311" s="20" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B311" s="4">
         <v>250</v>
@@ -6432,7 +6468,7 @@
     </row>
     <row r="313" spans="1:4" ht="15" customHeight="1">
       <c r="A313" s="20" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B313" s="4">
         <v>130</v>
@@ -6460,7 +6496,7 @@
     </row>
     <row r="315" spans="1:4" ht="15" customHeight="1">
       <c r="A315" s="21" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B315" s="4">
         <v>0</v>
@@ -6488,7 +6524,7 @@
     </row>
     <row r="317" spans="1:4" ht="15" customHeight="1">
       <c r="A317" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B317" s="4">
         <v>50</v>
@@ -6500,7 +6536,7 @@
     </row>
     <row r="318" spans="1:4" ht="15" customHeight="1">
       <c r="A318" s="20" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B318" s="5">
         <v>400</v>
@@ -6528,7 +6564,7 @@
     </row>
     <row r="320" spans="1:4" ht="15" customHeight="1">
       <c r="A320" s="15" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B320" s="5">
         <v>452</v>
@@ -6542,7 +6578,7 @@
     </row>
     <row r="321" spans="1:4" ht="15" customHeight="1">
       <c r="A321" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B321" s="4">
         <v>160</v>
@@ -6556,7 +6592,7 @@
     </row>
     <row r="322" spans="1:4" ht="15" customHeight="1">
       <c r="A322" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B322" s="4">
         <v>90</v>
@@ -6570,7 +6606,7 @@
     </row>
     <row r="323" spans="1:4" ht="15" customHeight="1">
       <c r="A323" s="15" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B323" s="4">
         <v>120</v>
@@ -6584,7 +6620,7 @@
     </row>
     <row r="324" spans="1:4" ht="15" customHeight="1">
       <c r="A324" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B324" s="4">
         <v>139</v>
@@ -6598,7 +6634,7 @@
     </row>
     <row r="325" spans="1:4" ht="15" customHeight="1">
       <c r="A325" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B325" s="4">
         <v>157</v>
@@ -6612,7 +6648,7 @@
     </row>
     <row r="326" spans="1:4" ht="15" customHeight="1">
       <c r="A326" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B326" s="4">
         <v>274</v>
@@ -6626,7 +6662,7 @@
     </row>
     <row r="327" spans="1:4" ht="15" customHeight="1">
       <c r="A327" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B327" s="4">
         <v>225</v>
@@ -6640,7 +6676,7 @@
     </row>
     <row r="328" spans="1:4" ht="15" customHeight="1">
       <c r="A328" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B328" s="4">
         <v>249</v>
@@ -6654,7 +6690,7 @@
     </row>
     <row r="329" spans="1:4" ht="15" customHeight="1">
       <c r="A329" s="15" t="s">
-        <v>103</v>
+        <v>379</v>
       </c>
       <c r="B329" s="5">
         <v>502</v>
@@ -6668,7 +6704,7 @@
     </row>
     <row r="330" spans="1:4" ht="15" customHeight="1">
       <c r="A330" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B330" s="4">
         <v>112</v>
@@ -6682,7 +6718,7 @@
     </row>
     <row r="331" spans="1:4" ht="15" customHeight="1">
       <c r="A331" s="20" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B331" s="4">
         <v>108</v>
@@ -6696,7 +6732,7 @@
     </row>
     <row r="332" spans="1:4" ht="15" customHeight="1">
       <c r="A332" s="20" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B332" s="4">
         <v>126</v>
@@ -6710,7 +6746,7 @@
     </row>
     <row r="333" spans="1:4" ht="15" customHeight="1">
       <c r="A333" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B333" s="5">
         <v>1390</v>
@@ -6724,7 +6760,7 @@
     </row>
     <row r="334" spans="1:4" ht="15" customHeight="1">
       <c r="A334" s="15" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B334" s="4">
         <v>380</v>
@@ -6738,7 +6774,7 @@
     </row>
     <row r="335" spans="1:4" ht="15" customHeight="1">
       <c r="A335" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B335" s="4">
         <v>130</v>
@@ -6752,7 +6788,7 @@
     </row>
     <row r="336" spans="1:4" ht="15" customHeight="1">
       <c r="A336" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B336" s="4">
         <v>103</v>
@@ -6766,7 +6802,7 @@
     </row>
     <row r="337" spans="1:4" ht="15" customHeight="1">
       <c r="A337" s="35" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B337" s="4">
         <v>31</v>
@@ -6775,12 +6811,12 @@
         <v>36</v>
       </c>
       <c r="D337" s="7">
-        <v>-448</v>
+        <v>448</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15" customHeight="1">
       <c r="A338" s="15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B338" s="4">
         <v>260</v>
@@ -6794,7 +6830,7 @@
     </row>
     <row r="339" spans="1:4" ht="15" customHeight="1">
       <c r="A339" s="36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B339" s="4">
         <v>355</v>
@@ -6808,7 +6844,7 @@
     </row>
     <row r="340" spans="1:4" ht="15" customHeight="1">
       <c r="A340" s="36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B340" s="4">
         <v>335</v>
@@ -6822,7 +6858,7 @@
     </row>
     <row r="341" spans="1:4" ht="15" customHeight="1">
       <c r="A341" s="36" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B341" s="4">
         <v>300</v>
@@ -6836,7 +6872,7 @@
     </row>
     <row r="342" spans="1:4" ht="15" customHeight="1">
       <c r="A342" s="36" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B342" s="4">
         <v>348</v>
@@ -6850,7 +6886,7 @@
     </row>
     <row r="343" spans="1:4" ht="15" customHeight="1">
       <c r="A343" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B343" s="4">
         <v>219</v>
@@ -6864,7 +6900,7 @@
     </row>
     <row r="344" spans="1:4" ht="15" customHeight="1">
       <c r="A344" s="33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B344" s="4">
         <v>32</v>
@@ -6873,12 +6909,12 @@
         <v>15</v>
       </c>
       <c r="D344" s="7">
-        <v>-400</v>
+        <v>400</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15" customHeight="1">
       <c r="A345" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B345" s="4">
         <v>70</v>
@@ -6892,7 +6928,7 @@
     </row>
     <row r="346" spans="1:4" ht="15" customHeight="1">
       <c r="A346" s="25" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B346" s="4">
         <v>70</v>
@@ -6906,7 +6942,7 @@
     </row>
     <row r="347" spans="1:4" ht="15" customHeight="1">
       <c r="A347" s="39" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B347" s="4">
         <v>160</v>
@@ -6920,7 +6956,7 @@
     </row>
     <row r="348" spans="1:4" ht="15" customHeight="1">
       <c r="A348" s="39" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B348" s="4">
         <v>120</v>
@@ -6934,7 +6970,7 @@
     </row>
     <row r="349" spans="1:4" ht="15" customHeight="1">
       <c r="A349" s="39" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B349" s="4">
         <v>220</v>
@@ -6948,7 +6984,7 @@
     </row>
     <row r="350" spans="1:4" ht="15" customHeight="1">
       <c r="A350" s="39" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B350" s="4">
         <v>100</v>
@@ -6962,7 +6998,7 @@
     </row>
     <row r="351" spans="1:4" ht="15" customHeight="1">
       <c r="A351" s="39" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B351" s="4">
         <v>200</v>
@@ -6976,7 +7012,7 @@
     </row>
     <row r="352" spans="1:4" ht="15" customHeight="1">
       <c r="A352" s="20" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B352" s="4">
         <v>150</v>
@@ -6990,7 +7026,7 @@
     </row>
     <row r="353" spans="1:4" ht="15" customHeight="1">
       <c r="A353" s="20" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B353" s="4">
         <v>100</v>
@@ -7004,7 +7040,7 @@
     </row>
     <row r="354" spans="1:4" ht="15" customHeight="1">
       <c r="A354" s="20" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B354" s="4">
         <v>100</v>
@@ -7018,7 +7054,7 @@
     </row>
     <row r="355" spans="1:4" ht="15" customHeight="1">
       <c r="A355" s="20" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B355" s="4">
         <v>145</v>
@@ -7032,7 +7068,7 @@
     </row>
     <row r="356" spans="1:4" ht="15" customHeight="1">
       <c r="A356" s="20" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B356" s="4">
         <v>338</v>
@@ -7046,7 +7082,7 @@
     </row>
     <row r="357" spans="1:4" ht="15" customHeight="1">
       <c r="A357" s="20" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B357" s="4">
         <v>209</v>
@@ -7060,7 +7096,7 @@
     </row>
     <row r="358" spans="1:4" ht="15" customHeight="1">
       <c r="A358" s="20" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B358" s="4">
         <v>131</v>
@@ -7074,7 +7110,7 @@
     </row>
     <row r="359" spans="1:4" ht="15" customHeight="1">
       <c r="A359" s="17" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B359" s="4">
         <v>1</v>
@@ -7085,49 +7121,51 @@
       <c r="D359" s="7"/>
     </row>
     <row r="360" spans="1:4" ht="15" customHeight="1">
-      <c r="A360" s="19" t="s">
-        <v>123</v>
+      <c r="A360" s="21" t="s">
+        <v>344</v>
       </c>
       <c r="B360" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C360" s="2">
-        <v>1</v>
-      </c>
-      <c r="D360" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="D360" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="361" spans="1:4" ht="15" customHeight="1">
-      <c r="A361" s="28" t="s">
-        <v>370</v>
+      <c r="A361" s="19" t="s">
+        <v>121</v>
       </c>
       <c r="B361" s="4">
         <v>1</v>
       </c>
       <c r="C361" s="2">
-        <v>15</v>
-      </c>
-      <c r="D361" s="7">
+        <v>1</v>
+      </c>
+      <c r="D361" s="7"/>
+    </row>
+    <row r="362" spans="1:4" ht="15" customHeight="1">
+      <c r="A362" s="28" t="s">
+        <v>362</v>
+      </c>
+      <c r="B362" s="4">
+        <v>1</v>
+      </c>
+      <c r="C362" s="2">
+        <v>12</v>
+      </c>
+      <c r="D362" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="362" spans="1:4" ht="15" customHeight="1">
-      <c r="A362" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="B362" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="C362" s="2">
-        <v>1</v>
-      </c>
-      <c r="D362" s="7"/>
     </row>
     <row r="363" spans="1:4" ht="15" customHeight="1">
       <c r="A363" s="21" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B363" s="4">
-        <v>7.5</v>
+        <v>10.8</v>
       </c>
       <c r="C363" s="2">
         <v>1</v>
@@ -7136,275 +7174,285 @@
     </row>
     <row r="364" spans="1:4" ht="15" customHeight="1">
       <c r="A364" s="21" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B364" s="4">
-        <v>9</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D364" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="C364" s="2">
         <v>1</v>
       </c>
+      <c r="D364" s="7"/>
     </row>
     <row r="365" spans="1:4" ht="15" customHeight="1">
       <c r="A365" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="B365" s="4">
+        <v>9</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D365" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" ht="15" customHeight="1">
+      <c r="A366" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="B365" s="4">
+      <c r="B366" s="4">
+        <v>50</v>
+      </c>
+      <c r="C366" s="2">
+        <v>50</v>
+      </c>
+      <c r="D366" s="7"/>
+    </row>
+    <row r="367" spans="1:4" ht="15" customHeight="1">
+      <c r="A367" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="B367" s="4">
+        <v>10</v>
+      </c>
+      <c r="C367" s="2">
+        <v>100</v>
+      </c>
+      <c r="D367" s="7"/>
+    </row>
+    <row r="368" spans="1:4" ht="15" customHeight="1">
+      <c r="A368" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B368" s="4">
         <v>37</v>
       </c>
-      <c r="C365" s="2">
+      <c r="C368" s="2">
         <v>1</v>
       </c>
-      <c r="D365" s="7">
+      <c r="D368" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="15" customHeight="1">
-      <c r="A366" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="B366" s="4">
+    <row r="369" spans="1:4" ht="15" customHeight="1">
+      <c r="A369" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B369" s="4">
         <v>400</v>
       </c>
-      <c r="C366" s="2">
+      <c r="C369" s="2">
         <v>60</v>
       </c>
-      <c r="D366" s="7">
+      <c r="D369" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="15" customHeight="1">
-      <c r="A367" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="B367" s="4">
+    <row r="370" spans="1:4" ht="15" customHeight="1">
+      <c r="A370" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B370" s="4">
         <v>549</v>
       </c>
-      <c r="C367" s="2">
+      <c r="C370" s="2">
         <v>152</v>
       </c>
-      <c r="D367" s="7">
+      <c r="D370" s="7">
         <v>26</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="15" customHeight="1">
-      <c r="A368" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="B368" s="4">
+    <row r="371" spans="1:4" ht="15" customHeight="1">
+      <c r="A371" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="B371" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="C371" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="D371" s="7"/>
+    </row>
+    <row r="372" spans="1:4" ht="15" customHeight="1">
+      <c r="A372" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="B372" s="4">
         <v>150</v>
       </c>
-      <c r="C368" s="2">
+      <c r="C372" s="2">
         <v>90</v>
       </c>
-      <c r="D368" s="7"/>
-    </row>
-    <row r="369" spans="1:4" ht="15" customHeight="1">
-      <c r="A369" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="B369" s="4">
+      <c r="D372" s="7"/>
+    </row>
+    <row r="373" spans="1:4" ht="15" customHeight="1">
+      <c r="A373" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B373" s="4">
         <v>49</v>
       </c>
-      <c r="C369" s="2">
+      <c r="C373" s="2">
         <v>3</v>
       </c>
-      <c r="D369" s="7">
+      <c r="D373" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="15" customHeight="1">
-      <c r="A370" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="B370" s="4">
+    <row r="374" spans="1:4" ht="15" customHeight="1">
+      <c r="A374" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="B374" s="4">
         <v>80</v>
       </c>
-      <c r="C370" s="2">
+      <c r="C374" s="2">
         <v>35</v>
       </c>
-      <c r="D370" s="7">
+      <c r="D374" s="7">
         <v>4</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" ht="15" customHeight="1">
-      <c r="A371" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="B371" s="4">
-        <v>78</v>
-      </c>
-      <c r="C371" s="2">
-        <v>80</v>
-      </c>
-      <c r="D371" s="7">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4" ht="15" customHeight="1">
-      <c r="A372" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B372" s="4">
-        <v>3</v>
-      </c>
-      <c r="C372" s="2">
-        <v>0</v>
-      </c>
-      <c r="D372" s="7">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4" ht="15" customHeight="1">
-      <c r="A373" s="44" t="s">
-        <v>374</v>
-      </c>
-      <c r="B373" s="4">
-        <v>1.9</v>
-      </c>
-      <c r="C373" s="2">
-        <v>0</v>
-      </c>
-      <c r="D373" s="7">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4" ht="15" customHeight="1">
-      <c r="A374" s="44" t="s">
-        <v>375</v>
-      </c>
-      <c r="B374" s="40">
-        <v>0</v>
-      </c>
-      <c r="C374" s="41">
-        <v>0</v>
-      </c>
-      <c r="D374" s="41">
-        <v>119</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15" customHeight="1">
       <c r="A375" s="21" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B375" s="4">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="C375" s="2">
+        <v>80</v>
+      </c>
+      <c r="D375" s="7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" ht="15" customHeight="1">
+      <c r="A376" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B376" s="4">
         <v>3</v>
       </c>
-      <c r="D375" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="376" spans="1:4" ht="15" customHeight="1">
-      <c r="A376" s="45" t="s">
-        <v>383</v>
-      </c>
-      <c r="B376" s="4">
-        <v>27</v>
-      </c>
       <c r="C376" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D376" s="7">
-        <v>10</v>
+        <v>91</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15" customHeight="1">
-      <c r="A377" s="46" t="s">
-        <v>384</v>
+      <c r="A377" s="47" t="s">
+        <v>366</v>
       </c>
       <c r="B377" s="4">
-        <v>27</v>
+        <v>1.9</v>
       </c>
       <c r="C377" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D377" s="7">
-        <v>5</v>
+        <v>219</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15" customHeight="1">
-      <c r="A378" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="B378" s="4">
-        <v>50</v>
-      </c>
-      <c r="C378" s="2">
-        <v>50</v>
-      </c>
-      <c r="D378" s="7"/>
+      <c r="A378" s="47" t="s">
+        <v>367</v>
+      </c>
+      <c r="B378" s="40">
+        <v>0</v>
+      </c>
+      <c r="C378" s="41">
+        <v>0</v>
+      </c>
+      <c r="D378" s="41">
+        <v>119</v>
+      </c>
     </row>
     <row r="379" spans="1:4" ht="15" customHeight="1">
       <c r="A379" s="21" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B379" s="4">
         <v>10</v>
       </c>
       <c r="C379" s="2">
-        <v>100</v>
-      </c>
-      <c r="D379" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="D379" s="7">
+        <v>14</v>
+      </c>
     </row>
     <row r="380" spans="1:4" ht="15" customHeight="1">
-      <c r="A380" s="21" t="s">
-        <v>352</v>
+      <c r="A380" s="44" t="s">
+        <v>375</v>
       </c>
       <c r="B380" s="4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C380" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D380" s="7">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15" customHeight="1">
-      <c r="A381" s="21" t="s">
-        <v>113</v>
+      <c r="A381" s="45" t="s">
+        <v>376</v>
       </c>
       <c r="B381" s="4">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C381" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D381" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15" customHeight="1">
       <c r="A382" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B382" s="4">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C382" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D382" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15" customHeight="1">
       <c r="A383" s="21" t="s">
-        <v>240</v>
+        <v>113</v>
       </c>
       <c r="B383" s="4">
+        <v>102</v>
+      </c>
+      <c r="C383" s="2">
+        <v>10</v>
+      </c>
+      <c r="D383" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="15" customHeight="1">
+      <c r="A384" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B384" s="4">
         <v>0</v>
       </c>
-      <c r="C383" s="2">
+      <c r="C384" s="2">
         <v>0</v>
       </c>
-      <c r="D383" s="7">
+      <c r="D384" s="7">
         <v>0</v>
       </c>
     </row>
@@ -7432,13 +7480,13 @@
       <formula>2000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B383">
+  <conditionalFormatting sqref="B2:B384">
     <cfRule type="cellIs" dxfId="5" priority="18" operator="between">
       <formula>400</formula>
       <formula>5000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B383">
+  <conditionalFormatting sqref="B1:B384">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="between">
       <formula>100</formula>
       <formula>200</formula>

--- a/KPH-AI.xlsx
+++ b/KPH-AI.xlsx
@@ -3233,7 +3233,7 @@
         <v>239</v>
       </c>
       <c r="B81" s="4">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="C81" s="2">
         <v>140</v>
@@ -3247,7 +3247,7 @@
         <v>240</v>
       </c>
       <c r="B82" s="4">
-        <v>220</v>
+        <v>345</v>
       </c>
       <c r="C82" s="2">
         <v>130</v>

--- a/KPH-AI.xlsx
+++ b/KPH-AI.xlsx
@@ -244,9 +244,6 @@
     <t>Feferoni kiseli</t>
   </si>
   <si>
-    <t>Paradajz ketchup</t>
-  </si>
-  <si>
     <t>Paradajz sok</t>
   </si>
   <si>
@@ -370,18 +367,12 @@
     <t>Cedjeni limun</t>
   </si>
   <si>
-    <t>Grejpfrut  K148-320  P18-20</t>
-  </si>
-  <si>
     <t>Kafa espresso</t>
   </si>
   <si>
     <t>Mineralna voda (San Pelegrino limun)</t>
   </si>
   <si>
-    <t>Guarana - E? Kofein+++, secer+++</t>
-  </si>
-  <si>
     <t>Dimljena kobasica industrijska</t>
   </si>
   <si>
@@ -394,9 +385,6 @@
     <t>Paprika zelena sveza</t>
   </si>
   <si>
-    <t>Ajvar  K250-400  P40-60</t>
-  </si>
-  <si>
     <t>Kiseli kupus - ocedjeno</t>
   </si>
   <si>
@@ -623,9 +611,6 @@
   </si>
   <si>
     <t>Kikiriki przen, soljen</t>
-  </si>
-  <si>
-    <t>Jetrena pasteta Fosfor 200-400 aditivi</t>
   </si>
   <si>
     <t>Virsle</t>
@@ -732,20 +717,6 @@
         <family val="2"/>
       </rPr>
       <t>ne slani</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Boza </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>belo kukuruzno brasno K350, Ph 350 100g 1/10</t>
     </r>
   </si>
   <si>
@@ -1030,9 +1001,6 @@
     <t>Curece jaje</t>
   </si>
   <si>
-    <t>Majonez  +Na</t>
-  </si>
-  <si>
     <t>Senf zuti  +++Na</t>
   </si>
   <si>
@@ -1051,164 +1019,215 @@
     <t>Cips</t>
   </si>
   <si>
+    <t>Lisicarke gljive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sampinjoni gljive gajeni </t>
+  </si>
+  <si>
+    <t>Vrganji gljive</t>
+  </si>
+  <si>
+    <t>Ananas sok –konzerva</t>
+  </si>
+  <si>
+    <t>Krekeri slani (TUC)</t>
+  </si>
+  <si>
+    <t>Secer kristal</t>
+  </si>
+  <si>
+    <t>Cokolada mlecna</t>
+  </si>
+  <si>
+    <t>Zito Celo zrno</t>
+  </si>
+  <si>
+    <t>Krompir kuvan ceo</t>
+  </si>
+  <si>
+    <t>Kesten pire (kuvan)</t>
+  </si>
+  <si>
+    <t>Hleb Psenicni crni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hleb Psenicni polubeli </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hleb Psenicni beli </t>
+  </si>
+  <si>
+    <t>Hleb mesani Psenica + raz</t>
+  </si>
+  <si>
+    <t>Hleb Razani</t>
+  </si>
+  <si>
+    <t>Hleb Graham</t>
+  </si>
+  <si>
+    <t>Hleb Dvopek psenicni</t>
+  </si>
+  <si>
+    <t>Kvas sok</t>
+  </si>
+  <si>
+    <t>Sok Tonic water</t>
+  </si>
+  <si>
+    <t>Spagete</t>
+  </si>
+  <si>
+    <t>Burek sa sirom</t>
+  </si>
+  <si>
+    <t>Burek sa mesom</t>
+  </si>
+  <si>
+    <t>Burek sa jabukama</t>
+  </si>
+  <si>
+    <t>Pita sa visnjama</t>
+  </si>
+  <si>
+    <t>Pita sa spanacem</t>
+  </si>
+  <si>
+    <t>Supa koksija - porcija tanjir 250ml</t>
+  </si>
+  <si>
+    <t>Supa govedja - porcija tanjir 250ml</t>
+  </si>
+  <si>
+    <t>Riba Losos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riba Stuka </t>
+  </si>
+  <si>
+    <t>Hamburger npr. Big Mack Mc.Donalds</t>
+  </si>
+  <si>
+    <t>Sataras - becar paprikas</t>
+  </si>
+  <si>
+    <t>Sok od jabuke 50%</t>
+  </si>
+  <si>
+    <t>Sok od Narandze Orange juice 100% / cedjena</t>
+  </si>
+  <si>
+    <t>Caj biljni + secer</t>
+  </si>
+  <si>
+    <t>Red Bull 0.25 clasic</t>
+  </si>
+  <si>
+    <t>Red Bull 0.25 zeroo</t>
+  </si>
+  <si>
+    <t>Sok narandza bistri/mutni</t>
+  </si>
+  <si>
+    <t>Sok CEDEVITA sa kiselom vodom</t>
+  </si>
+  <si>
+    <t>Sok CEDEVITA sa obicnom vodom</t>
+  </si>
+  <si>
+    <t>Sok Brusnica</t>
+  </si>
+  <si>
+    <t>Sok Borovnica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sok Jagoda </t>
+  </si>
+  <si>
+    <t>Sok Ananas</t>
+  </si>
+  <si>
+    <t>Sok Visnja</t>
+  </si>
+  <si>
+    <t>Sok Malina sirup razreden</t>
+  </si>
+  <si>
+    <t>Sok Grozde</t>
+  </si>
+  <si>
+    <t>Pivo bezalkoholno Heineken 0.0</t>
+  </si>
+  <si>
+    <t>Pivo 5% alk.</t>
+  </si>
+  <si>
+    <t>Sljiva suva</t>
+  </si>
+  <si>
+    <t>Sljiva sveza</t>
+  </si>
+  <si>
+    <t>Kukuruz Celo zrno</t>
+  </si>
+  <si>
+    <t>Kafa Ness + secer</t>
+  </si>
+  <si>
+    <t>Mleko za kafu 100ml</t>
+  </si>
+  <si>
+    <t>Kafa Capuchino + secer</t>
+  </si>
+  <si>
+    <t>Spargla</t>
+  </si>
+  <si>
+    <t>Pomfrit McDonalds npr.</t>
+  </si>
+  <si>
+    <t>Jetrena pasteta - upozorenje na aditive</t>
+  </si>
+  <si>
+    <t>Hamburger klasicni sa prilozima</t>
+  </si>
+  <si>
+    <t>Palacinke kom. Cca 60g prazna</t>
+  </si>
+  <si>
+    <t>Majonez</t>
+  </si>
+  <si>
+    <t>Ajvar</t>
+  </si>
+  <si>
+    <t>Krastavci kiseli  upozorenje na natrijum</t>
+  </si>
+  <si>
+    <t>Masline zel. Marinirane - upozorenje na natrijum</t>
+  </si>
+  <si>
+    <t>Paprika kisela  upozorenje na natrijum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paradajz ketchup </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grejpfrut  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprite, Schwepss </t>
+  </si>
+  <si>
+    <t>Energy Drink Guarana - upozorenje na kofein I secer</t>
+  </si>
+  <si>
+    <t>Coca Cola  upozorenje na fosfor</t>
+  </si>
+  <si>
     <r>
-      <t>Krastavci kiseli  +++</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>Natrium</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Masline zel. Marinirane - +++</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>Natrium</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Paprika kisela  +++</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>Natrium</t>
-    </r>
-  </si>
-  <si>
-    <t>Lisicarke gljive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sampinjoni gljive gajeni </t>
-  </si>
-  <si>
-    <t>Vrganji gljive</t>
-  </si>
-  <si>
-    <t>Ananas sok –konzerva</t>
-  </si>
-  <si>
-    <t>Krekeri slani (TUC)</t>
-  </si>
-  <si>
-    <t>Secer kristal</t>
-  </si>
-  <si>
-    <t>Cokolada mlecna</t>
-  </si>
-  <si>
-    <t>Zito Celo zrno</t>
-  </si>
-  <si>
-    <t>Krompir kuvan ceo</t>
-  </si>
-  <si>
-    <t>Kesten pire (kuvan)</t>
-  </si>
-  <si>
-    <t>Hleb Psenicni crni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hleb Psenicni polubeli </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hleb Psenicni beli </t>
-  </si>
-  <si>
-    <t>Hleb mesani Psenica + raz</t>
-  </si>
-  <si>
-    <t>Hleb Razani</t>
-  </si>
-  <si>
-    <t>Hleb Graham</t>
-  </si>
-  <si>
-    <t>Hleb Dvopek psenicni</t>
-  </si>
-  <si>
-    <t>Sprite, Schwepss + E330 limunska kiselina</t>
-  </si>
-  <si>
-    <t>Kvas sok</t>
-  </si>
-  <si>
-    <t>Sok Tonic water</t>
-  </si>
-  <si>
-    <t>Spagete</t>
-  </si>
-  <si>
-    <t>Burek sa sirom</t>
-  </si>
-  <si>
-    <t>Burek sa mesom</t>
-  </si>
-  <si>
-    <t>Burek sa jabukama</t>
-  </si>
-  <si>
-    <t>Pita sa visnjama</t>
-  </si>
-  <si>
-    <t>Pita sa spanacem</t>
-  </si>
-  <si>
-    <t>Supa koksija - porcija tanjir 250ml</t>
-  </si>
-  <si>
-    <t>Supa govedja - porcija tanjir 250ml</t>
-  </si>
-  <si>
-    <t>Riba Losos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riba Stuka </t>
-  </si>
-  <si>
-    <t>Hamburger npr. Big Mack Mc.Donalds</t>
-  </si>
-  <si>
-    <t>Hamburger klasicni sa prilozima meso pola-pola jun-svinj.</t>
-  </si>
-  <si>
-    <t>Sataras - becar paprikas</t>
-  </si>
-  <si>
-    <t>Palacinke kom. Cca 60g (prazna + fil)</t>
-  </si>
-  <si>
-    <t>Sok od jabuke 50%</t>
-  </si>
-  <si>
-    <t>Sok od Narandze Orange juice 100% / cedjena</t>
-  </si>
-  <si>
-    <t>Caj biljni + secer</t>
-  </si>
-  <si>
-    <r>
-      <t>Coca Cola  +</t>
+      <t xml:space="preserve">Boza </t>
     </r>
     <r>
       <rPr>
@@ -1217,77 +1236,11 @@
         <rFont val="Verdana"/>
         <family val="2"/>
       </rPr>
-      <t>E338!</t>
+      <t xml:space="preserve">belo kukuruzno brasno </t>
     </r>
   </si>
   <si>
-    <t>Red Bull 0.25 clasic</t>
-  </si>
-  <si>
-    <t>Red Bull 0.25 zeroo</t>
-  </si>
-  <si>
-    <t>Sok narandza bistri/mutni</t>
-  </si>
-  <si>
-    <t>Sok CEDEVITA sa kiselom vodom</t>
-  </si>
-  <si>
-    <t>Sok CEDEVITA sa obicnom vodom</t>
-  </si>
-  <si>
-    <t>Sok Brusnica</t>
-  </si>
-  <si>
-    <t>Sok Borovnica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sok Jagoda </t>
-  </si>
-  <si>
-    <t>Sok Ananas</t>
-  </si>
-  <si>
-    <t>Sok Visnja</t>
-  </si>
-  <si>
-    <t>Sok Malina sirup razreden</t>
-  </si>
-  <si>
-    <t>Sok Grozde</t>
-  </si>
-  <si>
-    <t>Pivo bezalkoholno Heineken 0.0</t>
-  </si>
-  <si>
-    <t>Pivo 5% alk.</t>
-  </si>
-  <si>
-    <t>Sljiva suva</t>
-  </si>
-  <si>
-    <t>Sljiva sveza</t>
-  </si>
-  <si>
-    <t>Kukuruz Celo zrno</t>
-  </si>
-  <si>
-    <t>Kafa Ness + secer</t>
-  </si>
-  <si>
-    <t>Mleko za kafu porcija 5ml</t>
-  </si>
-  <si>
-    <t>Mleko za kafu 100ml</t>
-  </si>
-  <si>
-    <t>Kafa Capuchino + secer</t>
-  </si>
-  <si>
-    <t>Spargla</t>
-  </si>
-  <si>
-    <t>Pomfrit McDonalds npr.</t>
+    <t>Mleko za kafu porcija 10ml</t>
   </si>
 </sst>
 </file>
@@ -2124,7 +2077,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B2" s="4">
         <v>300</v>
@@ -2138,7 +2091,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="15" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B3" s="4">
         <v>245</v>
@@ -2152,7 +2105,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B4" s="4">
         <v>360</v>
@@ -2166,7 +2119,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="15" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B5" s="4">
         <v>330</v>
@@ -2180,7 +2133,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="15" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B6" s="4">
         <v>240</v>
@@ -2194,7 +2147,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="15" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B7" s="4">
         <v>340</v>
@@ -2208,7 +2161,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="15" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B8" s="4">
         <v>340</v>
@@ -2222,7 +2175,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="15" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B9" s="4">
         <v>320</v>
@@ -2236,7 +2189,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="17" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B10" s="4">
         <v>150</v>
@@ -2250,7 +2203,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="17" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B11" s="4">
         <v>125</v>
@@ -2264,7 +2217,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="17" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="B12" s="4">
         <v>290</v>
@@ -2278,7 +2231,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="15" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B13" s="4">
         <v>370</v>
@@ -2292,7 +2245,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B14" s="4">
         <v>331</v>
@@ -2306,7 +2259,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="15" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B15" s="4">
         <v>220</v>
@@ -2320,7 +2273,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="15" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B16" s="4">
         <v>289</v>
@@ -2334,7 +2287,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B17" s="4">
         <v>220</v>
@@ -2348,7 +2301,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B18" s="4">
         <v>230</v>
@@ -2362,7 +2315,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="15" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B19" s="4">
         <v>210</v>
@@ -2376,7 +2329,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="15" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B20" s="4">
         <v>220</v>
@@ -2390,7 +2343,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B21" s="4">
         <v>300</v>
@@ -2404,7 +2357,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B22" s="4">
         <v>289</v>
@@ -2418,7 +2371,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="15" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B23" s="4">
         <v>333</v>
@@ -2432,7 +2385,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="15" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B24" s="4">
         <v>315</v>
@@ -2446,7 +2399,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B25" s="4">
         <v>220</v>
@@ -2488,7 +2441,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="15" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B28" s="4">
         <v>310</v>
@@ -2502,7 +2455,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B29" s="4">
         <v>301</v>
@@ -2530,7 +2483,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="15" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B31" s="4">
         <v>218</v>
@@ -2544,7 +2497,7 @@
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B32" s="4">
         <v>292</v>
@@ -2558,7 +2511,7 @@
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B33" s="4">
         <v>290</v>
@@ -2586,7 +2539,7 @@
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1">
       <c r="A35" s="15" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B35" s="4">
         <v>310</v>
@@ -2600,7 +2553,7 @@
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1">
       <c r="A36" s="15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B36" s="4">
         <v>255</v>
@@ -2642,7 +2595,7 @@
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1">
       <c r="A39" s="15" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B39" s="4">
         <v>281</v>
@@ -2656,7 +2609,7 @@
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1">
       <c r="A40" s="15" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B40" s="4">
         <v>320</v>
@@ -2670,7 +2623,7 @@
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1">
       <c r="A41" s="15" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B41" s="4">
         <v>248</v>
@@ -2684,7 +2637,7 @@
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1">
       <c r="A42" s="15" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B42" s="4">
         <v>262</v>
@@ -2712,7 +2665,7 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1">
       <c r="A44" s="15" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B44" s="4">
         <v>265</v>
@@ -2726,7 +2679,7 @@
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1">
       <c r="A45" s="15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B45" s="4">
         <v>177</v>
@@ -2740,7 +2693,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="31" t="s">
-        <v>203</v>
+        <v>371</v>
       </c>
       <c r="B46" s="4">
         <v>173</v>
@@ -2754,7 +2707,7 @@
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1">
       <c r="A47" s="19" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B47" s="4">
         <v>263</v>
@@ -2768,7 +2721,7 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1">
       <c r="A48" s="15" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B48" s="4">
         <v>200</v>
@@ -2782,7 +2735,7 @@
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1">
       <c r="A49" s="15" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B49" s="4">
         <v>207</v>
@@ -2838,7 +2791,7 @@
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1">
       <c r="A53" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B53" s="5">
         <v>400</v>
@@ -2852,7 +2805,7 @@
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1">
       <c r="A54" s="15" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B54" s="4">
         <v>285</v>
@@ -2866,7 +2819,7 @@
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1">
       <c r="A55" s="15" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B55" s="4">
         <v>310</v>
@@ -2894,7 +2847,7 @@
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B57" s="4">
         <v>204</v>
@@ -2908,7 +2861,7 @@
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1">
       <c r="A58" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B58" s="4">
         <v>377</v>
@@ -2922,7 +2875,7 @@
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1">
       <c r="A59" s="20" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B59" s="4">
         <v>800</v>
@@ -2936,7 +2889,7 @@
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1">
       <c r="A60" s="21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B60" s="4">
         <v>115</v>
@@ -2950,7 +2903,7 @@
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1">
       <c r="A61" s="19" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B61" s="4">
         <v>180</v>
@@ -2964,7 +2917,7 @@
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1">
       <c r="A62" s="20" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B62" s="4">
         <v>300</v>
@@ -2978,7 +2931,7 @@
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1">
       <c r="A63" s="20" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B63" s="4">
         <v>190</v>
@@ -3006,7 +2959,7 @@
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1">
       <c r="A65" s="20" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B65" s="4">
         <v>200</v>
@@ -3020,7 +2973,7 @@
     </row>
     <row r="66" spans="1:4" ht="15" customHeight="1">
       <c r="A66" s="15" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B66" s="4">
         <v>335</v>
@@ -3034,7 +2987,7 @@
     </row>
     <row r="67" spans="1:4" ht="15" customHeight="1">
       <c r="A67" s="19" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B67" s="4">
         <v>210</v>
@@ -3048,7 +3001,7 @@
     </row>
     <row r="68" spans="1:4" ht="15" customHeight="1">
       <c r="A68" s="15" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B68" s="4">
         <v>329</v>
@@ -3062,7 +3015,7 @@
     </row>
     <row r="69" spans="1:4" ht="15" customHeight="1">
       <c r="A69" s="15" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="B69" s="4">
         <v>192</v>
@@ -3076,7 +3029,7 @@
     </row>
     <row r="70" spans="1:4" ht="15" customHeight="1">
       <c r="A70" s="15" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="B70" s="4">
         <v>260</v>
@@ -3090,7 +3043,7 @@
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1">
       <c r="A71" s="15" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B71" s="4">
         <v>313</v>
@@ -3104,7 +3057,7 @@
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1">
       <c r="A72" s="15" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B72" s="4">
         <v>194</v>
@@ -3118,7 +3071,7 @@
     </row>
     <row r="73" spans="1:4" ht="15" customHeight="1">
       <c r="A73" s="15" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B73" s="4">
         <v>275</v>
@@ -3132,7 +3085,7 @@
     </row>
     <row r="74" spans="1:4" ht="15" customHeight="1">
       <c r="A74" s="15" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B74" s="4">
         <v>405</v>
@@ -3146,7 +3099,7 @@
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1">
       <c r="A75" s="21" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B75" s="4">
         <v>133</v>
@@ -3160,7 +3113,7 @@
     </row>
     <row r="76" spans="1:4" ht="15" customHeight="1">
       <c r="A76" s="20" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B76" s="4">
         <v>204</v>
@@ -3188,7 +3141,7 @@
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1">
       <c r="A78" s="20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B78" s="4">
         <v>280</v>
@@ -3202,7 +3155,7 @@
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1">
       <c r="A79" s="20" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B79" s="4">
         <v>245</v>
@@ -3216,7 +3169,7 @@
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1">
       <c r="A80" s="20" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B80" s="4">
         <v>280</v>
@@ -3230,7 +3183,7 @@
     </row>
     <row r="81" spans="1:4" ht="15" customHeight="1">
       <c r="A81" s="38" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B81" s="4">
         <v>300</v>
@@ -3244,7 +3197,7 @@
     </row>
     <row r="82" spans="1:4" ht="15" customHeight="1">
       <c r="A82" s="38" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B82" s="4">
         <v>345</v>
@@ -3258,7 +3211,7 @@
     </row>
     <row r="83" spans="1:4" ht="15" customHeight="1">
       <c r="A83" s="15" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B83" s="4">
         <v>330</v>
@@ -3272,7 +3225,7 @@
     </row>
     <row r="84" spans="1:4" ht="15" customHeight="1">
       <c r="A84" s="15" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B84" s="4">
         <v>362</v>
@@ -3286,7 +3239,7 @@
     </row>
     <row r="85" spans="1:4" ht="15" customHeight="1">
       <c r="A85" s="15" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B85" s="4">
         <v>340</v>
@@ -3300,7 +3253,7 @@
     </row>
     <row r="86" spans="1:4" ht="15" customHeight="1">
       <c r="A86" s="15" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B86" s="4">
         <v>250</v>
@@ -3314,7 +3267,7 @@
     </row>
     <row r="87" spans="1:4" ht="15" customHeight="1">
       <c r="A87" s="15" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B87" s="4">
         <v>371</v>
@@ -3384,7 +3337,7 @@
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1">
       <c r="A92" s="15" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B92" s="4">
         <v>310</v>
@@ -3412,7 +3365,7 @@
     </row>
     <row r="94" spans="1:4" ht="15" customHeight="1">
       <c r="A94" s="15" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B94" s="5">
         <v>439</v>
@@ -3426,7 +3379,7 @@
     </row>
     <row r="95" spans="1:4" ht="15" customHeight="1">
       <c r="A95" s="15" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B95" s="4">
         <v>328</v>
@@ -3440,7 +3393,7 @@
     </row>
     <row r="96" spans="1:4" ht="15" customHeight="1">
       <c r="A96" s="15" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B96" s="4">
         <v>400</v>
@@ -3452,7 +3405,7 @@
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
       <c r="A97" s="15" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B97" s="4">
         <v>294</v>
@@ -3466,7 +3419,7 @@
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
       <c r="A98" s="15" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B98" s="4">
         <v>396</v>
@@ -3480,7 +3433,7 @@
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
       <c r="A99" s="15" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B99" s="4">
         <v>324</v>
@@ -3494,7 +3447,7 @@
     </row>
     <row r="100" spans="1:4" ht="15" customHeight="1">
       <c r="A100" s="15" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B100" s="4">
         <v>330</v>
@@ -3508,7 +3461,7 @@
     </row>
     <row r="101" spans="1:4" ht="15" customHeight="1">
       <c r="A101" s="15" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B101" s="4">
         <v>441</v>
@@ -3522,7 +3475,7 @@
     </row>
     <row r="102" spans="1:4" ht="15" customHeight="1">
       <c r="A102" s="15" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="B102" s="4">
         <v>630</v>
@@ -3534,7 +3487,7 @@
     </row>
     <row r="103" spans="1:4" ht="15" customHeight="1">
       <c r="A103" s="15" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="B103" s="4">
         <v>400</v>
@@ -3546,7 +3499,7 @@
     </row>
     <row r="104" spans="1:4" ht="15" customHeight="1">
       <c r="A104" s="15" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B104" s="4">
         <v>299</v>
@@ -3560,7 +3513,7 @@
     </row>
     <row r="105" spans="1:4" ht="15" customHeight="1">
       <c r="A105" s="15" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B105" s="4">
         <v>306</v>
@@ -3574,7 +3527,7 @@
     </row>
     <row r="106" spans="1:4" ht="15" customHeight="1">
       <c r="A106" s="15" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B106" s="4">
         <v>349</v>
@@ -3588,7 +3541,7 @@
     </row>
     <row r="107" spans="1:4" ht="15" customHeight="1">
       <c r="A107" s="15" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B107" s="4">
         <v>340</v>
@@ -3602,7 +3555,7 @@
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
       <c r="A108" s="15" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B108" s="5">
         <v>427</v>
@@ -3616,7 +3569,7 @@
     </row>
     <row r="109" spans="1:4" ht="15" customHeight="1">
       <c r="A109" s="15" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B109" s="4">
         <v>268</v>
@@ -3630,7 +3583,7 @@
     </row>
     <row r="110" spans="1:4" ht="15" customHeight="1">
       <c r="A110" s="15" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B110" s="4">
         <v>352</v>
@@ -3644,7 +3597,7 @@
     </row>
     <row r="111" spans="1:4" ht="15" customHeight="1">
       <c r="A111" s="22" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B111" s="4">
         <v>168</v>
@@ -3658,7 +3611,7 @@
     </row>
     <row r="112" spans="1:4" ht="15" customHeight="1">
       <c r="A112" s="22" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B112" s="4">
         <v>182</v>
@@ -3672,7 +3625,7 @@
     </row>
     <row r="113" spans="1:4" ht="15" customHeight="1">
       <c r="A113" s="15" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B113" s="5">
         <v>637</v>
@@ -3686,7 +3639,7 @@
     </row>
     <row r="114" spans="1:4" ht="15" customHeight="1">
       <c r="A114" s="23" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B114" s="5">
         <v>351</v>
@@ -3714,7 +3667,7 @@
     </row>
     <row r="116" spans="1:4" ht="15" customHeight="1">
       <c r="A116" s="15" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B116" s="5">
         <v>430</v>
@@ -3728,7 +3681,7 @@
     </row>
     <row r="117" spans="1:4" ht="15" customHeight="1">
       <c r="A117" s="15" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B117" s="4">
         <v>267</v>
@@ -3742,7 +3695,7 @@
     </row>
     <row r="118" spans="1:4" ht="15" customHeight="1">
       <c r="A118" s="15" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B118" s="4">
         <v>280</v>
@@ -3756,7 +3709,7 @@
     </row>
     <row r="119" spans="1:4" ht="15" customHeight="1">
       <c r="A119" s="19" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B119" s="4">
         <v>149</v>
@@ -3770,7 +3723,7 @@
     </row>
     <row r="120" spans="1:4" ht="15" customHeight="1">
       <c r="A120" s="19" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B120" s="4">
         <v>158</v>
@@ -3784,7 +3737,7 @@
     </row>
     <row r="121" spans="1:4" ht="15" customHeight="1">
       <c r="A121" s="20" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B121" s="4">
         <v>205</v>
@@ -3798,7 +3751,7 @@
     </row>
     <row r="122" spans="1:4" ht="15" customHeight="1">
       <c r="A122" s="19" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B122" s="4">
         <v>158</v>
@@ -3812,7 +3765,7 @@
     </row>
     <row r="123" spans="1:4" ht="15" customHeight="1">
       <c r="A123" s="15" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B123" s="4">
         <v>136</v>
@@ -3868,7 +3821,7 @@
     </row>
     <row r="127" spans="1:4" ht="15" customHeight="1">
       <c r="A127" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B127" s="4">
         <v>167</v>
@@ -3896,7 +3849,7 @@
     </row>
     <row r="129" spans="1:4" ht="15" customHeight="1">
       <c r="A129" s="20" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B129" s="4">
         <v>170</v>
@@ -3966,7 +3919,7 @@
     </row>
     <row r="134" spans="1:4" ht="15" customHeight="1">
       <c r="A134" s="20" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="B134" s="4">
         <v>150</v>
@@ -3994,7 +3947,7 @@
     </row>
     <row r="136" spans="1:4" ht="15" customHeight="1">
       <c r="A136" s="15" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B136" s="4">
         <v>132</v>
@@ -4008,7 +3961,7 @@
     </row>
     <row r="137" spans="1:4" ht="15" customHeight="1">
       <c r="A137" s="15" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B137" s="4">
         <v>120</v>
@@ -4022,7 +3975,7 @@
     </row>
     <row r="138" spans="1:4" ht="15" customHeight="1">
       <c r="A138" s="15" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B138" s="4">
         <v>102</v>
@@ -4036,7 +3989,7 @@
     </row>
     <row r="139" spans="1:4" ht="15" customHeight="1">
       <c r="A139" s="15" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B139" s="4">
         <v>95</v>
@@ -4050,7 +4003,7 @@
     </row>
     <row r="140" spans="1:4" ht="15" customHeight="1">
       <c r="A140" s="15" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B140" s="4">
         <v>87</v>
@@ -4064,7 +4017,7 @@
     </row>
     <row r="141" spans="1:4" ht="15" customHeight="1">
       <c r="A141" s="15" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B141" s="4">
         <v>107</v>
@@ -4078,7 +4031,7 @@
     </row>
     <row r="142" spans="1:4" ht="15" customHeight="1">
       <c r="A142" s="15" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B142" s="4">
         <v>62</v>
@@ -4092,7 +4045,7 @@
     </row>
     <row r="143" spans="1:4" ht="15" customHeight="1">
       <c r="A143" s="15" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B143" s="4">
         <v>76</v>
@@ -4106,7 +4059,7 @@
     </row>
     <row r="144" spans="1:4" ht="15" customHeight="1">
       <c r="A144" s="15" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B144" s="4">
         <v>123</v>
@@ -4120,7 +4073,7 @@
     </row>
     <row r="145" spans="1:4" ht="15" customHeight="1">
       <c r="A145" s="15" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B145" s="4">
         <v>81</v>
@@ -4134,7 +4087,7 @@
     </row>
     <row r="146" spans="1:4" ht="15" customHeight="1">
       <c r="A146" s="15" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B146" s="4">
         <v>128</v>
@@ -4148,7 +4101,7 @@
     </row>
     <row r="147" spans="1:4" ht="15" customHeight="1">
       <c r="A147" s="20" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B147" s="4">
         <v>38</v>
@@ -4176,7 +4129,7 @@
     </row>
     <row r="149" spans="1:4" ht="15" customHeight="1">
       <c r="A149" s="20" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B149" s="4">
         <v>95</v>
@@ -4190,7 +4143,7 @@
     </row>
     <row r="150" spans="1:4" ht="15" customHeight="1">
       <c r="A150" s="20" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B150" s="4">
         <v>190</v>
@@ -4204,7 +4157,7 @@
     </row>
     <row r="151" spans="1:4" ht="15" customHeight="1">
       <c r="A151" s="20" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B151" s="4">
         <v>190</v>
@@ -4218,7 +4171,7 @@
     </row>
     <row r="152" spans="1:4" ht="15" customHeight="1">
       <c r="A152" s="20" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B152" s="4">
         <v>149</v>
@@ -4232,7 +4185,7 @@
     </row>
     <row r="153" spans="1:4" ht="15" customHeight="1">
       <c r="A153" s="20" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B153" s="4">
         <v>147</v>
@@ -4246,7 +4199,7 @@
     </row>
     <row r="154" spans="1:4" ht="15" customHeight="1">
       <c r="A154" s="15" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B154" s="4">
         <v>130</v>
@@ -4260,7 +4213,7 @@
     </row>
     <row r="155" spans="1:4" ht="15" customHeight="1">
       <c r="A155" s="15" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B155" s="4">
         <v>210</v>
@@ -4274,7 +4227,7 @@
     </row>
     <row r="156" spans="1:4" ht="15" customHeight="1">
       <c r="A156" s="15" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B156" s="4">
         <v>233</v>
@@ -4288,7 +4241,7 @@
     </row>
     <row r="157" spans="1:4" ht="15" customHeight="1">
       <c r="A157" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B157" s="4">
         <v>132</v>
@@ -4302,7 +4255,7 @@
     </row>
     <row r="158" spans="1:4" ht="15" customHeight="1">
       <c r="A158" s="16" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B158" s="6">
         <v>142</v>
@@ -4375,32 +4328,32 @@
         <v>43</v>
       </c>
       <c r="B163" s="12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C163" s="13">
         <v>0</v>
       </c>
       <c r="D163" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15" customHeight="1">
-      <c r="A164" s="21" t="s">
-        <v>315</v>
+      <c r="A164" s="20" t="s">
+        <v>374</v>
       </c>
       <c r="B164" s="12">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C164" s="2">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D164" s="7">
-        <v>568</v>
+        <v>600</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15" customHeight="1">
       <c r="A165" s="20" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B165" s="4">
         <v>130</v>
@@ -4414,7 +4367,7 @@
     </row>
     <row r="166" spans="1:4" ht="15" customHeight="1">
       <c r="A166" s="15" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B166" s="5">
         <v>570</v>
@@ -4428,7 +4381,7 @@
     </row>
     <row r="167" spans="1:4" ht="15" customHeight="1">
       <c r="A167" s="15" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B167" s="4">
         <v>310</v>
@@ -4442,7 +4395,7 @@
     </row>
     <row r="168" spans="1:4" ht="15" customHeight="1">
       <c r="A168" s="15" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B168" s="5">
         <v>455</v>
@@ -4456,7 +4409,7 @@
     </row>
     <row r="169" spans="1:4" ht="15" customHeight="1">
       <c r="A169" s="15" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B169" s="4">
         <v>350</v>
@@ -4470,7 +4423,7 @@
     </row>
     <row r="170" spans="1:4" ht="15" customHeight="1">
       <c r="A170" s="18" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B170" s="5">
         <v>500</v>
@@ -4484,7 +4437,7 @@
     </row>
     <row r="171" spans="1:4" ht="15" customHeight="1">
       <c r="A171" s="18" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="B171" s="5">
         <v>460</v>
@@ -4498,7 +4451,7 @@
     </row>
     <row r="172" spans="1:4" ht="15" customHeight="1">
       <c r="A172" s="18" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B172" s="5">
         <v>1275</v>
@@ -4512,7 +4465,7 @@
     </row>
     <row r="173" spans="1:4" ht="15" customHeight="1">
       <c r="A173" s="15" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B173" s="4">
         <v>376</v>
@@ -4624,7 +4577,7 @@
     </row>
     <row r="181" spans="1:4" ht="15" customHeight="1">
       <c r="A181" s="15" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B181" s="4">
         <v>288</v>
@@ -4652,7 +4605,7 @@
     </row>
     <row r="183" spans="1:4" ht="15" customHeight="1">
       <c r="A183" s="15" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B183" s="4">
         <v>399</v>
@@ -4666,7 +4619,7 @@
     </row>
     <row r="184" spans="1:4" ht="15" customHeight="1">
       <c r="A184" s="26" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B184" s="5">
         <v>1000</v>
@@ -4694,7 +4647,7 @@
     </row>
     <row r="186" spans="1:4" ht="15" customHeight="1">
       <c r="A186" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B186" s="4">
         <v>322</v>
@@ -4750,7 +4703,7 @@
     </row>
     <row r="190" spans="1:4" ht="15" customHeight="1">
       <c r="A190" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B190" s="5">
         <v>633</v>
@@ -4834,7 +4787,7 @@
     </row>
     <row r="196" spans="1:4" ht="15" customHeight="1">
       <c r="A196" s="20" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B196" s="4">
         <v>315</v>
@@ -4904,7 +4857,7 @@
     </row>
     <row r="201" spans="1:4" ht="15" customHeight="1">
       <c r="A201" s="15" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="B201" s="4">
         <v>210</v>
@@ -4918,7 +4871,7 @@
     </row>
     <row r="202" spans="1:4" ht="15" customHeight="1">
       <c r="A202" s="15" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="B202" s="4">
         <v>180</v>
@@ -4946,7 +4899,7 @@
     </row>
     <row r="204" spans="1:4" ht="15" customHeight="1">
       <c r="A204" s="15" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B204" s="4">
         <v>550</v>
@@ -4960,7 +4913,7 @@
     </row>
     <row r="205" spans="1:4" ht="15" customHeight="1">
       <c r="A205" s="15" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B205" s="4">
         <v>340</v>
@@ -4974,7 +4927,7 @@
     </row>
     <row r="206" spans="1:4" ht="15" customHeight="1">
       <c r="A206" s="15" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B206" s="4">
         <v>250</v>
@@ -5030,7 +4983,7 @@
     </row>
     <row r="210" spans="1:4" ht="15" customHeight="1">
       <c r="A210" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B210" s="4">
         <v>121</v>
@@ -5044,7 +4997,7 @@
     </row>
     <row r="211" spans="1:4" ht="15" customHeight="1">
       <c r="A211" s="24" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B211" s="5">
         <v>1660</v>
@@ -5072,7 +5025,7 @@
     </row>
     <row r="213" spans="1:4" ht="15" customHeight="1">
       <c r="A213" s="27" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B213" s="4">
         <v>140</v>
@@ -5100,7 +5053,7 @@
     </row>
     <row r="215" spans="1:4" ht="15" customHeight="1">
       <c r="A215" s="20" t="s">
-        <v>126</v>
+        <v>375</v>
       </c>
       <c r="B215" s="4">
         <v>320</v>
@@ -5128,7 +5081,7 @@
     </row>
     <row r="217" spans="1:4" ht="15" customHeight="1">
       <c r="A217" s="28" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B217" s="5">
         <v>3170</v>
@@ -5142,7 +5095,7 @@
     </row>
     <row r="218" spans="1:4" ht="15" customHeight="1">
       <c r="A218" s="29" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B218" s="4">
         <v>129</v>
@@ -5156,7 +5109,7 @@
     </row>
     <row r="219" spans="1:4" ht="15" customHeight="1">
       <c r="A219" s="29" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B219" s="4">
         <v>176</v>
@@ -5170,7 +5123,7 @@
     </row>
     <row r="220" spans="1:4" ht="15" customHeight="1">
       <c r="A220" s="20" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B220" s="4">
         <v>305</v>
@@ -5184,7 +5137,7 @@
     </row>
     <row r="221" spans="1:4" ht="15" customHeight="1">
       <c r="A221" s="20" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B221" s="4">
         <v>275</v>
@@ -5198,7 +5151,7 @@
     </row>
     <row r="222" spans="1:4" ht="15" customHeight="1">
       <c r="A222" s="20" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="B222" s="4">
         <v>207</v>
@@ -5296,7 +5249,7 @@
     </row>
     <row r="229" spans="1:4" ht="15" customHeight="1">
       <c r="A229" s="20" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>10</v>
@@ -5310,7 +5263,7 @@
     </row>
     <row r="230" spans="1:4" ht="15" customHeight="1">
       <c r="A230" s="20" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B230" s="4">
         <v>140</v>
@@ -5324,7 +5277,7 @@
     </row>
     <row r="231" spans="1:4" ht="15" customHeight="1">
       <c r="A231" s="20" t="s">
-        <v>323</v>
+        <v>377</v>
       </c>
       <c r="B231" s="4">
         <v>43</v>
@@ -5338,7 +5291,7 @@
     </row>
     <row r="232" spans="1:4" ht="15" customHeight="1">
       <c r="A232" s="20" t="s">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="B232" s="4">
         <v>131</v>
@@ -5352,7 +5305,7 @@
     </row>
     <row r="233" spans="1:4" ht="15" customHeight="1">
       <c r="A233" s="30" t="s">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="B233" s="5">
         <v>800</v>
@@ -5366,7 +5319,7 @@
     </row>
     <row r="234" spans="1:4" ht="15" customHeight="1">
       <c r="A234" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B234" s="4">
         <v>220</v>
@@ -5380,7 +5333,7 @@
     </row>
     <row r="235" spans="1:4" ht="15" customHeight="1">
       <c r="A235" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B235" s="5">
         <v>1000</v>
@@ -5394,7 +5347,7 @@
     </row>
     <row r="236" spans="1:4" ht="15" customHeight="1">
       <c r="A236" s="15" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B236" s="5">
         <v>450</v>
@@ -5408,7 +5361,7 @@
     </row>
     <row r="237" spans="1:4" ht="15" customHeight="1">
       <c r="A237" s="15" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B237" s="5">
         <v>422</v>
@@ -5422,7 +5375,7 @@
     </row>
     <row r="238" spans="1:4" ht="15" customHeight="1">
       <c r="A238" s="15" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B238" s="4">
         <v>346</v>
@@ -5436,7 +5389,7 @@
     </row>
     <row r="239" spans="1:4" ht="15" customHeight="1">
       <c r="A239" s="20" t="s">
-        <v>118</v>
+        <v>380</v>
       </c>
       <c r="B239" s="4">
         <v>277</v>
@@ -5450,7 +5403,7 @@
     </row>
     <row r="240" spans="1:4" ht="15" customHeight="1">
       <c r="A240" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B240" s="4">
         <v>149</v>
@@ -5464,7 +5417,7 @@
     </row>
     <row r="241" spans="1:4" ht="15" customHeight="1">
       <c r="A241" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B241" s="4">
         <v>210</v>
@@ -5478,7 +5431,7 @@
     </row>
     <row r="242" spans="1:4" ht="15" customHeight="1">
       <c r="A242" s="20" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B242" s="4">
         <v>260</v>
@@ -5492,7 +5445,7 @@
     </row>
     <row r="243" spans="1:4" ht="15" customHeight="1">
       <c r="A243" s="20" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B243" s="4">
         <v>177</v>
@@ -5506,7 +5459,7 @@
     </row>
     <row r="244" spans="1:4" ht="15" customHeight="1">
       <c r="A244" s="21" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B244" s="4">
         <v>81</v>
@@ -5520,7 +5473,7 @@
     </row>
     <row r="245" spans="1:4" ht="15" customHeight="1">
       <c r="A245" s="24" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B245" s="5">
         <v>782</v>
@@ -5534,7 +5487,7 @@
     </row>
     <row r="246" spans="1:4" ht="15" customHeight="1">
       <c r="A246" s="20" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B246" s="4">
         <v>192</v>
@@ -5548,7 +5501,7 @@
     </row>
     <row r="247" spans="1:4" ht="15" customHeight="1">
       <c r="A247" s="20" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B247" s="4">
         <v>147</v>
@@ -5562,7 +5515,7 @@
     </row>
     <row r="248" spans="1:4" ht="15" customHeight="1">
       <c r="A248" s="20" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B248" s="4">
         <v>170</v>
@@ -5576,7 +5529,7 @@
     </row>
     <row r="249" spans="1:4" ht="15" customHeight="1">
       <c r="A249" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B249" s="4">
         <v>310</v>
@@ -5590,7 +5543,7 @@
     </row>
     <row r="250" spans="1:4" ht="15" customHeight="1">
       <c r="A250" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B250" s="4">
         <v>238</v>
@@ -5604,7 +5557,7 @@
     </row>
     <row r="251" spans="1:4" ht="15" customHeight="1">
       <c r="A251" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B251" s="4">
         <v>114</v>
@@ -5616,7 +5569,7 @@
     </row>
     <row r="252" spans="1:4" ht="15" customHeight="1">
       <c r="A252" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B252" s="4">
         <v>144</v>
@@ -5630,7 +5583,7 @@
     </row>
     <row r="253" spans="1:4" ht="15" customHeight="1">
       <c r="A253" s="29" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B253" s="4">
         <v>126</v>
@@ -5644,7 +5597,7 @@
     </row>
     <row r="254" spans="1:4" ht="15" customHeight="1">
       <c r="A254" s="31" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B254" s="5">
         <v>1340</v>
@@ -5658,7 +5611,7 @@
     </row>
     <row r="255" spans="1:4" ht="15" customHeight="1">
       <c r="A255" s="20" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B255" s="4">
         <v>205</v>
@@ -5672,7 +5625,7 @@
     </row>
     <row r="256" spans="1:4" ht="15" customHeight="1">
       <c r="A256" s="32" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B256" s="5">
         <v>1370</v>
@@ -5686,7 +5639,7 @@
     </row>
     <row r="257" spans="1:4" ht="15" customHeight="1">
       <c r="A257" s="20" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B257" s="4">
         <v>278</v>
@@ -5700,7 +5653,7 @@
     </row>
     <row r="258" spans="1:4" ht="15" customHeight="1">
       <c r="A258" s="31" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="B258" s="5">
         <v>860</v>
@@ -5714,7 +5667,7 @@
     </row>
     <row r="259" spans="1:4" ht="15" customHeight="1">
       <c r="A259" s="20" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B259" s="4">
         <v>221</v>
@@ -5728,7 +5681,7 @@
     </row>
     <row r="260" spans="1:4" ht="15" customHeight="1">
       <c r="A260" s="20" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B260" s="4">
         <v>229</v>
@@ -5742,7 +5695,7 @@
     </row>
     <row r="261" spans="1:4" ht="15" customHeight="1">
       <c r="A261" s="20" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B261" s="4">
         <v>191</v>
@@ -5756,7 +5709,7 @@
     </row>
     <row r="262" spans="1:4" ht="15" customHeight="1">
       <c r="A262" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B262" s="4">
         <v>173</v>
@@ -5770,7 +5723,7 @@
     </row>
     <row r="263" spans="1:4" ht="15" customHeight="1">
       <c r="A263" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B263" s="5">
         <v>503</v>
@@ -5784,7 +5737,7 @@
     </row>
     <row r="264" spans="1:4" ht="15" customHeight="1">
       <c r="A264" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B264" s="4">
         <v>393</v>
@@ -5798,7 +5751,7 @@
     </row>
     <row r="265" spans="1:4" ht="15" customHeight="1">
       <c r="A265" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B265" s="4">
         <v>295</v>
@@ -5812,7 +5765,7 @@
     </row>
     <row r="266" spans="1:4" ht="15" customHeight="1">
       <c r="A266" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B266" s="4">
         <v>190</v>
@@ -5840,7 +5793,7 @@
     </row>
     <row r="268" spans="1:4" ht="15" customHeight="1">
       <c r="A268" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B268" s="4">
         <v>158</v>
@@ -5854,7 +5807,7 @@
     </row>
     <row r="269" spans="1:4" ht="15" customHeight="1">
       <c r="A269" s="20" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B269" s="4">
         <v>240</v>
@@ -5868,7 +5821,7 @@
     </row>
     <row r="270" spans="1:4" ht="15" customHeight="1">
       <c r="A270" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B270" s="5">
         <v>850</v>
@@ -5882,7 +5835,7 @@
     </row>
     <row r="271" spans="1:4" ht="15" customHeight="1">
       <c r="A271" s="42" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B271" s="4">
         <v>140</v>
@@ -5896,7 +5849,7 @@
     </row>
     <row r="272" spans="1:4" ht="15" customHeight="1">
       <c r="A272" s="42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B272" s="4">
         <v>124</v>
@@ -5910,7 +5863,7 @@
     </row>
     <row r="273" spans="1:4" ht="15" customHeight="1">
       <c r="A273" s="42" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B273" s="4">
         <v>132</v>
@@ -5924,7 +5877,7 @@
     </row>
     <row r="274" spans="1:4" ht="15" customHeight="1">
       <c r="A274" s="42" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="B274" s="4">
         <v>105</v>
@@ -5938,7 +5891,7 @@
     </row>
     <row r="275" spans="1:4" ht="15" customHeight="1">
       <c r="A275" s="43" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="B275" s="4">
         <v>100</v>
@@ -5952,7 +5905,7 @@
     </row>
     <row r="276" spans="1:4" ht="15" customHeight="1">
       <c r="A276" s="42" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="B276" s="4">
         <v>200</v>
@@ -5966,7 +5919,7 @@
     </row>
     <row r="277" spans="1:4" ht="15" customHeight="1">
       <c r="A277" s="42" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B277" s="4">
         <v>33</v>
@@ -5980,7 +5933,7 @@
     </row>
     <row r="278" spans="1:4" ht="15" customHeight="1">
       <c r="A278" s="42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B278" s="4">
         <v>78</v>
@@ -5994,7 +5947,7 @@
     </row>
     <row r="279" spans="1:4" ht="15" customHeight="1">
       <c r="A279" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B279" s="4">
         <v>362</v>
@@ -6008,7 +5961,7 @@
     </row>
     <row r="280" spans="1:4" ht="15" customHeight="1">
       <c r="A280" s="42" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B280" s="4">
         <v>50</v>
@@ -6022,7 +5975,7 @@
     </row>
     <row r="281" spans="1:4" ht="15" customHeight="1">
       <c r="A281" s="42" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B281" s="4">
         <v>80</v>
@@ -6036,7 +5989,7 @@
     </row>
     <row r="282" spans="1:4" ht="15" customHeight="1">
       <c r="A282" s="42" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B282" s="4">
         <v>100</v>
@@ -6050,7 +6003,7 @@
     </row>
     <row r="283" spans="1:4" ht="15" customHeight="1">
       <c r="A283" s="42" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="B283" s="4">
         <v>60</v>
@@ -6064,7 +6017,7 @@
     </row>
     <row r="284" spans="1:4" ht="15" customHeight="1">
       <c r="A284" s="42" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B284" s="4">
         <v>130</v>
@@ -6078,7 +6031,7 @@
     </row>
     <row r="285" spans="1:4" ht="15" customHeight="1">
       <c r="A285" s="33" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B285" s="4">
         <v>94</v>
@@ -6092,7 +6045,7 @@
     </row>
     <row r="286" spans="1:4" ht="15" customHeight="1">
       <c r="A286" s="34" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B286" s="4">
         <v>150</v>
@@ -6106,7 +6059,7 @@
     </row>
     <row r="287" spans="1:4" ht="15" customHeight="1">
       <c r="A287" s="33" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B287" s="4">
         <v>90</v>
@@ -6120,7 +6073,7 @@
     </row>
     <row r="288" spans="1:4" ht="15" customHeight="1">
       <c r="A288" s="34" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B288" s="4">
         <v>260</v>
@@ -6134,7 +6087,7 @@
     </row>
     <row r="289" spans="1:4" ht="15" customHeight="1">
       <c r="A289" s="33" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B289" s="4">
         <v>80</v>
@@ -6148,7 +6101,7 @@
     </row>
     <row r="290" spans="1:4" ht="15" customHeight="1">
       <c r="A290" s="33" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B290" s="4">
         <v>125</v>
@@ -6162,7 +6115,7 @@
     </row>
     <row r="291" spans="1:4" ht="15" customHeight="1">
       <c r="A291" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B291" s="4">
         <v>407</v>
@@ -6174,7 +6127,7 @@
     </row>
     <row r="292" spans="1:4" ht="15" customHeight="1">
       <c r="A292" s="46" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B292" s="4">
         <v>45</v>
@@ -6202,7 +6155,7 @@
     </row>
     <row r="294" spans="1:4" ht="15" customHeight="1">
       <c r="A294" s="46" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B294" s="4">
         <v>65</v>
@@ -6216,7 +6169,7 @@
     </row>
     <row r="295" spans="1:4" ht="15" customHeight="1">
       <c r="A295" s="46" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B295" s="4">
         <v>104</v>
@@ -6230,7 +6183,7 @@
     </row>
     <row r="296" spans="1:4" ht="15" customHeight="1">
       <c r="A296" s="46" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B296" s="4">
         <v>130</v>
@@ -6244,7 +6197,7 @@
     </row>
     <row r="297" spans="1:4" ht="15" customHeight="1">
       <c r="A297" s="46" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B297" s="4">
         <v>44</v>
@@ -6258,7 +6211,7 @@
     </row>
     <row r="298" spans="1:4" ht="15" customHeight="1">
       <c r="A298" s="15" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B298" s="5">
         <v>705</v>
@@ -6272,7 +6225,7 @@
     </row>
     <row r="299" spans="1:4" ht="15" customHeight="1">
       <c r="A299" s="15" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B299" s="5">
         <v>592</v>
@@ -6286,7 +6239,7 @@
     </row>
     <row r="300" spans="1:4" ht="15" customHeight="1">
       <c r="A300" s="15" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B300" s="5">
         <v>500</v>
@@ -6300,7 +6253,7 @@
     </row>
     <row r="301" spans="1:4" ht="15" customHeight="1">
       <c r="A301" s="15" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B301" s="5">
         <v>777</v>
@@ -6314,7 +6267,7 @@
     </row>
     <row r="302" spans="1:4" ht="15" customHeight="1">
       <c r="A302" s="15" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B302" s="5">
         <v>786</v>
@@ -6328,7 +6281,7 @@
     </row>
     <row r="303" spans="1:4" ht="15" customHeight="1">
       <c r="A303" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B303" s="4">
         <v>379</v>
@@ -6342,7 +6295,7 @@
     </row>
     <row r="304" spans="1:4" ht="15" customHeight="1">
       <c r="A304" s="15" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B304" s="5">
         <v>704</v>
@@ -6356,7 +6309,7 @@
     </row>
     <row r="305" spans="1:4" ht="15" customHeight="1">
       <c r="A305" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B305" s="5">
         <v>544</v>
@@ -6370,7 +6323,7 @@
     </row>
     <row r="306" spans="1:4" ht="15" customHeight="1">
       <c r="A306" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B306" s="5">
         <v>818</v>
@@ -6384,7 +6337,7 @@
     </row>
     <row r="307" spans="1:4" ht="15" customHeight="1">
       <c r="A307" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B307" s="5">
         <v>705</v>
@@ -6398,7 +6351,7 @@
     </row>
     <row r="308" spans="1:4" ht="15" customHeight="1">
       <c r="A308" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B308" s="4">
         <v>458</v>
@@ -6412,7 +6365,7 @@
     </row>
     <row r="309" spans="1:4" ht="15" customHeight="1">
       <c r="A309" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B309" s="5">
         <v>690</v>
@@ -6426,7 +6379,7 @@
     </row>
     <row r="310" spans="1:4" ht="15" customHeight="1">
       <c r="A310" s="21" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B310" s="4">
         <v>100</v>
@@ -6440,7 +6393,7 @@
     </row>
     <row r="311" spans="1:4" ht="15" customHeight="1">
       <c r="A311" s="20" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B311" s="4">
         <v>250</v>
@@ -6454,7 +6407,7 @@
     </row>
     <row r="312" spans="1:4" ht="15" customHeight="1">
       <c r="A312" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B312" s="4">
         <v>100</v>
@@ -6468,7 +6421,7 @@
     </row>
     <row r="313" spans="1:4" ht="15" customHeight="1">
       <c r="A313" s="20" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B313" s="4">
         <v>130</v>
@@ -6496,7 +6449,7 @@
     </row>
     <row r="315" spans="1:4" ht="15" customHeight="1">
       <c r="A315" s="21" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B315" s="4">
         <v>0</v>
@@ -6510,7 +6463,7 @@
     </row>
     <row r="316" spans="1:4" ht="15" customHeight="1">
       <c r="A316" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B316" s="4">
         <v>3</v>
@@ -6524,7 +6477,7 @@
     </row>
     <row r="317" spans="1:4" ht="15" customHeight="1">
       <c r="A317" s="21" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B317" s="4">
         <v>50</v>
@@ -6536,7 +6489,7 @@
     </row>
     <row r="318" spans="1:4" ht="15" customHeight="1">
       <c r="A318" s="20" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B318" s="5">
         <v>400</v>
@@ -6550,7 +6503,7 @@
     </row>
     <row r="319" spans="1:4" ht="15" customHeight="1">
       <c r="A319" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B319" s="4">
         <v>151</v>
@@ -6564,7 +6517,7 @@
     </row>
     <row r="320" spans="1:4" ht="15" customHeight="1">
       <c r="A320" s="15" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B320" s="5">
         <v>452</v>
@@ -6578,7 +6531,7 @@
     </row>
     <row r="321" spans="1:4" ht="15" customHeight="1">
       <c r="A321" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B321" s="4">
         <v>160</v>
@@ -6592,7 +6545,7 @@
     </row>
     <row r="322" spans="1:4" ht="15" customHeight="1">
       <c r="A322" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B322" s="4">
         <v>90</v>
@@ -6606,7 +6559,7 @@
     </row>
     <row r="323" spans="1:4" ht="15" customHeight="1">
       <c r="A323" s="15" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B323" s="4">
         <v>120</v>
@@ -6620,7 +6573,7 @@
     </row>
     <row r="324" spans="1:4" ht="15" customHeight="1">
       <c r="A324" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B324" s="4">
         <v>139</v>
@@ -6634,7 +6587,7 @@
     </row>
     <row r="325" spans="1:4" ht="15" customHeight="1">
       <c r="A325" s="20" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B325" s="4">
         <v>157</v>
@@ -6648,7 +6601,7 @@
     </row>
     <row r="326" spans="1:4" ht="15" customHeight="1">
       <c r="A326" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B326" s="4">
         <v>274</v>
@@ -6662,7 +6615,7 @@
     </row>
     <row r="327" spans="1:4" ht="15" customHeight="1">
       <c r="A327" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B327" s="4">
         <v>225</v>
@@ -6676,7 +6629,7 @@
     </row>
     <row r="328" spans="1:4" ht="15" customHeight="1">
       <c r="A328" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B328" s="4">
         <v>249</v>
@@ -6690,7 +6643,7 @@
     </row>
     <row r="329" spans="1:4" ht="15" customHeight="1">
       <c r="A329" s="15" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="B329" s="5">
         <v>502</v>
@@ -6704,7 +6657,7 @@
     </row>
     <row r="330" spans="1:4" ht="15" customHeight="1">
       <c r="A330" s="21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B330" s="4">
         <v>112</v>
@@ -6718,7 +6671,7 @@
     </row>
     <row r="331" spans="1:4" ht="15" customHeight="1">
       <c r="A331" s="20" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B331" s="4">
         <v>108</v>
@@ -6732,7 +6685,7 @@
     </row>
     <row r="332" spans="1:4" ht="15" customHeight="1">
       <c r="A332" s="20" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B332" s="4">
         <v>126</v>
@@ -6746,7 +6699,7 @@
     </row>
     <row r="333" spans="1:4" ht="15" customHeight="1">
       <c r="A333" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B333" s="5">
         <v>1390</v>
@@ -6760,7 +6713,7 @@
     </row>
     <row r="334" spans="1:4" ht="15" customHeight="1">
       <c r="A334" s="15" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B334" s="4">
         <v>380</v>
@@ -6774,7 +6727,7 @@
     </row>
     <row r="335" spans="1:4" ht="15" customHeight="1">
       <c r="A335" s="15" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B335" s="4">
         <v>130</v>
@@ -6788,7 +6741,7 @@
     </row>
     <row r="336" spans="1:4" ht="15" customHeight="1">
       <c r="A336" s="20" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B336" s="4">
         <v>103</v>
@@ -6802,7 +6755,7 @@
     </row>
     <row r="337" spans="1:4" ht="15" customHeight="1">
       <c r="A337" s="35" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B337" s="4">
         <v>31</v>
@@ -6816,7 +6769,7 @@
     </row>
     <row r="338" spans="1:4" ht="15" customHeight="1">
       <c r="A338" s="15" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B338" s="4">
         <v>260</v>
@@ -6830,7 +6783,7 @@
     </row>
     <row r="339" spans="1:4" ht="15" customHeight="1">
       <c r="A339" s="36" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B339" s="4">
         <v>355</v>
@@ -6844,7 +6797,7 @@
     </row>
     <row r="340" spans="1:4" ht="15" customHeight="1">
       <c r="A340" s="36" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B340" s="4">
         <v>335</v>
@@ -6858,7 +6811,7 @@
     </row>
     <row r="341" spans="1:4" ht="15" customHeight="1">
       <c r="A341" s="36" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B341" s="4">
         <v>300</v>
@@ -6872,7 +6825,7 @@
     </row>
     <row r="342" spans="1:4" ht="15" customHeight="1">
       <c r="A342" s="36" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B342" s="4">
         <v>348</v>
@@ -6886,7 +6839,7 @@
     </row>
     <row r="343" spans="1:4" ht="15" customHeight="1">
       <c r="A343" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B343" s="4">
         <v>219</v>
@@ -6900,7 +6853,7 @@
     </row>
     <row r="344" spans="1:4" ht="15" customHeight="1">
       <c r="A344" s="33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B344" s="4">
         <v>32</v>
@@ -6914,7 +6867,7 @@
     </row>
     <row r="345" spans="1:4" ht="15" customHeight="1">
       <c r="A345" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B345" s="4">
         <v>70</v>
@@ -6928,7 +6881,7 @@
     </row>
     <row r="346" spans="1:4" ht="15" customHeight="1">
       <c r="A346" s="25" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B346" s="4">
         <v>70</v>
@@ -6942,7 +6895,7 @@
     </row>
     <row r="347" spans="1:4" ht="15" customHeight="1">
       <c r="A347" s="39" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B347" s="4">
         <v>160</v>
@@ -6956,7 +6909,7 @@
     </row>
     <row r="348" spans="1:4" ht="15" customHeight="1">
       <c r="A348" s="39" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B348" s="4">
         <v>120</v>
@@ -6970,7 +6923,7 @@
     </row>
     <row r="349" spans="1:4" ht="15" customHeight="1">
       <c r="A349" s="39" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B349" s="4">
         <v>220</v>
@@ -6984,7 +6937,7 @@
     </row>
     <row r="350" spans="1:4" ht="15" customHeight="1">
       <c r="A350" s="39" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="B350" s="4">
         <v>100</v>
@@ -6998,7 +6951,7 @@
     </row>
     <row r="351" spans="1:4" ht="15" customHeight="1">
       <c r="A351" s="39" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B351" s="4">
         <v>200</v>
@@ -7012,7 +6965,7 @@
     </row>
     <row r="352" spans="1:4" ht="15" customHeight="1">
       <c r="A352" s="20" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="B352" s="4">
         <v>150</v>
@@ -7026,7 +6979,7 @@
     </row>
     <row r="353" spans="1:4" ht="15" customHeight="1">
       <c r="A353" s="20" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B353" s="4">
         <v>100</v>
@@ -7040,7 +6993,7 @@
     </row>
     <row r="354" spans="1:4" ht="15" customHeight="1">
       <c r="A354" s="20" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B354" s="4">
         <v>100</v>
@@ -7054,7 +7007,7 @@
     </row>
     <row r="355" spans="1:4" ht="15" customHeight="1">
       <c r="A355" s="20" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B355" s="4">
         <v>145</v>
@@ -7068,7 +7021,7 @@
     </row>
     <row r="356" spans="1:4" ht="15" customHeight="1">
       <c r="A356" s="20" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B356" s="4">
         <v>338</v>
@@ -7082,7 +7035,7 @@
     </row>
     <row r="357" spans="1:4" ht="15" customHeight="1">
       <c r="A357" s="20" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B357" s="4">
         <v>209</v>
@@ -7096,7 +7049,7 @@
     </row>
     <row r="358" spans="1:4" ht="15" customHeight="1">
       <c r="A358" s="20" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B358" s="4">
         <v>131</v>
@@ -7110,7 +7063,7 @@
     </row>
     <row r="359" spans="1:4" ht="15" customHeight="1">
       <c r="A359" s="17" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="B359" s="4">
         <v>1</v>
@@ -7122,7 +7075,7 @@
     </row>
     <row r="360" spans="1:4" ht="15" customHeight="1">
       <c r="A360" s="21" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B360" s="4">
         <v>0</v>
@@ -7136,7 +7089,7 @@
     </row>
     <row r="361" spans="1:4" ht="15" customHeight="1">
       <c r="A361" s="19" t="s">
-        <v>121</v>
+        <v>382</v>
       </c>
       <c r="B361" s="4">
         <v>1</v>
@@ -7148,13 +7101,13 @@
     </row>
     <row r="362" spans="1:4" ht="15" customHeight="1">
       <c r="A362" s="28" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="B362" s="4">
         <v>1</v>
       </c>
       <c r="C362" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D362" s="7">
         <v>8</v>
@@ -7162,7 +7115,7 @@
     </row>
     <row r="363" spans="1:4" ht="15" customHeight="1">
       <c r="A363" s="21" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B363" s="4">
         <v>10.8</v>
@@ -7174,7 +7127,7 @@
     </row>
     <row r="364" spans="1:4" ht="15" customHeight="1">
       <c r="A364" s="21" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B364" s="4">
         <v>7.5</v>
@@ -7186,7 +7139,7 @@
     </row>
     <row r="365" spans="1:4" ht="15" customHeight="1">
       <c r="A365" s="21" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B365" s="4">
         <v>9</v>
@@ -7200,7 +7153,7 @@
     </row>
     <row r="366" spans="1:4" ht="15" customHeight="1">
       <c r="A366" s="21" t="s">
-        <v>236</v>
+        <v>384</v>
       </c>
       <c r="B366" s="4">
         <v>50</v>
@@ -7212,7 +7165,7 @@
     </row>
     <row r="367" spans="1:4" ht="15" customHeight="1">
       <c r="A367" s="21" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B367" s="4">
         <v>10</v>
@@ -7224,7 +7177,7 @@
     </row>
     <row r="368" spans="1:4" ht="15" customHeight="1">
       <c r="A368" s="21" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B368" s="4">
         <v>37</v>
@@ -7238,7 +7191,7 @@
     </row>
     <row r="369" spans="1:4" ht="15" customHeight="1">
       <c r="A369" s="20" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B369" s="4">
         <v>400</v>
@@ -7252,7 +7205,7 @@
     </row>
     <row r="370" spans="1:4" ht="15" customHeight="1">
       <c r="A370" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B370" s="4">
         <v>549</v>
@@ -7266,7 +7219,7 @@
     </row>
     <row r="371" spans="1:4" ht="15" customHeight="1">
       <c r="A371" s="20" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B371" s="4">
         <v>7.5</v>
@@ -7278,7 +7231,7 @@
     </row>
     <row r="372" spans="1:4" ht="15" customHeight="1">
       <c r="A372" s="20" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="B372" s="4">
         <v>150</v>
@@ -7290,7 +7243,7 @@
     </row>
     <row r="373" spans="1:4" ht="15" customHeight="1">
       <c r="A373" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B373" s="4">
         <v>49</v>
@@ -7304,7 +7257,7 @@
     </row>
     <row r="374" spans="1:4" ht="15" customHeight="1">
       <c r="A374" s="21" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B374" s="4">
         <v>80</v>
@@ -7318,7 +7271,7 @@
     </row>
     <row r="375" spans="1:4" ht="15" customHeight="1">
       <c r="A375" s="21" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="B375" s="4">
         <v>78</v>
@@ -7332,7 +7285,7 @@
     </row>
     <row r="376" spans="1:4" ht="15" customHeight="1">
       <c r="A376" s="21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B376" s="4">
         <v>3</v>
@@ -7346,7 +7299,7 @@
     </row>
     <row r="377" spans="1:4" ht="15" customHeight="1">
       <c r="A377" s="47" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="B377" s="4">
         <v>1.9</v>
@@ -7360,7 +7313,7 @@
     </row>
     <row r="378" spans="1:4" ht="15" customHeight="1">
       <c r="A378" s="47" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="B378" s="40">
         <v>0</v>
@@ -7374,7 +7327,7 @@
     </row>
     <row r="379" spans="1:4" ht="15" customHeight="1">
       <c r="A379" s="21" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="B379" s="4">
         <v>10</v>
@@ -7388,7 +7341,7 @@
     </row>
     <row r="380" spans="1:4" ht="15" customHeight="1">
       <c r="A380" s="44" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="B380" s="4">
         <v>27</v>
@@ -7402,7 +7355,7 @@
     </row>
     <row r="381" spans="1:4" ht="15" customHeight="1">
       <c r="A381" s="45" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B381" s="4">
         <v>27</v>
@@ -7416,7 +7369,7 @@
     </row>
     <row r="382" spans="1:4" ht="15" customHeight="1">
       <c r="A382" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B382" s="4">
         <v>82</v>
@@ -7430,7 +7383,7 @@
     </row>
     <row r="383" spans="1:4" ht="15" customHeight="1">
       <c r="A383" s="21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B383" s="4">
         <v>102</v>
@@ -7444,7 +7397,7 @@
     </row>
     <row r="384" spans="1:4" ht="15" customHeight="1">
       <c r="A384" s="21" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B384" s="4">
         <v>0</v>

--- a/KPH-AI.xlsx
+++ b/KPH-AI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="389">
   <si>
     <t>Praziluk</t>
   </si>
@@ -1241,6 +1241,15 @@
   </si>
   <si>
     <t>Mleko za kafu porcija 10ml</t>
+  </si>
+  <si>
+    <t>Hleb sa marmeladom namaz snita</t>
+  </si>
+  <si>
+    <t>Hleb sa medom namaz snita</t>
+  </si>
+  <si>
+    <t>Kiflice sa dzemom</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1469,11 +1478,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1613,6 +1663,36 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2053,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D384"/>
+  <dimension ref="A1:D387"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54.8984375" style="37" customWidth="1"/>
@@ -5251,9 +5331,7 @@
       <c r="A229" s="20" t="s">
         <v>376</v>
       </c>
-      <c r="B229" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="B229" s="4"/>
       <c r="C229" s="2">
         <v>15</v>
       </c>
@@ -7048,89 +7126,93 @@
       </c>
     </row>
     <row r="358" spans="1:4" ht="15" customHeight="1">
-      <c r="A358" s="20" t="s">
+      <c r="A358" s="51" t="s">
         <v>331</v>
       </c>
-      <c r="B358" s="4">
+      <c r="B358" s="52">
         <v>131</v>
       </c>
-      <c r="C358" s="2">
+      <c r="C358" s="53">
         <v>120</v>
       </c>
-      <c r="D358" s="7">
+      <c r="D358" s="54">
         <v>635</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="15" customHeight="1">
-      <c r="A359" s="17" t="s">
+    <row r="359" spans="1:4" s="50" customFormat="1" ht="17.850000000000001" customHeight="1">
+      <c r="A359" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="B359" s="59">
+        <v>42</v>
+      </c>
+      <c r="C359" s="59">
+        <v>14</v>
+      </c>
+      <c r="D359" s="59">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" s="50" customFormat="1" ht="16.7" customHeight="1">
+      <c r="A360" s="59" t="s">
+        <v>387</v>
+      </c>
+      <c r="B360" s="59">
+        <v>53</v>
+      </c>
+      <c r="C360" s="59">
+        <v>9</v>
+      </c>
+      <c r="D360" s="59">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" s="50" customFormat="1" ht="19.05" customHeight="1">
+      <c r="A361" s="59" t="s">
+        <v>388</v>
+      </c>
+      <c r="B361" s="59">
+        <v>77</v>
+      </c>
+      <c r="C361" s="59">
+        <v>47</v>
+      </c>
+      <c r="D361" s="59">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" ht="15" customHeight="1">
+      <c r="A362" s="55" t="s">
         <v>381</v>
       </c>
-      <c r="B359" s="4">
+      <c r="B362" s="56">
         <v>1</v>
       </c>
-      <c r="C359" s="2">
+      <c r="C362" s="57">
         <v>1</v>
       </c>
-      <c r="D359" s="7"/>
-    </row>
-    <row r="360" spans="1:4" ht="15" customHeight="1">
-      <c r="A360" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="B360" s="4">
-        <v>0</v>
-      </c>
-      <c r="C360" s="2">
-        <v>0</v>
-      </c>
-      <c r="D360" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" ht="15" customHeight="1">
-      <c r="A361" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="B361" s="4">
-        <v>1</v>
-      </c>
-      <c r="C361" s="2">
-        <v>1</v>
-      </c>
-      <c r="D361" s="7"/>
-    </row>
-    <row r="362" spans="1:4" ht="15" customHeight="1">
-      <c r="A362" s="28" t="s">
-        <v>383</v>
-      </c>
-      <c r="B362" s="4">
-        <v>1</v>
-      </c>
-      <c r="C362" s="2">
-        <v>17</v>
-      </c>
-      <c r="D362" s="7">
-        <v>8</v>
-      </c>
+      <c r="D362" s="58"/>
     </row>
     <row r="363" spans="1:4" ht="15" customHeight="1">
       <c r="A363" s="21" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B363" s="4">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="C363" s="2">
+        <v>0</v>
+      </c>
+      <c r="D363" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" ht="15" customHeight="1">
+      <c r="A364" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B364" s="4">
         <v>1</v>
-      </c>
-      <c r="D363" s="7"/>
-    </row>
-    <row r="364" spans="1:4" ht="15" customHeight="1">
-      <c r="A364" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="B364" s="4">
-        <v>7.5</v>
       </c>
       <c r="C364" s="2">
         <v>1</v>
@@ -7138,286 +7220,324 @@
       <c r="D364" s="7"/>
     </row>
     <row r="365" spans="1:4" ht="15" customHeight="1">
-      <c r="A365" s="21" t="s">
-        <v>348</v>
+      <c r="A365" s="28" t="s">
+        <v>383</v>
       </c>
       <c r="B365" s="4">
-        <v>9</v>
-      </c>
-      <c r="C365" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="C365" s="2">
+        <v>17</v>
       </c>
       <c r="D365" s="7">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15" customHeight="1">
       <c r="A366" s="21" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="B366" s="4">
-        <v>50</v>
+        <v>10.8</v>
       </c>
       <c r="C366" s="2">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D366" s="7"/>
     </row>
     <row r="367" spans="1:4" ht="15" customHeight="1">
       <c r="A367" s="21" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B367" s="4">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="C367" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D367" s="7"/>
     </row>
     <row r="368" spans="1:4" ht="15" customHeight="1">
       <c r="A368" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="B368" s="4">
+        <v>9</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D368" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" ht="15" customHeight="1">
+      <c r="A369" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="B369" s="4">
+        <v>50</v>
+      </c>
+      <c r="C369" s="2">
+        <v>50</v>
+      </c>
+      <c r="D369" s="7"/>
+    </row>
+    <row r="370" spans="1:4" ht="15" customHeight="1">
+      <c r="A370" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="B370" s="4">
+        <v>10</v>
+      </c>
+      <c r="C370" s="2">
+        <v>100</v>
+      </c>
+      <c r="D370" s="7"/>
+    </row>
+    <row r="371" spans="1:4" ht="15" customHeight="1">
+      <c r="A371" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B368" s="4">
+      <c r="B371" s="4">
         <v>37</v>
       </c>
-      <c r="C368" s="2">
+      <c r="C371" s="2">
         <v>1</v>
       </c>
-      <c r="D368" s="7">
+      <c r="D371" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="369" spans="1:4" ht="15" customHeight="1">
-      <c r="A369" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="B369" s="4">
-        <v>400</v>
-      </c>
-      <c r="C369" s="2">
-        <v>60</v>
-      </c>
-      <c r="D369" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4" ht="15" customHeight="1">
-      <c r="A370" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B370" s="4">
-        <v>549</v>
-      </c>
-      <c r="C370" s="2">
-        <v>152</v>
-      </c>
-      <c r="D370" s="7">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" ht="15" customHeight="1">
-      <c r="A371" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="B371" s="4">
-        <v>7.5</v>
-      </c>
-      <c r="C371" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="D371" s="7"/>
     </row>
     <row r="372" spans="1:4" ht="15" customHeight="1">
       <c r="A372" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B372" s="4">
+        <v>400</v>
+      </c>
+      <c r="C372" s="2">
+        <v>60</v>
+      </c>
+      <c r="D372" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" ht="15" customHeight="1">
+      <c r="A373" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B373" s="4">
+        <v>549</v>
+      </c>
+      <c r="C373" s="2">
+        <v>152</v>
+      </c>
+      <c r="D373" s="7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" ht="15" customHeight="1">
+      <c r="A374" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="B374" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="C374" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="D374" s="7"/>
+    </row>
+    <row r="375" spans="1:4" ht="15" customHeight="1">
+      <c r="A375" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="B372" s="4">
+      <c r="B375" s="4">
         <v>150</v>
       </c>
-      <c r="C372" s="2">
+      <c r="C375" s="2">
         <v>90</v>
       </c>
-      <c r="D372" s="7"/>
-    </row>
-    <row r="373" spans="1:4" ht="15" customHeight="1">
-      <c r="A373" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B373" s="4">
-        <v>49</v>
-      </c>
-      <c r="C373" s="2">
-        <v>3</v>
-      </c>
-      <c r="D373" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4" ht="15" customHeight="1">
-      <c r="A374" s="21" t="s">
-        <v>366</v>
-      </c>
-      <c r="B374" s="4">
-        <v>80</v>
-      </c>
-      <c r="C374" s="2">
-        <v>35</v>
-      </c>
-      <c r="D374" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4" ht="15" customHeight="1">
-      <c r="A375" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="B375" s="4">
-        <v>78</v>
-      </c>
-      <c r="C375" s="2">
-        <v>80</v>
-      </c>
-      <c r="D375" s="7">
-        <v>39</v>
-      </c>
+      <c r="D375" s="7"/>
     </row>
     <row r="376" spans="1:4" ht="15" customHeight="1">
       <c r="A376" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B376" s="4">
+        <v>49</v>
+      </c>
+      <c r="C376" s="2">
         <v>3</v>
       </c>
-      <c r="C376" s="2">
-        <v>0</v>
-      </c>
       <c r="D376" s="7">
-        <v>91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15" customHeight="1">
-      <c r="A377" s="47" t="s">
-        <v>352</v>
+      <c r="A377" s="21" t="s">
+        <v>366</v>
       </c>
       <c r="B377" s="4">
-        <v>1.9</v>
+        <v>80</v>
       </c>
       <c r="C377" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D377" s="7">
-        <v>219</v>
+        <v>4</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15" customHeight="1">
-      <c r="A378" s="47" t="s">
-        <v>353</v>
-      </c>
-      <c r="B378" s="40">
-        <v>0</v>
-      </c>
-      <c r="C378" s="41">
-        <v>0</v>
-      </c>
-      <c r="D378" s="41">
-        <v>119</v>
+      <c r="A378" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="B378" s="4">
+        <v>78</v>
+      </c>
+      <c r="C378" s="2">
+        <v>80</v>
+      </c>
+      <c r="D378" s="7">
+        <v>39</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15" customHeight="1">
       <c r="A379" s="21" t="s">
-        <v>351</v>
+        <v>118</v>
       </c>
       <c r="B379" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C379" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D379" s="7">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15" customHeight="1">
-      <c r="A380" s="44" t="s">
-        <v>361</v>
+      <c r="A380" s="47" t="s">
+        <v>352</v>
       </c>
       <c r="B380" s="4">
-        <v>27</v>
+        <v>1.9</v>
       </c>
       <c r="C380" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D380" s="7">
-        <v>10</v>
+        <v>219</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15" customHeight="1">
-      <c r="A381" s="45" t="s">
-        <v>362</v>
-      </c>
-      <c r="B381" s="4">
-        <v>27</v>
-      </c>
-      <c r="C381" s="2">
-        <v>13</v>
-      </c>
-      <c r="D381" s="7">
-        <v>5</v>
+      <c r="A381" s="47" t="s">
+        <v>353</v>
+      </c>
+      <c r="B381" s="40">
+        <v>0</v>
+      </c>
+      <c r="C381" s="41">
+        <v>0</v>
+      </c>
+      <c r="D381" s="41">
+        <v>119</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15" customHeight="1">
       <c r="A382" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="B382" s="4">
+        <v>10</v>
+      </c>
+      <c r="C382" s="2">
+        <v>3</v>
+      </c>
+      <c r="D382" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" ht="15" customHeight="1">
+      <c r="A383" s="44" t="s">
+        <v>361</v>
+      </c>
+      <c r="B383" s="4">
+        <v>27</v>
+      </c>
+      <c r="C383" s="2">
+        <v>20</v>
+      </c>
+      <c r="D383" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="15" customHeight="1">
+      <c r="A384" s="45" t="s">
+        <v>362</v>
+      </c>
+      <c r="B384" s="4">
+        <v>27</v>
+      </c>
+      <c r="C384" s="2">
+        <v>13</v>
+      </c>
+      <c r="D384" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" ht="15" customHeight="1">
+      <c r="A385" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B382" s="4">
+      <c r="B385" s="4">
         <v>82</v>
       </c>
-      <c r="C382" s="2">
+      <c r="C385" s="2">
         <v>15</v>
       </c>
-      <c r="D382" s="7">
+      <c r="D385" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="15" customHeight="1">
-      <c r="A383" s="21" t="s">
+    <row r="386" spans="1:4" ht="15" customHeight="1">
+      <c r="A386" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B383" s="4">
+      <c r="B386" s="4">
         <v>102</v>
       </c>
-      <c r="C383" s="2">
+      <c r="C386" s="2">
         <v>10</v>
       </c>
-      <c r="D383" s="7">
+      <c r="D386" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="15" customHeight="1">
-      <c r="A384" s="21" t="s">
+    <row r="387" spans="1:4" ht="15" customHeight="1">
+      <c r="A387" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="B384" s="4">
+      <c r="B387" s="4">
         <v>0</v>
       </c>
-      <c r="C384" s="2">
+      <c r="C387" s="2">
         <v>0</v>
       </c>
-      <c r="D384" s="7">
+      <c r="D387" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B1048576">
+  <conditionalFormatting sqref="B1:B358 B362:B1048576">
     <cfRule type="cellIs" dxfId="9" priority="24" operator="between">
       <formula>200</formula>
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
+  <conditionalFormatting sqref="D1:D358 D362:D1048576">
     <cfRule type="cellIs" dxfId="8" priority="20" operator="between">
       <formula>1</formula>
       <formula>300</formula>
@@ -7427,19 +7547,19 @@
       <formula>150</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
+  <conditionalFormatting sqref="D1:D358 D362:D1048576">
     <cfRule type="cellIs" dxfId="6" priority="13" operator="between">
       <formula>301</formula>
       <formula>2000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B384">
+  <conditionalFormatting sqref="B2:B358 B362:B387">
     <cfRule type="cellIs" dxfId="5" priority="18" operator="between">
       <formula>400</formula>
       <formula>5000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B384">
+  <conditionalFormatting sqref="B1:B358 B362:B387">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="between">
       <formula>100</formula>
       <formula>200</formula>
@@ -7449,7 +7569,7 @@
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
+  <conditionalFormatting sqref="C1:C358 C362:C1048576">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="between">
       <formula>301</formula>
       <formula>2000</formula>
